--- a/web_dashboard/Orden_Fabricacion_MRP_Codiagro.xlsx
+++ b/web_dashboard/Orden_Fabricacion_MRP_Codiagro.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Orden de Fabricación'!$A$8:$Q$301</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Plan Graneles por Mes'!$A$5:$M$87</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'SlowMovers &amp; NoMovers'!$A$8:$P$139</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'SlowMovers &amp; NoMovers'!$A$8:$O$139</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -845,7 +845,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Horizonte: Oct 26 (N) + Nov 26 + Dic 26 (3 meses)  |  Ámbito: Global (Nacional + Exportación)  |  Exportación: Siempre Sobre Pedido  |  Fecha Emisión: 07/10/2026 08:31</t>
+          <t xml:space="preserve">  Horizonte: Oct 26 (N) + Nov 26 + Dic 26 (3 meses)  |  Ámbito: Global (Nacional + Exportación)  |  Exportación: Siempre Sobre Pedido  |  Fecha Emisión: 07/10/2026 10:01</t>
         </is>
       </c>
     </row>
@@ -20782,7 +20782,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Horizonte: Octubre 2026 - Diciembre 2026  |  Total Graneles Químicos a Fabricar en Planta  |  Fecha Emisión: 07/10/2026 08:31</t>
+          <t xml:space="preserve">  Horizonte: Octubre 2026 - Diciembre 2026  |  Total Graneles Químicos a Fabricar en Planta  |  Fecha Emisión: 07/10/2026 10:01</t>
         </is>
       </c>
     </row>
@@ -25206,18 +25206,17 @@
     <col width="36" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="24" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
     <col width="22" customWidth="1" min="14" max="14"/>
-    <col width="22" customWidth="1" min="15" max="15"/>
-    <col width="34" customWidth="1" min="16" max="16"/>
+    <col width="34" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -25230,7 +25229,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Premisa de Gestión: Previsiones exclusivamente del Mercado Nacional (España). La exportación se fabricará siempre sobre pedido.  |  Fecha: 07/10/2026 08:31</t>
+          <t xml:space="preserve">  Premisa de Gestión: Previsiones exclusivamente del Mercado Nacional (España). La exportación se fabricará siempre sobre pedido.  |  Fecha: 07/10/2026 10:01</t>
         </is>
       </c>
     </row>
@@ -25320,7 +25319,7 @@
           <t>3. PREVISIÓN MERCADO NACIONAL (L/KG)</t>
         </is>
       </c>
-      <c r="I7" s="47" t="inlineStr">
+      <c r="H7" s="47" t="inlineStr">
         <is>
           <t>4. EVALUACIÓN DE ROTACIÓN Y VALORACIÓN ECONÓMICA</t>
         </is>
@@ -25354,55 +25353,50 @@
       </c>
       <c r="F8" s="15" t="inlineStr">
         <is>
-          <t>Prev. Nac Q4 (L/Kg)</t>
+          <t>(N+2) (L/Kg)</t>
         </is>
       </c>
       <c r="G8" s="15" t="inlineStr">
         <is>
-          <t>Prev. Nac Q1-27 (L/Kg)</t>
-        </is>
-      </c>
-      <c r="H8" s="15" t="inlineStr">
-        <is>
-          <t>Prev. Nac 6 Meses (L/Kg)</t>
+          <t>(N+5) (L/Kg)</t>
+        </is>
+      </c>
+      <c r="H8" s="48" t="inlineStr">
+        <is>
+          <t>SlowMovers (L/Kg)</t>
         </is>
       </c>
       <c r="I8" s="48" t="inlineStr">
         <is>
-          <t>SlowMovers (L/Kg)</t>
+          <t>NoMovers (L/Kg)</t>
         </is>
       </c>
       <c r="J8" s="48" t="inlineStr">
         <is>
-          <t>NoMovers (L/Kg)</t>
-        </is>
-      </c>
-      <c r="K8" s="48" t="inlineStr">
-        <is>
           <t>Envases NoMover (u)</t>
         </is>
       </c>
-      <c r="L8" s="49" t="inlineStr">
+      <c r="K8" s="49" t="inlineStr">
         <is>
           <t>Clasificación Rotación</t>
         </is>
       </c>
+      <c r="L8" s="48" t="inlineStr">
+        <is>
+          <t>Precio Ref. (€/(L·Kg))</t>
+        </is>
+      </c>
       <c r="M8" s="48" t="inlineStr">
         <is>
-          <t>Precio Ref. (€/(L·Kg))</t>
+          <t>Inmovilizado NoMover (€)</t>
         </is>
       </c>
       <c r="N8" s="48" t="inlineStr">
         <is>
-          <t>Inmovilizado NoMover (€)</t>
-        </is>
-      </c>
-      <c r="O8" s="48" t="inlineStr">
-        <is>
           <t>Inmovilizado SlowMover (€)</t>
         </is>
       </c>
-      <c r="P8" s="50" t="inlineStr">
+      <c r="O8" s="50" t="inlineStr">
         <is>
           <t>Acción Comercial Recomendada</t>
         </is>
@@ -25440,29 +25434,26 @@
         <v>0</v>
       </c>
       <c r="I9" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="25" t="n">
         <v>792</v>
       </c>
-      <c r="K9" s="24" t="n">
+      <c r="J9" s="24" t="n">
         <v>792</v>
       </c>
-      <c r="L9" s="26" t="inlineStr">
+      <c r="K9" s="26" t="inlineStr">
         <is>
           <t>🔴 NoMover (&gt;6M Nac)</t>
         </is>
       </c>
-      <c r="M9" s="52" t="n">
+      <c r="L9" s="52" t="n">
         <v>6.350509718</v>
       </c>
-      <c r="N9" s="53" t="n">
+      <c r="M9" s="53" t="n">
         <v>5029.6</v>
       </c>
-      <c r="O9" s="52" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" s="20" t="inlineStr">
+      <c r="N9" s="52" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" s="20" t="inlineStr">
         <is>
           <t>Sin Demanda Nacional (Inmovilizado Crítico)</t>
         </is>
@@ -25500,29 +25491,26 @@
         <v>45</v>
       </c>
       <c r="I10" s="34" t="n">
-        <v>45</v>
-      </c>
-      <c r="J10" s="34" t="n">
         <v>2080</v>
       </c>
-      <c r="K10" s="33" t="n">
+      <c r="J10" s="33" t="n">
         <v>416</v>
       </c>
-      <c r="L10" s="26" t="inlineStr">
+      <c r="K10" s="26" t="inlineStr">
         <is>
           <t>🔴 NoMover (&gt;6M Nac)</t>
         </is>
       </c>
-      <c r="M10" s="55" t="n">
+      <c r="L10" s="55" t="n">
         <v>1.807611829</v>
       </c>
-      <c r="N10" s="56" t="n">
+      <c r="M10" s="56" t="n">
         <v>3759.83</v>
       </c>
-      <c r="O10" s="57" t="n">
+      <c r="N10" s="57" t="n">
         <v>81.34</v>
       </c>
-      <c r="P10" s="29" t="inlineStr">
+      <c r="O10" s="29" t="inlineStr">
         <is>
           <t>Plan Choque Comercial Nac / Oferta</t>
         </is>
@@ -25560,29 +25548,26 @@
         <v>0</v>
       </c>
       <c r="I11" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="25" t="n">
         <v>7210</v>
       </c>
-      <c r="K11" s="24" t="n">
+      <c r="J11" s="24" t="n">
         <v>1442</v>
       </c>
-      <c r="L11" s="26" t="inlineStr">
+      <c r="K11" s="26" t="inlineStr">
         <is>
           <t>🔴 NoMover (&gt;6M Nac)</t>
         </is>
       </c>
-      <c r="M11" s="52" t="n">
+      <c r="L11" s="52" t="n">
         <v>0.519747475</v>
       </c>
-      <c r="N11" s="53" t="n">
+      <c r="M11" s="53" t="n">
         <v>3747.38</v>
       </c>
-      <c r="O11" s="52" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" s="20" t="inlineStr">
+      <c r="N11" s="52" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" s="20" t="inlineStr">
         <is>
           <t>Sin Demanda Nacional (Inmovilizado Crítico)</t>
         </is>
@@ -25620,29 +25605,26 @@
         <v>85</v>
       </c>
       <c r="I12" s="34" t="n">
-        <v>85</v>
-      </c>
-      <c r="J12" s="34" t="n">
         <v>775</v>
       </c>
-      <c r="K12" s="33" t="n">
+      <c r="J12" s="33" t="n">
         <v>155</v>
       </c>
-      <c r="L12" s="26" t="inlineStr">
+      <c r="K12" s="26" t="inlineStr">
         <is>
           <t>🔴 NoMover (&gt;6M Nac)</t>
         </is>
       </c>
-      <c r="M12" s="55" t="n">
+      <c r="L12" s="55" t="n">
         <v>3.984564732</v>
       </c>
-      <c r="N12" s="56" t="n">
+      <c r="M12" s="56" t="n">
         <v>3088.04</v>
       </c>
-      <c r="O12" s="57" t="n">
+      <c r="N12" s="57" t="n">
         <v>338.69</v>
       </c>
-      <c r="P12" s="29" t="inlineStr">
+      <c r="O12" s="29" t="inlineStr">
         <is>
           <t>Plan Choque Comercial Nac / Oferta</t>
         </is>
@@ -25677,32 +25659,29 @@
         <v>40</v>
       </c>
       <c r="H13" s="25" t="n">
-        <v>1140</v>
+        <v>40</v>
       </c>
       <c r="I13" s="25" t="n">
-        <v>40</v>
-      </c>
-      <c r="J13" s="25" t="n">
         <v>10540</v>
       </c>
-      <c r="K13" s="24" t="n">
+      <c r="J13" s="24" t="n">
         <v>527</v>
       </c>
-      <c r="L13" s="26" t="inlineStr">
+      <c r="K13" s="26" t="inlineStr">
         <is>
           <t>🔴 NoMover (&gt;6M Nac)</t>
         </is>
       </c>
-      <c r="M13" s="52" t="n">
+      <c r="L13" s="52" t="n">
         <v>0.269282211</v>
       </c>
-      <c r="N13" s="53" t="n">
+      <c r="M13" s="53" t="n">
         <v>2838.23</v>
       </c>
-      <c r="O13" s="58" t="n">
+      <c r="N13" s="58" t="n">
         <v>10.77</v>
       </c>
-      <c r="P13" s="20" t="inlineStr">
+      <c r="O13" s="20" t="inlineStr">
         <is>
           <t>Plan Choque Comercial Nac / Oferta</t>
         </is>
@@ -25740,29 +25719,26 @@
         <v>0</v>
       </c>
       <c r="I14" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="34" t="n">
         <v>640</v>
       </c>
-      <c r="K14" s="33" t="n">
+      <c r="J14" s="33" t="n">
         <v>32</v>
       </c>
-      <c r="L14" s="26" t="inlineStr">
+      <c r="K14" s="26" t="inlineStr">
         <is>
           <t>🔴 NoMover (&gt;6M Nac)</t>
         </is>
       </c>
-      <c r="M14" s="55" t="n">
+      <c r="L14" s="55" t="n">
         <v>4.198893797</v>
       </c>
-      <c r="N14" s="56" t="n">
+      <c r="M14" s="56" t="n">
         <v>2687.29</v>
       </c>
-      <c r="O14" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" s="29" t="inlineStr">
+      <c r="N14" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" s="29" t="inlineStr">
         <is>
           <t>Sin Demanda Nacional (Inmovilizado Crítico)</t>
         </is>
@@ -25800,29 +25776,26 @@
         <v>0</v>
       </c>
       <c r="I15" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="25" t="n">
         <v>1000</v>
       </c>
-      <c r="K15" s="24" t="n">
+      <c r="J15" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="L15" s="26" t="inlineStr">
+      <c r="K15" s="26" t="inlineStr">
         <is>
           <t>🔴 NoMover (&gt;6M Nac)</t>
         </is>
       </c>
-      <c r="M15" s="52" t="n">
+      <c r="L15" s="52" t="n">
         <v>2.106345208</v>
       </c>
-      <c r="N15" s="53" t="n">
+      <c r="M15" s="53" t="n">
         <v>2106.35</v>
       </c>
-      <c r="O15" s="52" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" s="20" t="inlineStr">
+      <c r="N15" s="52" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" s="20" t="inlineStr">
         <is>
           <t>Sin Demanda Nacional (Inmovilizado Crítico)</t>
         </is>
@@ -25857,32 +25830,29 @@
         <v>890</v>
       </c>
       <c r="H16" s="34" t="n">
-        <v>3315</v>
+        <v>890</v>
       </c>
       <c r="I16" s="34" t="n">
-        <v>890</v>
-      </c>
-      <c r="J16" s="34" t="n">
         <v>1315</v>
       </c>
-      <c r="K16" s="33" t="n">
+      <c r="J16" s="33" t="n">
         <v>263</v>
       </c>
-      <c r="L16" s="26" t="inlineStr">
+      <c r="K16" s="26" t="inlineStr">
         <is>
           <t>🔴 NoMover (&gt;6M Nac)</t>
         </is>
       </c>
-      <c r="M16" s="55" t="n">
+      <c r="L16" s="55" t="n">
         <v>1.57814305</v>
       </c>
-      <c r="N16" s="56" t="n">
+      <c r="M16" s="56" t="n">
         <v>2075.26</v>
       </c>
-      <c r="O16" s="57" t="n">
+      <c r="N16" s="57" t="n">
         <v>1404.55</v>
       </c>
-      <c r="P16" s="29" t="inlineStr">
+      <c r="O16" s="29" t="inlineStr">
         <is>
           <t>Plan Choque Comercial Nac / Oferta</t>
         </is>
@@ -25920,29 +25890,26 @@
         <v>0</v>
       </c>
       <c r="I17" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" s="25" t="n">
         <v>1200</v>
       </c>
-      <c r="K17" s="24" t="n">
+      <c r="J17" s="24" t="n">
         <v>1200</v>
       </c>
-      <c r="L17" s="26" t="inlineStr">
+      <c r="K17" s="26" t="inlineStr">
         <is>
           <t>🔴 NoMover (&gt;6M Nac)</t>
         </is>
       </c>
-      <c r="M17" s="52" t="n">
+      <c r="L17" s="52" t="n">
         <v>1.723612921</v>
       </c>
-      <c r="N17" s="53" t="n">
+      <c r="M17" s="53" t="n">
         <v>2068.34</v>
       </c>
-      <c r="O17" s="52" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" s="20" t="inlineStr">
+      <c r="N17" s="52" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" s="20" t="inlineStr">
         <is>
           <t>Sin Demanda Nacional (Inmovilizado Crítico)</t>
         </is>
@@ -25980,29 +25947,26 @@
         <v>25</v>
       </c>
       <c r="I18" s="34" t="n">
-        <v>25</v>
-      </c>
-      <c r="J18" s="34" t="n">
         <v>971</v>
       </c>
-      <c r="K18" s="33" t="n">
+      <c r="J18" s="33" t="n">
         <v>971</v>
       </c>
-      <c r="L18" s="26" t="inlineStr">
+      <c r="K18" s="26" t="inlineStr">
         <is>
           <t>🔴 NoMover (&gt;6M Nac)</t>
         </is>
       </c>
-      <c r="M18" s="55" t="n">
+      <c r="L18" s="55" t="n">
         <v>1.689842879</v>
       </c>
-      <c r="N18" s="56" t="n">
+      <c r="M18" s="56" t="n">
         <v>1640.84</v>
       </c>
-      <c r="O18" s="57" t="n">
+      <c r="N18" s="57" t="n">
         <v>42.25</v>
       </c>
-      <c r="P18" s="29" t="inlineStr">
+      <c r="O18" s="29" t="inlineStr">
         <is>
           <t>Plan Choque Comercial Nac / Oferta</t>
         </is>
@@ -26037,32 +26001,29 @@
         <v>580</v>
       </c>
       <c r="H19" s="25" t="n">
-        <v>780</v>
+        <v>580</v>
       </c>
       <c r="I19" s="25" t="n">
-        <v>580</v>
-      </c>
-      <c r="J19" s="25" t="n">
         <v>765</v>
       </c>
-      <c r="K19" s="24" t="n">
+      <c r="J19" s="24" t="n">
         <v>153</v>
       </c>
-      <c r="L19" s="26" t="inlineStr">
+      <c r="K19" s="26" t="inlineStr">
         <is>
           <t>🔴 NoMover (&gt;6M Nac)</t>
         </is>
       </c>
-      <c r="M19" s="52" t="n">
+      <c r="L19" s="52" t="n">
         <v>1.990086214</v>
       </c>
-      <c r="N19" s="53" t="n">
+      <c r="M19" s="53" t="n">
         <v>1522.42</v>
       </c>
-      <c r="O19" s="58" t="n">
+      <c r="N19" s="58" t="n">
         <v>1154.25</v>
       </c>
-      <c r="P19" s="20" t="inlineStr">
+      <c r="O19" s="20" t="inlineStr">
         <is>
           <t>Plan Choque Comercial Nac / Oferta</t>
         </is>
@@ -26097,32 +26058,29 @@
         <v>320</v>
       </c>
       <c r="H20" s="34" t="n">
-        <v>1320</v>
+        <v>320</v>
       </c>
       <c r="I20" s="34" t="n">
-        <v>320</v>
-      </c>
-      <c r="J20" s="34" t="n">
         <v>1080</v>
       </c>
-      <c r="K20" s="33" t="n">
+      <c r="J20" s="33" t="n">
         <v>54</v>
       </c>
-      <c r="L20" s="26" t="inlineStr">
+      <c r="K20" s="26" t="inlineStr">
         <is>
           <t>🔴 NoMover (&gt;6M Nac)</t>
         </is>
       </c>
-      <c r="M20" s="55" t="n">
+      <c r="L20" s="55" t="n">
         <v>1.391901777</v>
       </c>
-      <c r="N20" s="56" t="n">
+      <c r="M20" s="56" t="n">
         <v>1503.25</v>
       </c>
-      <c r="O20" s="57" t="n">
+      <c r="N20" s="57" t="n">
         <v>445.41</v>
       </c>
-      <c r="P20" s="29" t="inlineStr">
+      <c r="O20" s="29" t="inlineStr">
         <is>
           <t>Plan Choque Comercial Nac / Oferta</t>
         </is>
@@ -26157,32 +26115,29 @@
         <v>4800</v>
       </c>
       <c r="H21" s="25" t="n">
-        <v>12500</v>
+        <v>4800</v>
       </c>
       <c r="I21" s="25" t="n">
-        <v>4800</v>
-      </c>
-      <c r="J21" s="25" t="n">
         <v>3520</v>
       </c>
-      <c r="K21" s="24" t="n">
+      <c r="J21" s="24" t="n">
         <v>176</v>
       </c>
-      <c r="L21" s="26" t="inlineStr">
+      <c r="K21" s="26" t="inlineStr">
         <is>
           <t>🔴 NoMover (&gt;6M Nac)</t>
         </is>
       </c>
-      <c r="M21" s="52" t="n">
+      <c r="L21" s="52" t="n">
         <v>0.420535887</v>
       </c>
-      <c r="N21" s="53" t="n">
+      <c r="M21" s="53" t="n">
         <v>1480.29</v>
       </c>
-      <c r="O21" s="58" t="n">
+      <c r="N21" s="58" t="n">
         <v>2018.57</v>
       </c>
-      <c r="P21" s="20" t="inlineStr">
+      <c r="O21" s="20" t="inlineStr">
         <is>
           <t>Plan Choque Comercial Nac / Oferta</t>
         </is>
@@ -26220,29 +26175,26 @@
         <v>65</v>
       </c>
       <c r="I22" s="34" t="n">
-        <v>65</v>
-      </c>
-      <c r="J22" s="34" t="n">
         <v>735</v>
       </c>
-      <c r="K22" s="33" t="n">
+      <c r="J22" s="33" t="n">
         <v>147</v>
       </c>
-      <c r="L22" s="26" t="inlineStr">
+      <c r="K22" s="26" t="inlineStr">
         <is>
           <t>🔴 NoMover (&gt;6M Nac)</t>
         </is>
       </c>
-      <c r="M22" s="55" t="n">
+      <c r="L22" s="55" t="n">
         <v>1.872598763</v>
       </c>
-      <c r="N22" s="56" t="n">
+      <c r="M22" s="56" t="n">
         <v>1376.36</v>
       </c>
-      <c r="O22" s="57" t="n">
+      <c r="N22" s="57" t="n">
         <v>121.72</v>
       </c>
-      <c r="P22" s="29" t="inlineStr">
+      <c r="O22" s="29" t="inlineStr">
         <is>
           <t>Plan Choque Comercial Nac / Oferta</t>
         </is>
@@ -26280,29 +26232,26 @@
         <v>0</v>
       </c>
       <c r="I23" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" s="25" t="n">
         <v>2715</v>
       </c>
-      <c r="K23" s="24" t="n">
+      <c r="J23" s="24" t="n">
         <v>543</v>
       </c>
-      <c r="L23" s="26" t="inlineStr">
+      <c r="K23" s="26" t="inlineStr">
         <is>
           <t>🔴 NoMover (&gt;6M Nac)</t>
         </is>
       </c>
-      <c r="M23" s="52" t="n">
+      <c r="L23" s="52" t="n">
         <v>0.482514194</v>
       </c>
-      <c r="N23" s="53" t="n">
+      <c r="M23" s="53" t="n">
         <v>1310.03</v>
       </c>
-      <c r="O23" s="52" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" s="20" t="inlineStr">
+      <c r="N23" s="52" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" s="20" t="inlineStr">
         <is>
           <t>Sin Demanda Nacional (Inmovilizado Crítico)</t>
         </is>
@@ -26340,29 +26289,26 @@
         <v>0</v>
       </c>
       <c r="I24" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" s="34" t="n">
         <v>732</v>
       </c>
-      <c r="K24" s="33" t="n">
+      <c r="J24" s="33" t="n">
         <v>732</v>
       </c>
-      <c r="L24" s="26" t="inlineStr">
+      <c r="K24" s="26" t="inlineStr">
         <is>
           <t>🔴 NoMover (&gt;6M Nac)</t>
         </is>
       </c>
-      <c r="M24" s="55" t="n">
+      <c r="L24" s="55" t="n">
         <v>1.693123212</v>
       </c>
-      <c r="N24" s="56" t="n">
+      <c r="M24" s="56" t="n">
         <v>1239.37</v>
       </c>
-      <c r="O24" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" s="29" t="inlineStr">
+      <c r="N24" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" s="29" t="inlineStr">
         <is>
           <t>Sin Demanda Nacional (Inmovilizado Crítico)</t>
         </is>
@@ -26400,29 +26346,26 @@
         <v>76</v>
       </c>
       <c r="I25" s="25" t="n">
-        <v>76</v>
-      </c>
-      <c r="J25" s="25" t="n">
         <v>512</v>
       </c>
-      <c r="K25" s="24" t="n">
+      <c r="J25" s="24" t="n">
         <v>512</v>
       </c>
-      <c r="L25" s="26" t="inlineStr">
+      <c r="K25" s="26" t="inlineStr">
         <is>
           <t>🔴 NoMover (&gt;6M Nac)</t>
         </is>
       </c>
-      <c r="M25" s="52" t="n">
+      <c r="L25" s="52" t="n">
         <v>2.209337264</v>
       </c>
-      <c r="N25" s="53" t="n">
+      <c r="M25" s="53" t="n">
         <v>1131.18</v>
       </c>
-      <c r="O25" s="58" t="n">
+      <c r="N25" s="58" t="n">
         <v>167.91</v>
       </c>
-      <c r="P25" s="20" t="inlineStr">
+      <c r="O25" s="20" t="inlineStr">
         <is>
           <t>Plan Choque Comercial Nac / Oferta</t>
         </is>
@@ -26460,29 +26403,26 @@
         <v>221</v>
       </c>
       <c r="I26" s="34" t="n">
-        <v>221</v>
-      </c>
-      <c r="J26" s="34" t="n">
         <v>883</v>
       </c>
-      <c r="K26" s="33" t="n">
+      <c r="J26" s="33" t="n">
         <v>883</v>
       </c>
-      <c r="L26" s="26" t="inlineStr">
+      <c r="K26" s="26" t="inlineStr">
         <is>
           <t>🔴 NoMover (&gt;6M Nac)</t>
         </is>
       </c>
-      <c r="M26" s="55" t="n">
+      <c r="L26" s="55" t="n">
         <v>1.269033263</v>
       </c>
-      <c r="N26" s="56" t="n">
+      <c r="M26" s="56" t="n">
         <v>1120.56</v>
       </c>
-      <c r="O26" s="57" t="n">
+      <c r="N26" s="57" t="n">
         <v>280.46</v>
       </c>
-      <c r="P26" s="29" t="inlineStr">
+      <c r="O26" s="29" t="inlineStr">
         <is>
           <t>Plan Choque Comercial Nac / Oferta</t>
         </is>
@@ -26520,29 +26460,26 @@
         <v>0</v>
       </c>
       <c r="I27" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" s="25" t="n">
         <v>480</v>
       </c>
-      <c r="K27" s="24" t="n">
+      <c r="J27" s="24" t="n">
         <v>96</v>
       </c>
-      <c r="L27" s="26" t="inlineStr">
+      <c r="K27" s="26" t="inlineStr">
         <is>
           <t>🔴 NoMover (&gt;6M Nac)</t>
         </is>
       </c>
-      <c r="M27" s="52" t="n">
+      <c r="L27" s="52" t="n">
         <v>1.958383848</v>
       </c>
-      <c r="N27" s="53" t="n">
+      <c r="M27" s="53" t="n">
         <v>940.02</v>
       </c>
-      <c r="O27" s="52" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" s="20" t="inlineStr">
+      <c r="N27" s="52" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" s="20" t="inlineStr">
         <is>
           <t>Sin Demanda Nacional (Inmovilizado Crítico)</t>
         </is>
@@ -26580,29 +26517,26 @@
         <v>0</v>
       </c>
       <c r="I28" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" s="34" t="n">
         <v>715</v>
       </c>
-      <c r="K28" s="33" t="n">
+      <c r="J28" s="33" t="n">
         <v>143</v>
       </c>
-      <c r="L28" s="26" t="inlineStr">
+      <c r="K28" s="26" t="inlineStr">
         <is>
           <t>🔴 NoMover (&gt;6M Nac)</t>
         </is>
       </c>
-      <c r="M28" s="55" t="n">
+      <c r="L28" s="55" t="n">
         <v>1.305743992</v>
       </c>
-      <c r="N28" s="56" t="n">
+      <c r="M28" s="56" t="n">
         <v>933.61</v>
       </c>
-      <c r="O28" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" s="29" t="inlineStr">
+      <c r="N28" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" s="29" t="inlineStr">
         <is>
           <t>Sin Demanda Nacional (Inmovilizado Crítico)</t>
         </is>
@@ -26637,32 +26571,29 @@
         <v>4000</v>
       </c>
       <c r="H29" s="25" t="n">
-        <v>9600</v>
+        <v>4000</v>
       </c>
       <c r="I29" s="25" t="n">
-        <v>4000</v>
-      </c>
-      <c r="J29" s="25" t="n">
         <v>1600</v>
       </c>
-      <c r="K29" s="24" t="n">
+      <c r="J29" s="24" t="n">
         <v>8</v>
       </c>
-      <c r="L29" s="26" t="inlineStr">
+      <c r="K29" s="26" t="inlineStr">
         <is>
           <t>🔴 NoMover (&gt;6M Nac)</t>
         </is>
       </c>
-      <c r="M29" s="52" t="n">
+      <c r="L29" s="52" t="n">
         <v>0.529995259</v>
       </c>
-      <c r="N29" s="53" t="n">
+      <c r="M29" s="53" t="n">
         <v>847.99</v>
       </c>
-      <c r="O29" s="58" t="n">
+      <c r="N29" s="58" t="n">
         <v>2119.98</v>
       </c>
-      <c r="P29" s="20" t="inlineStr">
+      <c r="O29" s="20" t="inlineStr">
         <is>
           <t>Plan Choque Comercial Nac / Oferta</t>
         </is>
@@ -26700,29 +26631,26 @@
         <v>0</v>
       </c>
       <c r="I30" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" s="34" t="n">
         <v>1000</v>
       </c>
-      <c r="K30" s="33" t="n">
+      <c r="J30" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="L30" s="26" t="inlineStr">
+      <c r="K30" s="26" t="inlineStr">
         <is>
           <t>🔴 NoMover (&gt;6M Nac)</t>
         </is>
       </c>
-      <c r="M30" s="55" t="n">
+      <c r="L30" s="55" t="n">
         <v>0.843079557</v>
       </c>
-      <c r="N30" s="56" t="n">
+      <c r="M30" s="56" t="n">
         <v>843.08</v>
       </c>
-      <c r="O30" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" s="29" t="inlineStr">
+      <c r="N30" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" s="29" t="inlineStr">
         <is>
           <t>Sin Demanda Nacional (Inmovilizado Crítico)</t>
         </is>
@@ -26760,29 +26688,26 @@
         <v>1455</v>
       </c>
       <c r="I31" s="25" t="n">
-        <v>1455</v>
-      </c>
-      <c r="J31" s="25" t="n">
         <v>2125</v>
       </c>
-      <c r="K31" s="24" t="n">
+      <c r="J31" s="24" t="n">
         <v>425</v>
       </c>
-      <c r="L31" s="26" t="inlineStr">
+      <c r="K31" s="26" t="inlineStr">
         <is>
           <t>🔴 NoMover (&gt;6M Nac)</t>
         </is>
       </c>
-      <c r="M31" s="52" t="n">
+      <c r="L31" s="52" t="n">
         <v>0.378253729</v>
       </c>
-      <c r="N31" s="53" t="n">
+      <c r="M31" s="53" t="n">
         <v>803.79</v>
       </c>
-      <c r="O31" s="58" t="n">
+      <c r="N31" s="58" t="n">
         <v>550.36</v>
       </c>
-      <c r="P31" s="20" t="inlineStr">
+      <c r="O31" s="20" t="inlineStr">
         <is>
           <t>Plan Choque Comercial Nac / Oferta</t>
         </is>
@@ -26820,29 +26745,26 @@
         <v>43</v>
       </c>
       <c r="I32" s="34" t="n">
-        <v>43</v>
-      </c>
-      <c r="J32" s="34" t="n">
         <v>281</v>
       </c>
-      <c r="K32" s="33" t="n">
+      <c r="J32" s="33" t="n">
         <v>281</v>
       </c>
-      <c r="L32" s="26" t="inlineStr">
+      <c r="K32" s="26" t="inlineStr">
         <is>
           <t>🔴 NoMover (&gt;6M Nac)</t>
         </is>
       </c>
-      <c r="M32" s="55" t="n">
+      <c r="L32" s="55" t="n">
         <v>2.666815882</v>
       </c>
-      <c r="N32" s="56" t="n">
+      <c r="M32" s="56" t="n">
         <v>749.38</v>
       </c>
-      <c r="O32" s="57" t="n">
+      <c r="N32" s="57" t="n">
         <v>114.67</v>
       </c>
-      <c r="P32" s="29" t="inlineStr">
+      <c r="O32" s="29" t="inlineStr">
         <is>
           <t>Plan Choque Comercial Nac / Oferta</t>
         </is>
@@ -26880,29 +26802,26 @@
         <v>20</v>
       </c>
       <c r="I33" s="25" t="n">
-        <v>20</v>
-      </c>
-      <c r="J33" s="25" t="n">
         <v>580</v>
       </c>
-      <c r="K33" s="24" t="n">
+      <c r="J33" s="24" t="n">
         <v>116</v>
       </c>
-      <c r="L33" s="26" t="inlineStr">
+      <c r="K33" s="26" t="inlineStr">
         <is>
           <t>🔴 NoMover (&gt;6M Nac)</t>
         </is>
       </c>
-      <c r="M33" s="52" t="n">
+      <c r="L33" s="52" t="n">
         <v>1.221485831</v>
       </c>
-      <c r="N33" s="53" t="n">
+      <c r="M33" s="53" t="n">
         <v>708.46</v>
       </c>
-      <c r="O33" s="58" t="n">
+      <c r="N33" s="58" t="n">
         <v>24.43</v>
       </c>
-      <c r="P33" s="20" t="inlineStr">
+      <c r="O33" s="20" t="inlineStr">
         <is>
           <t>Plan Choque Comercial Nac / Oferta</t>
         </is>
@@ -26940,29 +26859,26 @@
         <v>40</v>
       </c>
       <c r="I34" s="34" t="n">
-        <v>40</v>
-      </c>
-      <c r="J34" s="34" t="n">
         <v>360</v>
       </c>
-      <c r="K34" s="33" t="n">
+      <c r="J34" s="33" t="n">
         <v>72</v>
       </c>
-      <c r="L34" s="26" t="inlineStr">
+      <c r="K34" s="26" t="inlineStr">
         <is>
           <t>🔴 NoMover (&gt;6M Nac)</t>
         </is>
       </c>
-      <c r="M34" s="55" t="n">
+      <c r="L34" s="55" t="n">
         <v>1.937974417</v>
       </c>
-      <c r="N34" s="56" t="n">
+      <c r="M34" s="56" t="n">
         <v>697.67</v>
       </c>
-      <c r="O34" s="57" t="n">
+      <c r="N34" s="57" t="n">
         <v>77.52</v>
       </c>
-      <c r="P34" s="29" t="inlineStr">
+      <c r="O34" s="29" t="inlineStr">
         <is>
           <t>Plan Choque Comercial Nac / Oferta</t>
         </is>
@@ -27000,29 +26916,26 @@
         <v>215</v>
       </c>
       <c r="I35" s="25" t="n">
-        <v>215</v>
-      </c>
-      <c r="J35" s="25" t="n">
         <v>505</v>
       </c>
-      <c r="K35" s="24" t="n">
+      <c r="J35" s="24" t="n">
         <v>101</v>
       </c>
-      <c r="L35" s="26" t="inlineStr">
+      <c r="K35" s="26" t="inlineStr">
         <is>
           <t>🔴 NoMover (&gt;6M Nac)</t>
         </is>
       </c>
-      <c r="M35" s="52" t="n">
+      <c r="L35" s="52" t="n">
         <v>1.293061752</v>
       </c>
-      <c r="N35" s="53" t="n">
+      <c r="M35" s="53" t="n">
         <v>653</v>
       </c>
-      <c r="O35" s="58" t="n">
+      <c r="N35" s="58" t="n">
         <v>278.01</v>
       </c>
-      <c r="P35" s="20" t="inlineStr">
+      <c r="O35" s="20" t="inlineStr">
         <is>
           <t>Plan Choque Comercial Nac / Oferta</t>
         </is>
@@ -27060,29 +26973,26 @@
         <v>0</v>
       </c>
       <c r="I36" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" s="34" t="n">
         <v>545</v>
       </c>
-      <c r="K36" s="33" t="n">
+      <c r="J36" s="33" t="n">
         <v>109</v>
       </c>
-      <c r="L36" s="26" t="inlineStr">
+      <c r="K36" s="26" t="inlineStr">
         <is>
           <t>🔴 NoMover (&gt;6M Nac)</t>
         </is>
       </c>
-      <c r="M36" s="55" t="n">
+      <c r="L36" s="55" t="n">
         <v>1.158218336</v>
       </c>
-      <c r="N36" s="56" t="n">
+      <c r="M36" s="56" t="n">
         <v>631.23</v>
       </c>
-      <c r="O36" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" s="29" t="inlineStr">
+      <c r="N36" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" s="29" t="inlineStr">
         <is>
           <t>Sin Demanda Nacional (Inmovilizado Crítico)</t>
         </is>
@@ -27120,29 +27030,26 @@
         <v>100</v>
       </c>
       <c r="I37" s="25" t="n">
-        <v>100</v>
-      </c>
-      <c r="J37" s="25" t="n">
         <v>520</v>
       </c>
-      <c r="K37" s="24" t="n">
+      <c r="J37" s="24" t="n">
         <v>26</v>
       </c>
-      <c r="L37" s="26" t="inlineStr">
+      <c r="K37" s="26" t="inlineStr">
         <is>
           <t>🔴 NoMover (&gt;6M Nac)</t>
         </is>
       </c>
-      <c r="M37" s="52" t="n">
+      <c r="L37" s="52" t="n">
         <v>1.166121141</v>
       </c>
-      <c r="N37" s="53" t="n">
+      <c r="M37" s="53" t="n">
         <v>606.38</v>
       </c>
-      <c r="O37" s="58" t="n">
+      <c r="N37" s="58" t="n">
         <v>116.61</v>
       </c>
-      <c r="P37" s="20" t="inlineStr">
+      <c r="O37" s="20" t="inlineStr">
         <is>
           <t>Plan Choque Comercial Nac / Oferta</t>
         </is>
@@ -27180,29 +27087,26 @@
         <v>78</v>
       </c>
       <c r="I38" s="34" t="n">
-        <v>78</v>
-      </c>
-      <c r="J38" s="34" t="n">
         <v>90</v>
       </c>
-      <c r="K38" s="33" t="n">
+      <c r="J38" s="33" t="n">
         <v>90</v>
       </c>
-      <c r="L38" s="26" t="inlineStr">
+      <c r="K38" s="26" t="inlineStr">
         <is>
           <t>🔴 NoMover (&gt;6M Nac)</t>
         </is>
       </c>
-      <c r="M38" s="55" t="n">
+      <c r="L38" s="55" t="n">
         <v>5.748149757</v>
       </c>
-      <c r="N38" s="56" t="n">
+      <c r="M38" s="56" t="n">
         <v>517.33</v>
       </c>
-      <c r="O38" s="57" t="n">
+      <c r="N38" s="57" t="n">
         <v>448.36</v>
       </c>
-      <c r="P38" s="29" t="inlineStr">
+      <c r="O38" s="29" t="inlineStr">
         <is>
           <t>Plan Choque Comercial Nac / Oferta</t>
         </is>
@@ -27240,29 +27144,26 @@
         <v>240</v>
       </c>
       <c r="I39" s="25" t="n">
-        <v>240</v>
-      </c>
-      <c r="J39" s="25" t="n">
         <v>270</v>
       </c>
-      <c r="K39" s="24" t="n">
+      <c r="J39" s="24" t="n">
         <v>54</v>
       </c>
-      <c r="L39" s="26" t="inlineStr">
+      <c r="K39" s="26" t="inlineStr">
         <is>
           <t>🔴 NoMover (&gt;6M Nac)</t>
         </is>
       </c>
-      <c r="M39" s="52" t="n">
+      <c r="L39" s="52" t="n">
         <v>1.88519534</v>
       </c>
-      <c r="N39" s="53" t="n">
+      <c r="M39" s="53" t="n">
         <v>509</v>
       </c>
-      <c r="O39" s="58" t="n">
+      <c r="N39" s="58" t="n">
         <v>452.45</v>
       </c>
-      <c r="P39" s="20" t="inlineStr">
+      <c r="O39" s="20" t="inlineStr">
         <is>
           <t>Plan Choque Comercial Nac / Oferta</t>
         </is>
@@ -27300,29 +27201,26 @@
         <v>90</v>
       </c>
       <c r="I40" s="34" t="n">
-        <v>90</v>
-      </c>
-      <c r="J40" s="34" t="n">
         <v>710</v>
       </c>
-      <c r="K40" s="33" t="n">
+      <c r="J40" s="33" t="n">
         <v>142</v>
       </c>
-      <c r="L40" s="26" t="inlineStr">
+      <c r="K40" s="26" t="inlineStr">
         <is>
           <t>🔴 NoMover (&gt;6M Nac)</t>
         </is>
       </c>
-      <c r="M40" s="55" t="n">
+      <c r="L40" s="55" t="n">
         <v>0.663997466</v>
       </c>
-      <c r="N40" s="56" t="n">
+      <c r="M40" s="56" t="n">
         <v>471.44</v>
       </c>
-      <c r="O40" s="57" t="n">
+      <c r="N40" s="57" t="n">
         <v>59.76</v>
       </c>
-      <c r="P40" s="29" t="inlineStr">
+      <c r="O40" s="29" t="inlineStr">
         <is>
           <t>Plan Choque Comercial Nac / Oferta</t>
         </is>
@@ -27360,29 +27258,26 @@
         <v>475</v>
       </c>
       <c r="I41" s="25" t="n">
-        <v>475</v>
-      </c>
-      <c r="J41" s="25" t="n">
         <v>300</v>
       </c>
-      <c r="K41" s="24" t="n">
+      <c r="J41" s="24" t="n">
         <v>60</v>
       </c>
-      <c r="L41" s="26" t="inlineStr">
+      <c r="K41" s="26" t="inlineStr">
         <is>
           <t>🔴 NoMover (&gt;6M Nac)</t>
         </is>
       </c>
-      <c r="M41" s="52" t="n">
+      <c r="L41" s="52" t="n">
         <v>1.407487685</v>
       </c>
-      <c r="N41" s="53" t="n">
+      <c r="M41" s="53" t="n">
         <v>422.25</v>
       </c>
-      <c r="O41" s="58" t="n">
+      <c r="N41" s="58" t="n">
         <v>668.5599999999999</v>
       </c>
-      <c r="P41" s="20" t="inlineStr">
+      <c r="O41" s="20" t="inlineStr">
         <is>
           <t>Plan Choque Comercial Nac / Oferta</t>
         </is>
@@ -27420,29 +27315,26 @@
         <v>0</v>
       </c>
       <c r="I42" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="J42" s="34" t="n">
         <v>265</v>
       </c>
-      <c r="K42" s="33" t="n">
+      <c r="J42" s="33" t="n">
         <v>53</v>
       </c>
-      <c r="L42" s="26" t="inlineStr">
+      <c r="K42" s="26" t="inlineStr">
         <is>
           <t>🔴 NoMover (&gt;6M Nac)</t>
         </is>
       </c>
-      <c r="M42" s="55" t="n">
+      <c r="L42" s="55" t="n">
         <v>1.575231243</v>
       </c>
-      <c r="N42" s="56" t="n">
+      <c r="M42" s="56" t="n">
         <v>417.44</v>
       </c>
-      <c r="O42" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="P42" s="29" t="inlineStr">
+      <c r="N42" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" s="29" t="inlineStr">
         <is>
           <t>Sin Demanda Nacional (Inmovilizado Crítico)</t>
         </is>
@@ -27480,29 +27372,26 @@
         <v>0</v>
       </c>
       <c r="I43" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J43" s="25" t="n">
         <v>400</v>
       </c>
-      <c r="K43" s="24" t="n">
+      <c r="J43" s="24" t="n">
         <v>80</v>
       </c>
-      <c r="L43" s="26" t="inlineStr">
+      <c r="K43" s="26" t="inlineStr">
         <is>
           <t>🔴 NoMover (&gt;6M Nac)</t>
         </is>
       </c>
-      <c r="M43" s="52" t="n">
+      <c r="L43" s="52" t="n">
         <v>0.953174241</v>
       </c>
-      <c r="N43" s="53" t="n">
+      <c r="M43" s="53" t="n">
         <v>381.27</v>
       </c>
-      <c r="O43" s="52" t="n">
-        <v>0</v>
-      </c>
-      <c r="P43" s="20" t="inlineStr">
+      <c r="N43" s="52" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" s="20" t="inlineStr">
         <is>
           <t>Sin Demanda Nacional (Inmovilizado Crítico)</t>
         </is>
@@ -27540,29 +27429,26 @@
         <v>0</v>
       </c>
       <c r="I44" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" s="34" t="n">
         <v>128</v>
       </c>
-      <c r="K44" s="33" t="n">
+      <c r="J44" s="33" t="n">
         <v>128</v>
       </c>
-      <c r="L44" s="26" t="inlineStr">
+      <c r="K44" s="26" t="inlineStr">
         <is>
           <t>🔴 NoMover (&gt;6M Nac)</t>
         </is>
       </c>
-      <c r="M44" s="55" t="n">
+      <c r="L44" s="55" t="n">
         <v>2.592611413</v>
       </c>
-      <c r="N44" s="56" t="n">
+      <c r="M44" s="56" t="n">
         <v>331.85</v>
       </c>
-      <c r="O44" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="P44" s="29" t="inlineStr">
+      <c r="N44" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" s="29" t="inlineStr">
         <is>
           <t>Sin Demanda Nacional (Inmovilizado Crítico)</t>
         </is>
@@ -27600,29 +27486,26 @@
         <v>75</v>
       </c>
       <c r="I45" s="25" t="n">
-        <v>75</v>
-      </c>
-      <c r="J45" s="25" t="n">
         <v>81</v>
       </c>
-      <c r="K45" s="24" t="n">
+      <c r="J45" s="24" t="n">
         <v>81</v>
       </c>
-      <c r="L45" s="26" t="inlineStr">
+      <c r="K45" s="26" t="inlineStr">
         <is>
           <t>🔴 NoMover (&gt;6M Nac)</t>
         </is>
       </c>
-      <c r="M45" s="52" t="n">
+      <c r="L45" s="52" t="n">
         <v>3.519051434</v>
       </c>
-      <c r="N45" s="53" t="n">
+      <c r="M45" s="53" t="n">
         <v>285.04</v>
       </c>
-      <c r="O45" s="58" t="n">
+      <c r="N45" s="58" t="n">
         <v>263.93</v>
       </c>
-      <c r="P45" s="20" t="inlineStr">
+      <c r="O45" s="20" t="inlineStr">
         <is>
           <t>Plan Choque Comercial Nac / Oferta</t>
         </is>
@@ -27657,32 +27540,29 @@
         <v>0</v>
       </c>
       <c r="H46" s="34" t="n">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="I46" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="J46" s="34" t="n">
         <v>43</v>
       </c>
-      <c r="K46" s="33" t="n">
+      <c r="J46" s="33" t="n">
         <v>43</v>
       </c>
-      <c r="L46" s="26" t="inlineStr">
+      <c r="K46" s="26" t="inlineStr">
         <is>
           <t>🔴 NoMover (&gt;6M Nac)</t>
         </is>
       </c>
-      <c r="M46" s="55" t="n">
+      <c r="L46" s="55" t="n">
         <v>5.153120375</v>
       </c>
-      <c r="N46" s="56" t="n">
+      <c r="M46" s="56" t="n">
         <v>221.58</v>
       </c>
-      <c r="O46" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="P46" s="29" t="inlineStr">
+      <c r="N46" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" s="29" t="inlineStr">
         <is>
           <t>Plan Choque Comercial Nac / Oferta</t>
         </is>
@@ -27720,29 +27600,26 @@
         <v>0</v>
       </c>
       <c r="I47" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J47" s="25" t="n">
         <v>36</v>
       </c>
-      <c r="K47" s="24" t="n">
+      <c r="J47" s="24" t="n">
         <v>36</v>
       </c>
-      <c r="L47" s="26" t="inlineStr">
+      <c r="K47" s="26" t="inlineStr">
         <is>
           <t>🔴 NoMover (&gt;6M Nac)</t>
         </is>
       </c>
-      <c r="M47" s="52" t="n">
+      <c r="L47" s="52" t="n">
         <v>5.952042248</v>
       </c>
-      <c r="N47" s="53" t="n">
+      <c r="M47" s="53" t="n">
         <v>214.27</v>
       </c>
-      <c r="O47" s="52" t="n">
-        <v>0</v>
-      </c>
-      <c r="P47" s="20" t="inlineStr">
+      <c r="N47" s="52" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" s="20" t="inlineStr">
         <is>
           <t>Sin Demanda Nacional (Inmovilizado Crítico)</t>
         </is>
@@ -27780,29 +27657,26 @@
         <v>0</v>
       </c>
       <c r="I48" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" s="34" t="n">
         <v>132</v>
       </c>
-      <c r="K48" s="33" t="n">
+      <c r="J48" s="33" t="n">
         <v>132</v>
       </c>
-      <c r="L48" s="26" t="inlineStr">
+      <c r="K48" s="26" t="inlineStr">
         <is>
           <t>🔴 NoMover (&gt;6M Nac)</t>
         </is>
       </c>
-      <c r="M48" s="55" t="n">
+      <c r="L48" s="55" t="n">
         <v>1.606300393</v>
       </c>
-      <c r="N48" s="56" t="n">
+      <c r="M48" s="56" t="n">
         <v>212.03</v>
       </c>
-      <c r="O48" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="P48" s="29" t="inlineStr">
+      <c r="N48" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" s="29" t="inlineStr">
         <is>
           <t>Sin Demanda Nacional (Inmovilizado Crítico)</t>
         </is>
@@ -27840,29 +27714,26 @@
         <v>0</v>
       </c>
       <c r="I49" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J49" s="25" t="n">
         <v>200</v>
       </c>
-      <c r="K49" s="24" t="n">
+      <c r="J49" s="24" t="n">
         <v>40</v>
       </c>
-      <c r="L49" s="26" t="inlineStr">
+      <c r="K49" s="26" t="inlineStr">
         <is>
           <t>🔴 NoMover (&gt;6M Nac)</t>
         </is>
       </c>
-      <c r="M49" s="52" t="n">
+      <c r="L49" s="52" t="n">
         <v>0.948319953</v>
       </c>
-      <c r="N49" s="53" t="n">
+      <c r="M49" s="53" t="n">
         <v>189.66</v>
       </c>
-      <c r="O49" s="52" t="n">
-        <v>0</v>
-      </c>
-      <c r="P49" s="20" t="inlineStr">
+      <c r="N49" s="52" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" s="20" t="inlineStr">
         <is>
           <t>Sin Demanda Nacional (Inmovilizado Crítico)</t>
         </is>
@@ -27900,29 +27771,26 @@
         <v>0</v>
       </c>
       <c r="I50" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="J50" s="34" t="n">
         <v>105</v>
       </c>
-      <c r="K50" s="33" t="n">
+      <c r="J50" s="33" t="n">
         <v>21</v>
       </c>
-      <c r="L50" s="26" t="inlineStr">
+      <c r="K50" s="26" t="inlineStr">
         <is>
           <t>🔴 NoMover (&gt;6M Nac)</t>
         </is>
       </c>
-      <c r="M50" s="55" t="n">
+      <c r="L50" s="55" t="n">
         <v>1.791702254</v>
       </c>
-      <c r="N50" s="56" t="n">
+      <c r="M50" s="56" t="n">
         <v>188.13</v>
       </c>
-      <c r="O50" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="P50" s="29" t="inlineStr">
+      <c r="N50" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="O50" s="29" t="inlineStr">
         <is>
           <t>Sin Demanda Nacional (Inmovilizado Crítico)</t>
         </is>
@@ -27957,32 +27825,29 @@
         <v>0</v>
       </c>
       <c r="H51" s="25" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="I51" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J51" s="25" t="n">
         <v>270</v>
       </c>
-      <c r="K51" s="24" t="n">
+      <c r="J51" s="24" t="n">
         <v>54</v>
       </c>
-      <c r="L51" s="26" t="inlineStr">
+      <c r="K51" s="26" t="inlineStr">
         <is>
           <t>🔴 NoMover (&gt;6M Nac)</t>
         </is>
       </c>
-      <c r="M51" s="52" t="n">
+      <c r="L51" s="52" t="n">
         <v>0.638528424</v>
       </c>
-      <c r="N51" s="53" t="n">
+      <c r="M51" s="53" t="n">
         <v>172.4</v>
       </c>
-      <c r="O51" s="52" t="n">
-        <v>0</v>
-      </c>
-      <c r="P51" s="20" t="inlineStr">
+      <c r="N51" s="52" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" s="20" t="inlineStr">
         <is>
           <t>Plan Choque Comercial Nac / Oferta</t>
         </is>
@@ -28020,29 +27885,26 @@
         <v>0</v>
       </c>
       <c r="I52" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="J52" s="34" t="n">
         <v>81</v>
       </c>
-      <c r="K52" s="33" t="n">
+      <c r="J52" s="33" t="n">
         <v>81</v>
       </c>
-      <c r="L52" s="26" t="inlineStr">
+      <c r="K52" s="26" t="inlineStr">
         <is>
           <t>🔴 NoMover (&gt;6M Nac)</t>
         </is>
       </c>
-      <c r="M52" s="55" t="n">
+      <c r="L52" s="55" t="n">
         <v>2.074756176</v>
       </c>
-      <c r="N52" s="56" t="n">
+      <c r="M52" s="56" t="n">
         <v>168.06</v>
       </c>
-      <c r="O52" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="P52" s="29" t="inlineStr">
+      <c r="N52" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" s="29" t="inlineStr">
         <is>
           <t>Sin Demanda Nacional (Inmovilizado Crítico)</t>
         </is>
@@ -28080,29 +27942,26 @@
         <v>77</v>
       </c>
       <c r="I53" s="25" t="n">
-        <v>77</v>
-      </c>
-      <c r="J53" s="25" t="n">
         <v>67</v>
       </c>
-      <c r="K53" s="24" t="n">
+      <c r="J53" s="24" t="n">
         <v>67</v>
       </c>
-      <c r="L53" s="26" t="inlineStr">
+      <c r="K53" s="26" t="inlineStr">
         <is>
           <t>🔴 NoMover (&gt;6M Nac)</t>
         </is>
       </c>
-      <c r="M53" s="52" t="n">
+      <c r="L53" s="52" t="n">
         <v>1.982570305</v>
       </c>
-      <c r="N53" s="53" t="n">
+      <c r="M53" s="53" t="n">
         <v>132.83</v>
       </c>
-      <c r="O53" s="58" t="n">
+      <c r="N53" s="58" t="n">
         <v>152.66</v>
       </c>
-      <c r="P53" s="20" t="inlineStr">
+      <c r="O53" s="20" t="inlineStr">
         <is>
           <t>Plan Choque Comercial Nac / Oferta</t>
         </is>
@@ -28140,29 +27999,26 @@
         <v>0</v>
       </c>
       <c r="I54" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" s="34" t="n">
         <v>140</v>
       </c>
-      <c r="K54" s="33" t="n">
+      <c r="J54" s="33" t="n">
         <v>7</v>
       </c>
-      <c r="L54" s="26" t="inlineStr">
+      <c r="K54" s="26" t="inlineStr">
         <is>
           <t>🔴 NoMover (&gt;6M Nac)</t>
         </is>
       </c>
-      <c r="M54" s="55" t="n">
+      <c r="L54" s="55" t="n">
         <v>0.8864784</v>
       </c>
-      <c r="N54" s="56" t="n">
+      <c r="M54" s="56" t="n">
         <v>124.11</v>
       </c>
-      <c r="O54" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="P54" s="29" t="inlineStr">
+      <c r="N54" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" s="29" t="inlineStr">
         <is>
           <t>Sin Demanda Nacional (Inmovilizado Crítico)</t>
         </is>
@@ -28200,29 +28056,26 @@
         <v>0</v>
       </c>
       <c r="I55" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J55" s="25" t="n">
         <v>80</v>
       </c>
-      <c r="K55" s="24" t="n">
+      <c r="J55" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="L55" s="26" t="inlineStr">
+      <c r="K55" s="26" t="inlineStr">
         <is>
           <t>🔴 NoMover (&gt;6M Nac)</t>
         </is>
       </c>
-      <c r="M55" s="52" t="n">
+      <c r="L55" s="52" t="n">
         <v>1.394218385</v>
       </c>
-      <c r="N55" s="53" t="n">
+      <c r="M55" s="53" t="n">
         <v>111.54</v>
       </c>
-      <c r="O55" s="52" t="n">
-        <v>0</v>
-      </c>
-      <c r="P55" s="20" t="inlineStr">
+      <c r="N55" s="52" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" s="20" t="inlineStr">
         <is>
           <t>Sin Demanda Nacional (Inmovilizado Crítico)</t>
         </is>
@@ -28262,27 +28115,24 @@
       <c r="I56" s="34" t="n">
         <v>100</v>
       </c>
-      <c r="J56" s="34" t="n">
-        <v>100</v>
-      </c>
-      <c r="K56" s="33" t="n">
+      <c r="J56" s="33" t="n">
         <v>5</v>
       </c>
-      <c r="L56" s="26" t="inlineStr">
+      <c r="K56" s="26" t="inlineStr">
         <is>
           <t>🔴 NoMover (&gt;6M Nac)</t>
         </is>
       </c>
-      <c r="M56" s="55" t="n">
+      <c r="L56" s="55" t="n">
         <v>1.016006974</v>
       </c>
-      <c r="N56" s="56" t="n">
+      <c r="M56" s="56" t="n">
         <v>101.6</v>
       </c>
-      <c r="O56" s="57" t="n">
+      <c r="N56" s="57" t="n">
         <v>101.6</v>
       </c>
-      <c r="P56" s="29" t="inlineStr">
+      <c r="O56" s="29" t="inlineStr">
         <is>
           <t>Plan Choque Comercial Nac / Oferta</t>
         </is>
@@ -28320,29 +28170,26 @@
         <v>0</v>
       </c>
       <c r="I57" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J57" s="25" t="n">
         <v>100</v>
       </c>
-      <c r="K57" s="24" t="n">
+      <c r="J57" s="24" t="n">
         <v>5</v>
       </c>
-      <c r="L57" s="26" t="inlineStr">
+      <c r="K57" s="26" t="inlineStr">
         <is>
           <t>🔴 NoMover (&gt;6M Nac)</t>
         </is>
       </c>
-      <c r="M57" s="52" t="n">
+      <c r="L57" s="52" t="n">
         <v>1.014598543</v>
       </c>
-      <c r="N57" s="53" t="n">
+      <c r="M57" s="53" t="n">
         <v>101.46</v>
       </c>
-      <c r="O57" s="52" t="n">
-        <v>0</v>
-      </c>
-      <c r="P57" s="20" t="inlineStr">
+      <c r="N57" s="52" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" s="20" t="inlineStr">
         <is>
           <t>Sin Demanda Nacional (Inmovilizado Crítico)</t>
         </is>
@@ -28382,27 +28229,24 @@
       <c r="I58" s="34" t="n">
         <v>100</v>
       </c>
-      <c r="J58" s="34" t="n">
-        <v>100</v>
-      </c>
-      <c r="K58" s="33" t="n">
+      <c r="J58" s="33" t="n">
         <v>5</v>
       </c>
-      <c r="L58" s="26" t="inlineStr">
+      <c r="K58" s="26" t="inlineStr">
         <is>
           <t>🔴 NoMover (&gt;6M Nac)</t>
         </is>
       </c>
-      <c r="M58" s="55" t="n">
+      <c r="L58" s="55" t="n">
         <v>0.935092885</v>
       </c>
-      <c r="N58" s="56" t="n">
+      <c r="M58" s="56" t="n">
         <v>93.51000000000001</v>
       </c>
-      <c r="O58" s="57" t="n">
+      <c r="N58" s="57" t="n">
         <v>93.51000000000001</v>
       </c>
-      <c r="P58" s="29" t="inlineStr">
+      <c r="O58" s="29" t="inlineStr">
         <is>
           <t>Plan Choque Comercial Nac / Oferta</t>
         </is>
@@ -28440,29 +28284,26 @@
         <v>0</v>
       </c>
       <c r="I59" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J59" s="25" t="n">
         <v>220</v>
       </c>
-      <c r="K59" s="24" t="n">
+      <c r="J59" s="24" t="n">
         <v>44</v>
       </c>
-      <c r="L59" s="26" t="inlineStr">
+      <c r="K59" s="26" t="inlineStr">
         <is>
           <t>🔴 NoMover (&gt;6M Nac)</t>
         </is>
       </c>
-      <c r="M59" s="52" t="n">
+      <c r="L59" s="52" t="n">
         <v>0.396319826</v>
       </c>
-      <c r="N59" s="53" t="n">
+      <c r="M59" s="53" t="n">
         <v>87.19</v>
       </c>
-      <c r="O59" s="52" t="n">
-        <v>0</v>
-      </c>
-      <c r="P59" s="20" t="inlineStr">
+      <c r="N59" s="52" t="n">
+        <v>0</v>
+      </c>
+      <c r="O59" s="20" t="inlineStr">
         <is>
           <t>Sin Demanda Nacional (Inmovilizado Crítico)</t>
         </is>
@@ -28500,29 +28341,26 @@
         <v>45</v>
       </c>
       <c r="I60" s="34" t="n">
-        <v>45</v>
-      </c>
-      <c r="J60" s="34" t="n">
         <v>95</v>
       </c>
-      <c r="K60" s="33" t="n">
+      <c r="J60" s="33" t="n">
         <v>19</v>
       </c>
-      <c r="L60" s="26" t="inlineStr">
+      <c r="K60" s="26" t="inlineStr">
         <is>
           <t>🔴 NoMover (&gt;6M Nac)</t>
         </is>
       </c>
-      <c r="M60" s="55" t="n">
+      <c r="L60" s="55" t="n">
         <v>0.875371215</v>
       </c>
-      <c r="N60" s="56" t="n">
+      <c r="M60" s="56" t="n">
         <v>83.16</v>
       </c>
-      <c r="O60" s="57" t="n">
+      <c r="N60" s="57" t="n">
         <v>39.39</v>
       </c>
-      <c r="P60" s="29" t="inlineStr">
+      <c r="O60" s="29" t="inlineStr">
         <is>
           <t>Plan Choque Comercial Nac / Oferta</t>
         </is>
@@ -28560,29 +28398,26 @@
         <v>0</v>
       </c>
       <c r="I61" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J61" s="25" t="n">
         <v>48</v>
       </c>
-      <c r="K61" s="24" t="n">
+      <c r="J61" s="24" t="n">
         <v>48</v>
       </c>
-      <c r="L61" s="26" t="inlineStr">
+      <c r="K61" s="26" t="inlineStr">
         <is>
           <t>🔴 NoMover (&gt;6M Nac)</t>
         </is>
       </c>
-      <c r="M61" s="52" t="n">
+      <c r="L61" s="52" t="n">
         <v>1.697671971</v>
       </c>
-      <c r="N61" s="53" t="n">
+      <c r="M61" s="53" t="n">
         <v>81.48999999999999</v>
       </c>
-      <c r="O61" s="52" t="n">
-        <v>0</v>
-      </c>
-      <c r="P61" s="20" t="inlineStr">
+      <c r="N61" s="52" t="n">
+        <v>0</v>
+      </c>
+      <c r="O61" s="20" t="inlineStr">
         <is>
           <t>Sin Demanda Nacional (Inmovilizado Crítico)</t>
         </is>
@@ -28620,29 +28455,26 @@
         <v>0</v>
       </c>
       <c r="I62" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="J62" s="34" t="n">
         <v>135</v>
       </c>
-      <c r="K62" s="33" t="n">
+      <c r="J62" s="33" t="n">
         <v>27</v>
       </c>
-      <c r="L62" s="26" t="inlineStr">
+      <c r="K62" s="26" t="inlineStr">
         <is>
           <t>🔴 NoMover (&gt;6M Nac)</t>
         </is>
       </c>
-      <c r="M62" s="55" t="n">
+      <c r="L62" s="55" t="n">
         <v>0.460286754</v>
       </c>
-      <c r="N62" s="56" t="n">
+      <c r="M62" s="56" t="n">
         <v>62.14</v>
       </c>
-      <c r="O62" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="P62" s="29" t="inlineStr">
+      <c r="N62" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="O62" s="29" t="inlineStr">
         <is>
           <t>Sin Demanda Nacional (Inmovilizado Crítico)</t>
         </is>
@@ -28680,29 +28512,26 @@
         <v>0</v>
       </c>
       <c r="I63" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J63" s="25" t="n">
         <v>23</v>
       </c>
-      <c r="K63" s="24" t="n">
+      <c r="J63" s="24" t="n">
         <v>23</v>
       </c>
-      <c r="L63" s="26" t="inlineStr">
+      <c r="K63" s="26" t="inlineStr">
         <is>
           <t>🔴 NoMover (&gt;6M Nac)</t>
         </is>
       </c>
-      <c r="M63" s="52" t="n">
+      <c r="L63" s="52" t="n">
         <v>2.595357906</v>
       </c>
-      <c r="N63" s="53" t="n">
+      <c r="M63" s="53" t="n">
         <v>59.69</v>
       </c>
-      <c r="O63" s="52" t="n">
-        <v>0</v>
-      </c>
-      <c r="P63" s="20" t="inlineStr">
+      <c r="N63" s="52" t="n">
+        <v>0</v>
+      </c>
+      <c r="O63" s="20" t="inlineStr">
         <is>
           <t>Sin Demanda Nacional (Inmovilizado Crítico)</t>
         </is>
@@ -28740,29 +28569,26 @@
         <v>0</v>
       </c>
       <c r="I64" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="J64" s="34" t="n">
         <v>24</v>
       </c>
-      <c r="K64" s="33" t="n">
+      <c r="J64" s="33" t="n">
         <v>24</v>
       </c>
-      <c r="L64" s="26" t="inlineStr">
+      <c r="K64" s="26" t="inlineStr">
         <is>
           <t>🔴 NoMover (&gt;6M Nac)</t>
         </is>
       </c>
-      <c r="M64" s="55" t="n">
+      <c r="L64" s="55" t="n">
         <v>2.075429556</v>
       </c>
-      <c r="N64" s="56" t="n">
+      <c r="M64" s="56" t="n">
         <v>49.81</v>
       </c>
-      <c r="O64" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="P64" s="29" t="inlineStr">
+      <c r="N64" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="O64" s="29" t="inlineStr">
         <is>
           <t>Sin Demanda Nacional (Inmovilizado Crítico)</t>
         </is>
@@ -28800,29 +28626,26 @@
         <v>0</v>
       </c>
       <c r="I65" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J65" s="25" t="n">
         <v>15</v>
       </c>
-      <c r="K65" s="24" t="n">
+      <c r="J65" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="L65" s="26" t="inlineStr">
+      <c r="K65" s="26" t="inlineStr">
         <is>
           <t>🔴 NoMover (&gt;6M Nac)</t>
         </is>
       </c>
-      <c r="M65" s="52" t="n">
+      <c r="L65" s="52" t="n">
         <v>2.221691276</v>
       </c>
-      <c r="N65" s="53" t="n">
+      <c r="M65" s="53" t="n">
         <v>33.33</v>
       </c>
-      <c r="O65" s="52" t="n">
-        <v>0</v>
-      </c>
-      <c r="P65" s="20" t="inlineStr">
+      <c r="N65" s="52" t="n">
+        <v>0</v>
+      </c>
+      <c r="O65" s="20" t="inlineStr">
         <is>
           <t>Sin Demanda Nacional (Inmovilizado Crítico)</t>
         </is>
@@ -28860,29 +28683,26 @@
         <v>0</v>
       </c>
       <c r="I66" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="J66" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="K66" s="33" t="n">
+      <c r="J66" s="33" t="n">
         <v>6</v>
       </c>
-      <c r="L66" s="26" t="inlineStr">
+      <c r="K66" s="26" t="inlineStr">
         <is>
           <t>🔴 NoMover (&gt;6M Nac)</t>
         </is>
       </c>
-      <c r="M66" s="55" t="n">
+      <c r="L66" s="55" t="n">
         <v>4.632662343</v>
       </c>
-      <c r="N66" s="56" t="n">
+      <c r="M66" s="56" t="n">
         <v>27.8</v>
       </c>
-      <c r="O66" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="P66" s="29" t="inlineStr">
+      <c r="N66" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="O66" s="29" t="inlineStr">
         <is>
           <t>Sin Demanda Nacional (Inmovilizado Crítico)</t>
         </is>
@@ -28920,29 +28740,26 @@
         <v>0</v>
       </c>
       <c r="I67" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J67" s="25" t="n">
         <v>6</v>
       </c>
-      <c r="K67" s="24" t="n">
+      <c r="J67" s="24" t="n">
         <v>6</v>
       </c>
-      <c r="L67" s="26" t="inlineStr">
+      <c r="K67" s="26" t="inlineStr">
         <is>
           <t>🔴 NoMover (&gt;6M Nac)</t>
         </is>
       </c>
-      <c r="M67" s="52" t="n">
+      <c r="L67" s="52" t="n">
         <v>3.034952431</v>
       </c>
-      <c r="N67" s="53" t="n">
+      <c r="M67" s="53" t="n">
         <v>18.21</v>
       </c>
-      <c r="O67" s="52" t="n">
-        <v>0</v>
-      </c>
-      <c r="P67" s="20" t="inlineStr">
+      <c r="N67" s="52" t="n">
+        <v>0</v>
+      </c>
+      <c r="O67" s="20" t="inlineStr">
         <is>
           <t>Sin Demanda Nacional (Inmovilizado Crítico)</t>
         </is>
@@ -28980,29 +28797,26 @@
         <v>0</v>
       </c>
       <c r="I68" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="J68" s="34" t="n">
         <v>12</v>
       </c>
-      <c r="K68" s="33" t="n">
+      <c r="J68" s="33" t="n">
         <v>12</v>
       </c>
-      <c r="L68" s="26" t="inlineStr">
+      <c r="K68" s="26" t="inlineStr">
         <is>
           <t>🔴 NoMover (&gt;6M Nac)</t>
         </is>
       </c>
-      <c r="M68" s="55" t="n">
+      <c r="L68" s="55" t="n">
         <v>1.398800383</v>
       </c>
-      <c r="N68" s="56" t="n">
+      <c r="M68" s="56" t="n">
         <v>16.79</v>
       </c>
-      <c r="O68" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="P68" s="29" t="inlineStr">
+      <c r="N68" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="O68" s="29" t="inlineStr">
         <is>
           <t>Sin Demanda Nacional (Inmovilizado Crítico)</t>
         </is>
@@ -29040,29 +28854,26 @@
         <v>0</v>
       </c>
       <c r="I69" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J69" s="25" t="n">
         <v>6</v>
       </c>
-      <c r="K69" s="24" t="n">
+      <c r="J69" s="24" t="n">
         <v>6</v>
       </c>
-      <c r="L69" s="26" t="inlineStr">
+      <c r="K69" s="26" t="inlineStr">
         <is>
           <t>🔴 NoMover (&gt;6M Nac)</t>
         </is>
       </c>
-      <c r="M69" s="52" t="n">
+      <c r="L69" s="52" t="n">
         <v>1.648864804</v>
       </c>
-      <c r="N69" s="53" t="n">
+      <c r="M69" s="53" t="n">
         <v>9.890000000000001</v>
       </c>
-      <c r="O69" s="52" t="n">
-        <v>0</v>
-      </c>
-      <c r="P69" s="20" t="inlineStr">
+      <c r="N69" s="52" t="n">
+        <v>0</v>
+      </c>
+      <c r="O69" s="20" t="inlineStr">
         <is>
           <t>Sin Demanda Nacional (Inmovilizado Crítico)</t>
         </is>
@@ -29100,29 +28911,26 @@
         <v>0</v>
       </c>
       <c r="I70" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="J70" s="34" t="n">
         <v>10</v>
       </c>
-      <c r="K70" s="33" t="n">
+      <c r="J70" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="L70" s="26" t="inlineStr">
+      <c r="K70" s="26" t="inlineStr">
         <is>
           <t>🔴 NoMover (&gt;6M Nac)</t>
         </is>
       </c>
-      <c r="M70" s="55" t="n">
+      <c r="L70" s="55" t="n">
         <v>0.473099992</v>
       </c>
-      <c r="N70" s="56" t="n">
+      <c r="M70" s="56" t="n">
         <v>4.73</v>
       </c>
-      <c r="O70" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="P70" s="29" t="inlineStr">
+      <c r="N70" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="O70" s="29" t="inlineStr">
         <is>
           <t>Sin Demanda Nacional (Inmovilizado Crítico)</t>
         </is>
@@ -29160,29 +28968,26 @@
         <v>530</v>
       </c>
       <c r="I71" s="25" t="n">
-        <v>530</v>
-      </c>
-      <c r="J71" s="25" t="n">
         <v>300</v>
       </c>
-      <c r="K71" s="24" t="n">
+      <c r="J71" s="24" t="n">
         <v>60</v>
       </c>
-      <c r="L71" s="26" t="inlineStr">
+      <c r="K71" s="26" t="inlineStr">
         <is>
           <t>🔴 NoMover (&gt;6M Nac)</t>
         </is>
       </c>
+      <c r="L71" s="52" t="n">
+        <v>0</v>
+      </c>
       <c r="M71" s="52" t="n">
         <v>0</v>
       </c>
       <c r="N71" s="52" t="n">
         <v>0</v>
       </c>
-      <c r="O71" s="52" t="n">
-        <v>0</v>
-      </c>
-      <c r="P71" s="20" t="inlineStr">
+      <c r="O71" s="20" t="inlineStr">
         <is>
           <t>Plan Choque Comercial Nac / Oferta</t>
         </is>
@@ -29217,32 +29022,29 @@
         <v>51020</v>
       </c>
       <c r="H72" s="34" t="n">
-        <v>81120</v>
+        <v>6180</v>
       </c>
       <c r="I72" s="34" t="n">
-        <v>6180</v>
-      </c>
-      <c r="J72" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K72" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L72" s="35" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J72" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K72" s="35" t="inlineStr">
         <is>
           <t>🟡 SlowMover (3-6M Nac)</t>
         </is>
       </c>
+      <c r="L72" s="55" t="n">
+        <v>0.299066378</v>
+      </c>
       <c r="M72" s="55" t="n">
-        <v>0.299066378</v>
-      </c>
-      <c r="N72" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="O72" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N72" s="57" t="n">
         <v>1848.23</v>
       </c>
-      <c r="P72" s="29" t="inlineStr">
+      <c r="O72" s="29" t="inlineStr">
         <is>
           <t>Consumo previsto en Q1-27 Nacional</t>
         </is>
@@ -29277,32 +29079,29 @@
         <v>5380</v>
       </c>
       <c r="H73" s="25" t="n">
-        <v>5380</v>
+        <v>2700</v>
       </c>
       <c r="I73" s="25" t="n">
-        <v>2700</v>
-      </c>
-      <c r="J73" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K73" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L73" s="35" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J73" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K73" s="35" t="inlineStr">
         <is>
           <t>🟡 SlowMover (3-6M Nac)</t>
         </is>
       </c>
+      <c r="L73" s="52" t="n">
+        <v>0.998649413</v>
+      </c>
       <c r="M73" s="52" t="n">
-        <v>0.998649413</v>
-      </c>
-      <c r="N73" s="52" t="n">
-        <v>0</v>
-      </c>
-      <c r="O73" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="N73" s="58" t="n">
         <v>2696.35</v>
       </c>
-      <c r="P73" s="20" t="inlineStr">
+      <c r="O73" s="20" t="inlineStr">
         <is>
           <t>Consumo previsto en Q1-27 Nacional</t>
         </is>
@@ -29337,32 +29136,29 @@
         <v>11600</v>
       </c>
       <c r="H74" s="34" t="n">
-        <v>19600</v>
+        <v>2100</v>
       </c>
       <c r="I74" s="34" t="n">
-        <v>2100</v>
-      </c>
-      <c r="J74" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K74" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L74" s="35" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J74" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K74" s="35" t="inlineStr">
         <is>
           <t>🟡 SlowMover (3-6M Nac)</t>
         </is>
       </c>
+      <c r="L74" s="55" t="n">
+        <v>1.097855221</v>
+      </c>
       <c r="M74" s="55" t="n">
-        <v>1.097855221</v>
-      </c>
-      <c r="N74" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="O74" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N74" s="57" t="n">
         <v>2305.5</v>
       </c>
-      <c r="P74" s="29" t="inlineStr">
+      <c r="O74" s="29" t="inlineStr">
         <is>
           <t>Consumo previsto en Q1-27 Nacional</t>
         </is>
@@ -29397,32 +29193,29 @@
         <v>16800</v>
       </c>
       <c r="H75" s="25" t="n">
-        <v>27850</v>
+        <v>1790</v>
       </c>
       <c r="I75" s="25" t="n">
-        <v>1790</v>
-      </c>
-      <c r="J75" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K75" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L75" s="35" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J75" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K75" s="35" t="inlineStr">
         <is>
           <t>🟡 SlowMover (3-6M Nac)</t>
         </is>
       </c>
+      <c r="L75" s="52" t="n">
+        <v>0.521188894</v>
+      </c>
       <c r="M75" s="52" t="n">
-        <v>0.521188894</v>
-      </c>
-      <c r="N75" s="52" t="n">
-        <v>0</v>
-      </c>
-      <c r="O75" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="N75" s="58" t="n">
         <v>932.9299999999999</v>
       </c>
-      <c r="P75" s="20" t="inlineStr">
+      <c r="O75" s="20" t="inlineStr">
         <is>
           <t>Consumo previsto en Q1-27 Nacional</t>
         </is>
@@ -29457,32 +29250,29 @@
         <v>2140</v>
       </c>
       <c r="H76" s="34" t="n">
-        <v>2140</v>
+        <v>1320</v>
       </c>
       <c r="I76" s="34" t="n">
-        <v>1320</v>
-      </c>
-      <c r="J76" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K76" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L76" s="35" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J76" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K76" s="35" t="inlineStr">
         <is>
           <t>🟡 SlowMover (3-6M Nac)</t>
         </is>
       </c>
+      <c r="L76" s="55" t="n">
+        <v>3.512262255</v>
+      </c>
       <c r="M76" s="55" t="n">
-        <v>3.512262255</v>
-      </c>
-      <c r="N76" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="O76" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N76" s="57" t="n">
         <v>4636.19</v>
       </c>
-      <c r="P76" s="29" t="inlineStr">
+      <c r="O76" s="29" t="inlineStr">
         <is>
           <t>Consumo previsto en Q1-27 Nacional</t>
         </is>
@@ -29517,32 +29307,29 @@
         <v>1360</v>
       </c>
       <c r="H77" s="25" t="n">
-        <v>1360</v>
+        <v>1280</v>
       </c>
       <c r="I77" s="25" t="n">
-        <v>1280</v>
-      </c>
-      <c r="J77" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K77" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L77" s="35" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J77" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K77" s="35" t="inlineStr">
         <is>
           <t>🟡 SlowMover (3-6M Nac)</t>
         </is>
       </c>
+      <c r="L77" s="52" t="n">
+        <v>0.7037288819999999</v>
+      </c>
       <c r="M77" s="52" t="n">
-        <v>0.7037288819999999</v>
-      </c>
-      <c r="N77" s="52" t="n">
-        <v>0</v>
-      </c>
-      <c r="O77" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="N77" s="58" t="n">
         <v>900.77</v>
       </c>
-      <c r="P77" s="20" t="inlineStr">
+      <c r="O77" s="20" t="inlineStr">
         <is>
           <t>Consumo previsto en Q1-27 Nacional</t>
         </is>
@@ -29577,32 +29364,29 @@
         <v>1420</v>
       </c>
       <c r="H78" s="34" t="n">
-        <v>2120</v>
+        <v>980</v>
       </c>
       <c r="I78" s="34" t="n">
-        <v>980</v>
-      </c>
-      <c r="J78" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K78" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L78" s="35" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J78" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K78" s="35" t="inlineStr">
         <is>
           <t>🟡 SlowMover (3-6M Nac)</t>
         </is>
       </c>
+      <c r="L78" s="55" t="n">
+        <v>1.162432485</v>
+      </c>
       <c r="M78" s="55" t="n">
-        <v>1.162432485</v>
-      </c>
-      <c r="N78" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="O78" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N78" s="57" t="n">
         <v>1139.18</v>
       </c>
-      <c r="P78" s="29" t="inlineStr">
+      <c r="O78" s="29" t="inlineStr">
         <is>
           <t>Consumo previsto en Q1-27 Nacional</t>
         </is>
@@ -29637,32 +29421,29 @@
         <v>2120</v>
       </c>
       <c r="H79" s="25" t="n">
-        <v>2120</v>
+        <v>900</v>
       </c>
       <c r="I79" s="25" t="n">
-        <v>900</v>
-      </c>
-      <c r="J79" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K79" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L79" s="35" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J79" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K79" s="35" t="inlineStr">
         <is>
           <t>🟡 SlowMover (3-6M Nac)</t>
         </is>
       </c>
+      <c r="L79" s="52" t="n">
+        <v>1.020366434</v>
+      </c>
       <c r="M79" s="52" t="n">
-        <v>1.020366434</v>
-      </c>
-      <c r="N79" s="52" t="n">
-        <v>0</v>
-      </c>
-      <c r="O79" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="N79" s="58" t="n">
         <v>918.33</v>
       </c>
-      <c r="P79" s="20" t="inlineStr">
+      <c r="O79" s="20" t="inlineStr">
         <is>
           <t>Consumo previsto en Q1-27 Nacional</t>
         </is>
@@ -29697,32 +29478,29 @@
         <v>2540</v>
       </c>
       <c r="H80" s="34" t="n">
-        <v>2540</v>
+        <v>820</v>
       </c>
       <c r="I80" s="34" t="n">
-        <v>820</v>
-      </c>
-      <c r="J80" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K80" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L80" s="35" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J80" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K80" s="35" t="inlineStr">
         <is>
           <t>🟡 SlowMover (3-6M Nac)</t>
         </is>
       </c>
+      <c r="L80" s="55" t="n">
+        <v>0.872689676</v>
+      </c>
       <c r="M80" s="55" t="n">
-        <v>0.872689676</v>
-      </c>
-      <c r="N80" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="O80" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N80" s="57" t="n">
         <v>715.61</v>
       </c>
-      <c r="P80" s="29" t="inlineStr">
+      <c r="O80" s="29" t="inlineStr">
         <is>
           <t>Consumo previsto en Q1-27 Nacional</t>
         </is>
@@ -29757,32 +29535,29 @@
         <v>1160</v>
       </c>
       <c r="H81" s="25" t="n">
-        <v>1800</v>
+        <v>780</v>
       </c>
       <c r="I81" s="25" t="n">
-        <v>780</v>
-      </c>
-      <c r="J81" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K81" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L81" s="35" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J81" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K81" s="35" t="inlineStr">
         <is>
           <t>🟡 SlowMover (3-6M Nac)</t>
         </is>
       </c>
+      <c r="L81" s="52" t="n">
+        <v>1.343582063</v>
+      </c>
       <c r="M81" s="52" t="n">
-        <v>1.343582063</v>
-      </c>
-      <c r="N81" s="52" t="n">
-        <v>0</v>
-      </c>
-      <c r="O81" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="N81" s="58" t="n">
         <v>1047.99</v>
       </c>
-      <c r="P81" s="20" t="inlineStr">
+      <c r="O81" s="20" t="inlineStr">
         <is>
           <t>Consumo previsto en Q1-27 Nacional</t>
         </is>
@@ -29817,32 +29592,29 @@
         <v>980</v>
       </c>
       <c r="H82" s="34" t="n">
-        <v>980</v>
+        <v>740</v>
       </c>
       <c r="I82" s="34" t="n">
-        <v>740</v>
-      </c>
-      <c r="J82" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K82" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L82" s="35" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J82" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K82" s="35" t="inlineStr">
         <is>
           <t>🟡 SlowMover (3-6M Nac)</t>
         </is>
       </c>
+      <c r="L82" s="55" t="n">
+        <v>0</v>
+      </c>
       <c r="M82" s="55" t="n">
         <v>0</v>
       </c>
       <c r="N82" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="O82" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="P82" s="29" t="inlineStr">
+      <c r="O82" s="29" t="inlineStr">
         <is>
           <t>Consumo previsto en Q1-27 Nacional</t>
         </is>
@@ -29877,32 +29649,29 @@
         <v>760</v>
       </c>
       <c r="H83" s="25" t="n">
-        <v>860</v>
+        <v>690</v>
       </c>
       <c r="I83" s="25" t="n">
-        <v>690</v>
-      </c>
-      <c r="J83" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K83" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L83" s="35" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J83" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K83" s="35" t="inlineStr">
         <is>
           <t>🟡 SlowMover (3-6M Nac)</t>
         </is>
       </c>
+      <c r="L83" s="52" t="n">
+        <v>1.156155803</v>
+      </c>
       <c r="M83" s="52" t="n">
-        <v>1.156155803</v>
-      </c>
-      <c r="N83" s="52" t="n">
-        <v>0</v>
-      </c>
-      <c r="O83" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="N83" s="58" t="n">
         <v>797.75</v>
       </c>
-      <c r="P83" s="20" t="inlineStr">
+      <c r="O83" s="20" t="inlineStr">
         <is>
           <t>Consumo previsto en Q1-27 Nacional</t>
         </is>
@@ -29937,32 +29706,29 @@
         <v>9060</v>
       </c>
       <c r="H84" s="34" t="n">
-        <v>12900</v>
+        <v>680</v>
       </c>
       <c r="I84" s="34" t="n">
-        <v>680</v>
-      </c>
-      <c r="J84" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K84" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L84" s="35" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J84" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K84" s="35" t="inlineStr">
         <is>
           <t>🟡 SlowMover (3-6M Nac)</t>
         </is>
       </c>
+      <c r="L84" s="55" t="n">
+        <v>0.912261163</v>
+      </c>
       <c r="M84" s="55" t="n">
-        <v>0.912261163</v>
-      </c>
-      <c r="N84" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="O84" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N84" s="57" t="n">
         <v>620.34</v>
       </c>
-      <c r="P84" s="29" t="inlineStr">
+      <c r="O84" s="29" t="inlineStr">
         <is>
           <t>Consumo previsto en Q1-27 Nacional</t>
         </is>
@@ -29997,32 +29763,29 @@
         <v>2130</v>
       </c>
       <c r="H85" s="25" t="n">
-        <v>3330</v>
+        <v>640</v>
       </c>
       <c r="I85" s="25" t="n">
-        <v>640</v>
-      </c>
-      <c r="J85" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K85" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L85" s="35" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J85" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K85" s="35" t="inlineStr">
         <is>
           <t>🟡 SlowMover (3-6M Nac)</t>
         </is>
       </c>
+      <c r="L85" s="52" t="n">
+        <v>1.735614356</v>
+      </c>
       <c r="M85" s="52" t="n">
-        <v>1.735614356</v>
-      </c>
-      <c r="N85" s="52" t="n">
-        <v>0</v>
-      </c>
-      <c r="O85" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="N85" s="58" t="n">
         <v>1110.79</v>
       </c>
-      <c r="P85" s="20" t="inlineStr">
+      <c r="O85" s="20" t="inlineStr">
         <is>
           <t>Consumo previsto en Q1-27 Nacional</t>
         </is>
@@ -30057,32 +29820,29 @@
         <v>5555</v>
       </c>
       <c r="H86" s="34" t="n">
-        <v>5955</v>
+        <v>640</v>
       </c>
       <c r="I86" s="34" t="n">
-        <v>640</v>
-      </c>
-      <c r="J86" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K86" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L86" s="35" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J86" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K86" s="35" t="inlineStr">
         <is>
           <t>🟡 SlowMover (3-6M Nac)</t>
         </is>
       </c>
+      <c r="L86" s="55" t="n">
+        <v>1.901092129</v>
+      </c>
       <c r="M86" s="55" t="n">
-        <v>1.901092129</v>
-      </c>
-      <c r="N86" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="O86" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N86" s="57" t="n">
         <v>1216.7</v>
       </c>
-      <c r="P86" s="29" t="inlineStr">
+      <c r="O86" s="29" t="inlineStr">
         <is>
           <t>Consumo previsto en Q1-27 Nacional</t>
         </is>
@@ -30117,32 +29877,29 @@
         <v>1980</v>
       </c>
       <c r="H87" s="25" t="n">
-        <v>1980</v>
+        <v>580</v>
       </c>
       <c r="I87" s="25" t="n">
-        <v>580</v>
-      </c>
-      <c r="J87" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K87" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L87" s="35" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J87" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K87" s="35" t="inlineStr">
         <is>
           <t>🟡 SlowMover (3-6M Nac)</t>
         </is>
       </c>
+      <c r="L87" s="52" t="n">
+        <v>1.746622963</v>
+      </c>
       <c r="M87" s="52" t="n">
-        <v>1.746622963</v>
-      </c>
-      <c r="N87" s="52" t="n">
-        <v>0</v>
-      </c>
-      <c r="O87" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="N87" s="58" t="n">
         <v>1013.04</v>
       </c>
-      <c r="P87" s="20" t="inlineStr">
+      <c r="O87" s="20" t="inlineStr">
         <is>
           <t>Consumo previsto en Q1-27 Nacional</t>
         </is>
@@ -30177,32 +29934,29 @@
         <v>1440</v>
       </c>
       <c r="H88" s="34" t="n">
-        <v>4000</v>
+        <v>520</v>
       </c>
       <c r="I88" s="34" t="n">
-        <v>520</v>
-      </c>
-      <c r="J88" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K88" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L88" s="35" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J88" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K88" s="35" t="inlineStr">
         <is>
           <t>🟡 SlowMover (3-6M Nac)</t>
         </is>
       </c>
+      <c r="L88" s="55" t="n">
+        <v>0.829425377</v>
+      </c>
       <c r="M88" s="55" t="n">
-        <v>0.829425377</v>
-      </c>
-      <c r="N88" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="O88" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N88" s="57" t="n">
         <v>431.3</v>
       </c>
-      <c r="P88" s="29" t="inlineStr">
+      <c r="O88" s="29" t="inlineStr">
         <is>
           <t>Consumo previsto en Q1-27 Nacional</t>
         </is>
@@ -30237,32 +29991,29 @@
         <v>2360</v>
       </c>
       <c r="H89" s="25" t="n">
-        <v>3640</v>
+        <v>440</v>
       </c>
       <c r="I89" s="25" t="n">
-        <v>440</v>
-      </c>
-      <c r="J89" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K89" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L89" s="35" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J89" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K89" s="35" t="inlineStr">
         <is>
           <t>🟡 SlowMover (3-6M Nac)</t>
         </is>
       </c>
+      <c r="L89" s="52" t="n">
+        <v>4.779781021</v>
+      </c>
       <c r="M89" s="52" t="n">
-        <v>4.779781021</v>
-      </c>
-      <c r="N89" s="52" t="n">
-        <v>0</v>
-      </c>
-      <c r="O89" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="N89" s="58" t="n">
         <v>2103.1</v>
       </c>
-      <c r="P89" s="20" t="inlineStr">
+      <c r="O89" s="20" t="inlineStr">
         <is>
           <t>Consumo previsto en Q1-27 Nacional</t>
         </is>
@@ -30297,32 +30048,29 @@
         <v>480</v>
       </c>
       <c r="H90" s="34" t="n">
-        <v>680</v>
+        <v>285</v>
       </c>
       <c r="I90" s="34" t="n">
-        <v>285</v>
-      </c>
-      <c r="J90" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K90" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L90" s="35" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J90" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K90" s="35" t="inlineStr">
         <is>
           <t>🟡 SlowMover (3-6M Nac)</t>
         </is>
       </c>
+      <c r="L90" s="55" t="n">
+        <v>1.408290539</v>
+      </c>
       <c r="M90" s="55" t="n">
-        <v>1.408290539</v>
-      </c>
-      <c r="N90" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="O90" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N90" s="57" t="n">
         <v>401.36</v>
       </c>
-      <c r="P90" s="29" t="inlineStr">
+      <c r="O90" s="29" t="inlineStr">
         <is>
           <t>Consumo previsto en Q1-27 Nacional</t>
         </is>
@@ -30357,32 +30105,29 @@
         <v>600</v>
       </c>
       <c r="H91" s="25" t="n">
-        <v>600</v>
+        <v>260</v>
       </c>
       <c r="I91" s="25" t="n">
-        <v>260</v>
-      </c>
-      <c r="J91" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K91" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L91" s="35" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J91" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K91" s="35" t="inlineStr">
         <is>
           <t>🟡 SlowMover (3-6M Nac)</t>
         </is>
       </c>
+      <c r="L91" s="52" t="n">
+        <v>0</v>
+      </c>
       <c r="M91" s="52" t="n">
         <v>0</v>
       </c>
       <c r="N91" s="52" t="n">
         <v>0</v>
       </c>
-      <c r="O91" s="52" t="n">
-        <v>0</v>
-      </c>
-      <c r="P91" s="20" t="inlineStr">
+      <c r="O91" s="20" t="inlineStr">
         <is>
           <t>Consumo previsto en Q1-27 Nacional</t>
         </is>
@@ -30417,32 +30162,29 @@
         <v>1055</v>
       </c>
       <c r="H92" s="34" t="n">
-        <v>1805</v>
+        <v>260</v>
       </c>
       <c r="I92" s="34" t="n">
-        <v>260</v>
-      </c>
-      <c r="J92" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K92" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L92" s="35" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J92" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K92" s="35" t="inlineStr">
         <is>
           <t>🟡 SlowMover (3-6M Nac)</t>
         </is>
       </c>
+      <c r="L92" s="55" t="n">
+        <v>1.188039774</v>
+      </c>
       <c r="M92" s="55" t="n">
-        <v>1.188039774</v>
-      </c>
-      <c r="N92" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="O92" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N92" s="57" t="n">
         <v>308.89</v>
       </c>
-      <c r="P92" s="29" t="inlineStr">
+      <c r="O92" s="29" t="inlineStr">
         <is>
           <t>Consumo previsto en Q1-27 Nacional</t>
         </is>
@@ -30477,32 +30219,29 @@
         <v>358</v>
       </c>
       <c r="H93" s="25" t="n">
-        <v>910</v>
+        <v>257</v>
       </c>
       <c r="I93" s="25" t="n">
-        <v>257</v>
-      </c>
-      <c r="J93" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K93" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L93" s="35" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J93" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K93" s="35" t="inlineStr">
         <is>
           <t>🟡 SlowMover (3-6M Nac)</t>
         </is>
       </c>
+      <c r="L93" s="52" t="n">
+        <v>3.751106806</v>
+      </c>
       <c r="M93" s="52" t="n">
-        <v>3.751106806</v>
-      </c>
-      <c r="N93" s="52" t="n">
-        <v>0</v>
-      </c>
-      <c r="O93" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="N93" s="58" t="n">
         <v>964.03</v>
       </c>
-      <c r="P93" s="20" t="inlineStr">
+      <c r="O93" s="20" t="inlineStr">
         <is>
           <t>Consumo previsto en Q1-27 Nacional</t>
         </is>
@@ -30537,32 +30276,29 @@
         <v>645</v>
       </c>
       <c r="H94" s="34" t="n">
-        <v>645</v>
+        <v>235</v>
       </c>
       <c r="I94" s="34" t="n">
-        <v>235</v>
-      </c>
-      <c r="J94" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K94" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L94" s="35" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J94" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K94" s="35" t="inlineStr">
         <is>
           <t>🟡 SlowMover (3-6M Nac)</t>
         </is>
       </c>
+      <c r="L94" s="55" t="n">
+        <v>1.798375791</v>
+      </c>
       <c r="M94" s="55" t="n">
-        <v>1.798375791</v>
-      </c>
-      <c r="N94" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="O94" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N94" s="57" t="n">
         <v>422.62</v>
       </c>
-      <c r="P94" s="29" t="inlineStr">
+      <c r="O94" s="29" t="inlineStr">
         <is>
           <t>Consumo previsto en Q1-27 Nacional</t>
         </is>
@@ -30597,32 +30333,29 @@
         <v>2955</v>
       </c>
       <c r="H95" s="25" t="n">
-        <v>4830</v>
+        <v>210</v>
       </c>
       <c r="I95" s="25" t="n">
-        <v>210</v>
-      </c>
-      <c r="J95" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K95" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L95" s="35" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J95" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K95" s="35" t="inlineStr">
         <is>
           <t>🟡 SlowMover (3-6M Nac)</t>
         </is>
       </c>
+      <c r="L95" s="52" t="n">
+        <v>1.709439653</v>
+      </c>
       <c r="M95" s="52" t="n">
-        <v>1.709439653</v>
-      </c>
-      <c r="N95" s="52" t="n">
-        <v>0</v>
-      </c>
-      <c r="O95" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="N95" s="58" t="n">
         <v>358.98</v>
       </c>
-      <c r="P95" s="20" t="inlineStr">
+      <c r="O95" s="20" t="inlineStr">
         <is>
           <t>Consumo previsto en Q1-27 Nacional</t>
         </is>
@@ -30657,32 +30390,29 @@
         <v>560</v>
       </c>
       <c r="H96" s="34" t="n">
-        <v>560</v>
+        <v>140</v>
       </c>
       <c r="I96" s="34" t="n">
-        <v>140</v>
-      </c>
-      <c r="J96" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K96" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L96" s="35" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J96" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K96" s="35" t="inlineStr">
         <is>
           <t>🟡 SlowMover (3-6M Nac)</t>
         </is>
       </c>
+      <c r="L96" s="55" t="n">
+        <v>3.884360639</v>
+      </c>
       <c r="M96" s="55" t="n">
-        <v>3.884360639</v>
-      </c>
-      <c r="N96" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="O96" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N96" s="57" t="n">
         <v>543.8099999999999</v>
       </c>
-      <c r="P96" s="29" t="inlineStr">
+      <c r="O96" s="29" t="inlineStr">
         <is>
           <t>Consumo previsto en Q1-27 Nacional</t>
         </is>
@@ -30717,32 +30447,29 @@
         <v>110</v>
       </c>
       <c r="H97" s="25" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="I97" s="25" t="n">
-        <v>100</v>
-      </c>
-      <c r="J97" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K97" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L97" s="35" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J97" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K97" s="35" t="inlineStr">
         <is>
           <t>🟡 SlowMover (3-6M Nac)</t>
         </is>
       </c>
+      <c r="L97" s="52" t="n">
+        <v>1.063734813</v>
+      </c>
       <c r="M97" s="52" t="n">
-        <v>1.063734813</v>
-      </c>
-      <c r="N97" s="52" t="n">
-        <v>0</v>
-      </c>
-      <c r="O97" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="N97" s="58" t="n">
         <v>106.37</v>
       </c>
-      <c r="P97" s="20" t="inlineStr">
+      <c r="O97" s="20" t="inlineStr">
         <is>
           <t>Consumo previsto en Q1-27 Nacional</t>
         </is>
@@ -30777,32 +30504,29 @@
         <v>114</v>
       </c>
       <c r="H98" s="34" t="n">
-        <v>114</v>
+        <v>84</v>
       </c>
       <c r="I98" s="34" t="n">
-        <v>84</v>
-      </c>
-      <c r="J98" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K98" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L98" s="35" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J98" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K98" s="35" t="inlineStr">
         <is>
           <t>🟡 SlowMover (3-6M Nac)</t>
         </is>
       </c>
+      <c r="L98" s="55" t="n">
+        <v>4.116960542</v>
+      </c>
       <c r="M98" s="55" t="n">
-        <v>4.116960542</v>
-      </c>
-      <c r="N98" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="O98" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N98" s="57" t="n">
         <v>345.82</v>
       </c>
-      <c r="P98" s="29" t="inlineStr">
+      <c r="O98" s="29" t="inlineStr">
         <is>
           <t>Consumo previsto en Q1-27 Nacional</t>
         </is>
@@ -30837,32 +30561,29 @@
         <v>1450</v>
       </c>
       <c r="H99" s="25" t="n">
-        <v>1450</v>
+        <v>80</v>
       </c>
       <c r="I99" s="25" t="n">
-        <v>80</v>
-      </c>
-      <c r="J99" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K99" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L99" s="35" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J99" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K99" s="35" t="inlineStr">
         <is>
           <t>🟡 SlowMover (3-6M Nac)</t>
         </is>
       </c>
+      <c r="L99" s="52" t="n">
+        <v>4.180478427</v>
+      </c>
       <c r="M99" s="52" t="n">
-        <v>4.180478427</v>
-      </c>
-      <c r="N99" s="52" t="n">
-        <v>0</v>
-      </c>
-      <c r="O99" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="N99" s="58" t="n">
         <v>334.44</v>
       </c>
-      <c r="P99" s="20" t="inlineStr">
+      <c r="O99" s="20" t="inlineStr">
         <is>
           <t>Consumo previsto en Q1-27 Nacional</t>
         </is>
@@ -30897,32 +30618,29 @@
         <v>220</v>
       </c>
       <c r="H100" s="34" t="n">
-        <v>220</v>
+        <v>80</v>
       </c>
       <c r="I100" s="34" t="n">
-        <v>80</v>
-      </c>
-      <c r="J100" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K100" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L100" s="35" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J100" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K100" s="35" t="inlineStr">
         <is>
           <t>🟡 SlowMover (3-6M Nac)</t>
         </is>
       </c>
+      <c r="L100" s="55" t="n">
+        <v>1.59930044</v>
+      </c>
       <c r="M100" s="55" t="n">
-        <v>1.59930044</v>
-      </c>
-      <c r="N100" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="O100" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N100" s="57" t="n">
         <v>127.94</v>
       </c>
-      <c r="P100" s="29" t="inlineStr">
+      <c r="O100" s="29" t="inlineStr">
         <is>
           <t>Consumo previsto en Q1-27 Nacional</t>
         </is>
@@ -30957,32 +30675,29 @@
         <v>387</v>
       </c>
       <c r="H101" s="25" t="n">
-        <v>603</v>
+        <v>76</v>
       </c>
       <c r="I101" s="25" t="n">
-        <v>76</v>
-      </c>
-      <c r="J101" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K101" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L101" s="35" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J101" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K101" s="35" t="inlineStr">
         <is>
           <t>🟡 SlowMover (3-6M Nac)</t>
         </is>
       </c>
+      <c r="L101" s="52" t="n">
+        <v>2.463336865</v>
+      </c>
       <c r="M101" s="52" t="n">
-        <v>2.463336865</v>
-      </c>
-      <c r="N101" s="52" t="n">
-        <v>0</v>
-      </c>
-      <c r="O101" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="N101" s="58" t="n">
         <v>187.21</v>
       </c>
-      <c r="P101" s="20" t="inlineStr">
+      <c r="O101" s="20" t="inlineStr">
         <is>
           <t>Consumo previsto en Q1-27 Nacional</t>
         </is>
@@ -31017,32 +30732,29 @@
         <v>101</v>
       </c>
       <c r="H102" s="34" t="n">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="I102" s="34" t="n">
-        <v>72</v>
-      </c>
-      <c r="J102" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K102" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L102" s="35" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J102" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K102" s="35" t="inlineStr">
         <is>
           <t>🟡 SlowMover (3-6M Nac)</t>
         </is>
       </c>
+      <c r="L102" s="55" t="n">
+        <v>9.755021372</v>
+      </c>
       <c r="M102" s="55" t="n">
-        <v>9.755021372</v>
-      </c>
-      <c r="N102" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="O102" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N102" s="57" t="n">
         <v>702.36</v>
       </c>
-      <c r="P102" s="29" t="inlineStr">
+      <c r="O102" s="29" t="inlineStr">
         <is>
           <t>Consumo previsto en Q1-27 Nacional</t>
         </is>
@@ -31077,32 +30789,29 @@
         <v>435</v>
       </c>
       <c r="H103" s="25" t="n">
-        <v>955</v>
+        <v>70</v>
       </c>
       <c r="I103" s="25" t="n">
-        <v>70</v>
-      </c>
-      <c r="J103" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K103" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L103" s="35" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J103" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K103" s="35" t="inlineStr">
         <is>
           <t>🟡 SlowMover (3-6M Nac)</t>
         </is>
       </c>
+      <c r="L103" s="52" t="n">
+        <v>0.981135536</v>
+      </c>
       <c r="M103" s="52" t="n">
-        <v>0.981135536</v>
-      </c>
-      <c r="N103" s="52" t="n">
-        <v>0</v>
-      </c>
-      <c r="O103" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="N103" s="58" t="n">
         <v>68.68000000000001</v>
       </c>
-      <c r="P103" s="20" t="inlineStr">
+      <c r="O103" s="20" t="inlineStr">
         <is>
           <t>Consumo previsto en Q1-27 Nacional</t>
         </is>
@@ -31137,32 +30846,29 @@
         <v>204</v>
       </c>
       <c r="H104" s="34" t="n">
-        <v>204</v>
+        <v>60</v>
       </c>
       <c r="I104" s="34" t="n">
-        <v>60</v>
-      </c>
-      <c r="J104" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K104" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L104" s="35" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J104" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K104" s="35" t="inlineStr">
         <is>
           <t>🟡 SlowMover (3-6M Nac)</t>
         </is>
       </c>
+      <c r="L104" s="55" t="n">
+        <v>2.460987652</v>
+      </c>
       <c r="M104" s="55" t="n">
-        <v>2.460987652</v>
-      </c>
-      <c r="N104" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="O104" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N104" s="57" t="n">
         <v>147.66</v>
       </c>
-      <c r="P104" s="29" t="inlineStr">
+      <c r="O104" s="29" t="inlineStr">
         <is>
           <t>Consumo previsto en Q1-27 Nacional</t>
         </is>
@@ -31197,32 +30903,29 @@
         <v>7695</v>
       </c>
       <c r="H105" s="25" t="n">
-        <v>8645</v>
+        <v>50</v>
       </c>
       <c r="I105" s="25" t="n">
-        <v>50</v>
-      </c>
-      <c r="J105" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K105" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L105" s="35" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J105" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K105" s="35" t="inlineStr">
         <is>
           <t>🟡 SlowMover (3-6M Nac)</t>
         </is>
       </c>
+      <c r="L105" s="52" t="n">
+        <v>0</v>
+      </c>
       <c r="M105" s="52" t="n">
         <v>0</v>
       </c>
       <c r="N105" s="52" t="n">
         <v>0</v>
       </c>
-      <c r="O105" s="52" t="n">
-        <v>0</v>
-      </c>
-      <c r="P105" s="20" t="inlineStr">
+      <c r="O105" s="20" t="inlineStr">
         <is>
           <t>Consumo previsto en Q1-27 Nacional</t>
         </is>
@@ -31257,32 +30960,29 @@
         <v>26</v>
       </c>
       <c r="H106" s="34" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="I106" s="34" t="n">
-        <v>24</v>
-      </c>
-      <c r="J106" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K106" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L106" s="35" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J106" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K106" s="35" t="inlineStr">
         <is>
           <t>🟡 SlowMover (3-6M Nac)</t>
         </is>
       </c>
+      <c r="L106" s="55" t="n">
+        <v>2.202275768</v>
+      </c>
       <c r="M106" s="55" t="n">
-        <v>2.202275768</v>
-      </c>
-      <c r="N106" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="O106" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N106" s="57" t="n">
         <v>52.85</v>
       </c>
-      <c r="P106" s="29" t="inlineStr">
+      <c r="O106" s="29" t="inlineStr">
         <is>
           <t>Consumo previsto en Q1-27 Nacional</t>
         </is>
@@ -31317,32 +31017,29 @@
         <v>86</v>
       </c>
       <c r="H107" s="25" t="n">
-        <v>86</v>
+        <v>10</v>
       </c>
       <c r="I107" s="25" t="n">
-        <v>10</v>
-      </c>
-      <c r="J107" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K107" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L107" s="35" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J107" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K107" s="35" t="inlineStr">
         <is>
           <t>🟡 SlowMover (3-6M Nac)</t>
         </is>
       </c>
+      <c r="L107" s="52" t="n">
+        <v>4.038956501</v>
+      </c>
       <c r="M107" s="52" t="n">
-        <v>4.038956501</v>
-      </c>
-      <c r="N107" s="52" t="n">
-        <v>0</v>
-      </c>
-      <c r="O107" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="N107" s="58" t="n">
         <v>40.39</v>
       </c>
-      <c r="P107" s="20" t="inlineStr">
+      <c r="O107" s="20" t="inlineStr">
         <is>
           <t>Consumo previsto en Q1-27 Nacional</t>
         </is>
@@ -31377,32 +31074,29 @@
         <v>9380</v>
       </c>
       <c r="H108" s="34" t="n">
-        <v>22460</v>
+        <v>0</v>
       </c>
       <c r="I108" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="J108" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K108" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L108" s="36" t="inlineStr">
+      <c r="J108" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K108" s="36" t="inlineStr">
         <is>
           <t>🟢 Alta Rotación (0-3M Nac)</t>
         </is>
       </c>
+      <c r="L108" s="55" t="n">
+        <v>0.709680779</v>
+      </c>
       <c r="M108" s="55" t="n">
-        <v>0.709680779</v>
+        <v>0</v>
       </c>
       <c r="N108" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="O108" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="P108" s="29" t="inlineStr">
+      <c r="O108" s="29" t="inlineStr">
         <is>
           <t>Rotación Normal en Campaña Q4</t>
         </is>
@@ -31437,32 +31131,29 @@
         <v>3180</v>
       </c>
       <c r="H109" s="25" t="n">
-        <v>5420</v>
+        <v>0</v>
       </c>
       <c r="I109" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="J109" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K109" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L109" s="36" t="inlineStr">
+      <c r="J109" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K109" s="36" t="inlineStr">
         <is>
           <t>🟢 Alta Rotación (0-3M Nac)</t>
         </is>
       </c>
+      <c r="L109" s="52" t="n">
+        <v>1.110221424</v>
+      </c>
       <c r="M109" s="52" t="n">
-        <v>1.110221424</v>
+        <v>0</v>
       </c>
       <c r="N109" s="52" t="n">
         <v>0</v>
       </c>
-      <c r="O109" s="52" t="n">
-        <v>0</v>
-      </c>
-      <c r="P109" s="20" t="inlineStr">
+      <c r="O109" s="20" t="inlineStr">
         <is>
           <t>Rotación Normal en Campaña Q4</t>
         </is>
@@ -31497,32 +31188,29 @@
         <v>980</v>
       </c>
       <c r="H110" s="34" t="n">
-        <v>11220</v>
+        <v>0</v>
       </c>
       <c r="I110" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="J110" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K110" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L110" s="36" t="inlineStr">
+      <c r="J110" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K110" s="36" t="inlineStr">
         <is>
           <t>🟢 Alta Rotación (0-3M Nac)</t>
         </is>
       </c>
+      <c r="L110" s="55" t="n">
+        <v>0.732601566</v>
+      </c>
       <c r="M110" s="55" t="n">
-        <v>0.732601566</v>
+        <v>0</v>
       </c>
       <c r="N110" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="O110" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="P110" s="29" t="inlineStr">
+      <c r="O110" s="29" t="inlineStr">
         <is>
           <t>Rotación Normal en Campaña Q4</t>
         </is>
@@ -31557,32 +31245,29 @@
         <v>20520</v>
       </c>
       <c r="H111" s="25" t="n">
-        <v>36180</v>
+        <v>0</v>
       </c>
       <c r="I111" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="J111" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K111" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L111" s="36" t="inlineStr">
+      <c r="J111" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K111" s="36" t="inlineStr">
         <is>
           <t>🟢 Alta Rotación (0-3M Nac)</t>
         </is>
       </c>
+      <c r="L111" s="52" t="n">
+        <v>0.937725858</v>
+      </c>
       <c r="M111" s="52" t="n">
-        <v>0.937725858</v>
+        <v>0</v>
       </c>
       <c r="N111" s="52" t="n">
         <v>0</v>
       </c>
-      <c r="O111" s="52" t="n">
-        <v>0</v>
-      </c>
-      <c r="P111" s="20" t="inlineStr">
+      <c r="O111" s="20" t="inlineStr">
         <is>
           <t>Rotación Normal en Campaña Q4</t>
         </is>
@@ -31617,32 +31302,29 @@
         <v>45800</v>
       </c>
       <c r="H112" s="34" t="n">
-        <v>98400</v>
+        <v>0</v>
       </c>
       <c r="I112" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="J112" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K112" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L112" s="36" t="inlineStr">
+      <c r="J112" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K112" s="36" t="inlineStr">
         <is>
           <t>🟢 Alta Rotación (0-3M Nac)</t>
         </is>
       </c>
+      <c r="L112" s="55" t="n">
+        <v>0.903521506</v>
+      </c>
       <c r="M112" s="55" t="n">
-        <v>0.903521506</v>
+        <v>0</v>
       </c>
       <c r="N112" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="O112" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="P112" s="29" t="inlineStr">
+      <c r="O112" s="29" t="inlineStr">
         <is>
           <t>Rotación Normal en Campaña Q4</t>
         </is>
@@ -31677,32 +31359,29 @@
         <v>220</v>
       </c>
       <c r="H113" s="25" t="n">
-        <v>1160</v>
+        <v>0</v>
       </c>
       <c r="I113" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="J113" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K113" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L113" s="36" t="inlineStr">
+      <c r="J113" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K113" s="36" t="inlineStr">
         <is>
           <t>🟢 Alta Rotación (0-3M Nac)</t>
         </is>
       </c>
+      <c r="L113" s="52" t="n">
+        <v>0.72122703</v>
+      </c>
       <c r="M113" s="52" t="n">
-        <v>0.72122703</v>
+        <v>0</v>
       </c>
       <c r="N113" s="52" t="n">
         <v>0</v>
       </c>
-      <c r="O113" s="52" t="n">
-        <v>0</v>
-      </c>
-      <c r="P113" s="20" t="inlineStr">
+      <c r="O113" s="20" t="inlineStr">
         <is>
           <t>Rotación Normal en Campaña Q4</t>
         </is>
@@ -31737,32 +31416,29 @@
         <v>3380</v>
       </c>
       <c r="H114" s="34" t="n">
-        <v>7180</v>
+        <v>0</v>
       </c>
       <c r="I114" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="J114" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K114" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L114" s="36" t="inlineStr">
+      <c r="J114" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K114" s="36" t="inlineStr">
         <is>
           <t>🟢 Alta Rotación (0-3M Nac)</t>
         </is>
       </c>
+      <c r="L114" s="55" t="n">
+        <v>1.841516796</v>
+      </c>
       <c r="M114" s="55" t="n">
-        <v>1.841516796</v>
+        <v>0</v>
       </c>
       <c r="N114" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="O114" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="P114" s="29" t="inlineStr">
+      <c r="O114" s="29" t="inlineStr">
         <is>
           <t>Rotación Normal en Campaña Q4</t>
         </is>
@@ -31797,32 +31473,29 @@
         <v>19600</v>
       </c>
       <c r="H115" s="25" t="n">
-        <v>26000</v>
+        <v>0</v>
       </c>
       <c r="I115" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="J115" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K115" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L115" s="36" t="inlineStr">
+      <c r="J115" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K115" s="36" t="inlineStr">
         <is>
           <t>🟢 Alta Rotación (0-3M Nac)</t>
         </is>
       </c>
+      <c r="L115" s="52" t="n">
+        <v>0.578397589</v>
+      </c>
       <c r="M115" s="52" t="n">
-        <v>0.578397589</v>
+        <v>0</v>
       </c>
       <c r="N115" s="52" t="n">
         <v>0</v>
       </c>
-      <c r="O115" s="52" t="n">
-        <v>0</v>
-      </c>
-      <c r="P115" s="20" t="inlineStr">
+      <c r="O115" s="20" t="inlineStr">
         <is>
           <t>Rotación Normal en Campaña Q4</t>
         </is>
@@ -31857,32 +31530,29 @@
         <v>61000</v>
       </c>
       <c r="H116" s="34" t="n">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="I116" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="J116" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K116" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L116" s="36" t="inlineStr">
+      <c r="J116" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K116" s="36" t="inlineStr">
         <is>
           <t>🟢 Alta Rotación (0-3M Nac)</t>
         </is>
       </c>
+      <c r="L116" s="55" t="n">
+        <v>0.513511126</v>
+      </c>
       <c r="M116" s="55" t="n">
-        <v>0.513511126</v>
+        <v>0</v>
       </c>
       <c r="N116" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="O116" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="P116" s="29" t="inlineStr">
+      <c r="O116" s="29" t="inlineStr">
         <is>
           <t>Rotación Normal en Campaña Q4</t>
         </is>
@@ -31917,32 +31587,29 @@
         <v>830</v>
       </c>
       <c r="H117" s="25" t="n">
-        <v>3030</v>
+        <v>0</v>
       </c>
       <c r="I117" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="J117" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K117" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L117" s="36" t="inlineStr">
+      <c r="J117" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K117" s="36" t="inlineStr">
         <is>
           <t>🟢 Alta Rotación (0-3M Nac)</t>
         </is>
       </c>
+      <c r="L117" s="52" t="n">
+        <v>1.037405651</v>
+      </c>
       <c r="M117" s="52" t="n">
-        <v>1.037405651</v>
+        <v>0</v>
       </c>
       <c r="N117" s="52" t="n">
         <v>0</v>
       </c>
-      <c r="O117" s="52" t="n">
-        <v>0</v>
-      </c>
-      <c r="P117" s="20" t="inlineStr">
+      <c r="O117" s="20" t="inlineStr">
         <is>
           <t>Rotación Normal en Campaña Q4</t>
         </is>
@@ -31977,32 +31644,29 @@
         <v>3295</v>
       </c>
       <c r="H118" s="34" t="n">
-        <v>4795</v>
+        <v>0</v>
       </c>
       <c r="I118" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="J118" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K118" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L118" s="36" t="inlineStr">
+      <c r="J118" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K118" s="36" t="inlineStr">
         <is>
           <t>🟢 Alta Rotación (0-3M Nac)</t>
         </is>
       </c>
+      <c r="L118" s="55" t="n">
+        <v>2.104980496</v>
+      </c>
       <c r="M118" s="55" t="n">
-        <v>2.104980496</v>
+        <v>0</v>
       </c>
       <c r="N118" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="O118" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="P118" s="29" t="inlineStr">
+      <c r="O118" s="29" t="inlineStr">
         <is>
           <t>Rotación Normal en Campaña Q4</t>
         </is>
@@ -32037,32 +31701,29 @@
         <v>460</v>
       </c>
       <c r="H119" s="25" t="n">
-        <v>2240</v>
+        <v>0</v>
       </c>
       <c r="I119" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="J119" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K119" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L119" s="36" t="inlineStr">
+      <c r="J119" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K119" s="36" t="inlineStr">
         <is>
           <t>🟢 Alta Rotación (0-3M Nac)</t>
         </is>
       </c>
+      <c r="L119" s="52" t="n">
+        <v>2.230385922</v>
+      </c>
       <c r="M119" s="52" t="n">
-        <v>2.230385922</v>
+        <v>0</v>
       </c>
       <c r="N119" s="52" t="n">
         <v>0</v>
       </c>
-      <c r="O119" s="52" t="n">
-        <v>0</v>
-      </c>
-      <c r="P119" s="20" t="inlineStr">
+      <c r="O119" s="20" t="inlineStr">
         <is>
           <t>Rotación Normal en Campaña Q4</t>
         </is>
@@ -32097,32 +31758,29 @@
         <v>2880</v>
       </c>
       <c r="H120" s="34" t="n">
-        <v>5440</v>
+        <v>0</v>
       </c>
       <c r="I120" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="J120" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K120" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L120" s="36" t="inlineStr">
+      <c r="J120" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K120" s="36" t="inlineStr">
         <is>
           <t>🟢 Alta Rotación (0-3M Nac)</t>
         </is>
       </c>
+      <c r="L120" s="55" t="n">
+        <v>2.767847302</v>
+      </c>
       <c r="M120" s="55" t="n">
-        <v>2.767847302</v>
+        <v>0</v>
       </c>
       <c r="N120" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="O120" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="P120" s="29" t="inlineStr">
+      <c r="O120" s="29" t="inlineStr">
         <is>
           <t>Rotación Normal en Campaña Q4</t>
         </is>
@@ -32157,32 +31815,29 @@
         <v>9900</v>
       </c>
       <c r="H121" s="25" t="n">
-        <v>16020</v>
+        <v>0</v>
       </c>
       <c r="I121" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="J121" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K121" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L121" s="36" t="inlineStr">
+      <c r="J121" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K121" s="36" t="inlineStr">
         <is>
           <t>🟢 Alta Rotación (0-3M Nac)</t>
         </is>
       </c>
+      <c r="L121" s="52" t="n">
+        <v>2.202540124</v>
+      </c>
       <c r="M121" s="52" t="n">
-        <v>2.202540124</v>
+        <v>0</v>
       </c>
       <c r="N121" s="52" t="n">
         <v>0</v>
       </c>
-      <c r="O121" s="52" t="n">
-        <v>0</v>
-      </c>
-      <c r="P121" s="20" t="inlineStr">
+      <c r="O121" s="20" t="inlineStr">
         <is>
           <t>Rotación Normal en Campaña Q4</t>
         </is>
@@ -32217,32 +31872,29 @@
         <v>4000</v>
       </c>
       <c r="H122" s="34" t="n">
-        <v>6300</v>
+        <v>0</v>
       </c>
       <c r="I122" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="J122" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K122" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L122" s="36" t="inlineStr">
+      <c r="J122" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K122" s="36" t="inlineStr">
         <is>
           <t>🟢 Alta Rotación (0-3M Nac)</t>
         </is>
       </c>
+      <c r="L122" s="55" t="n">
+        <v>1.275723763</v>
+      </c>
       <c r="M122" s="55" t="n">
-        <v>1.275723763</v>
+        <v>0</v>
       </c>
       <c r="N122" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="O122" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="P122" s="29" t="inlineStr">
+      <c r="O122" s="29" t="inlineStr">
         <is>
           <t>Rotación Normal en Campaña Q4</t>
         </is>
@@ -32277,32 +31929,29 @@
         <v>2425</v>
       </c>
       <c r="H123" s="25" t="n">
-        <v>3745</v>
+        <v>0</v>
       </c>
       <c r="I123" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="J123" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K123" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L123" s="36" t="inlineStr">
+      <c r="J123" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K123" s="36" t="inlineStr">
         <is>
           <t>🟢 Alta Rotación (0-3M Nac)</t>
         </is>
       </c>
+      <c r="L123" s="52" t="n">
+        <v>1.708866566</v>
+      </c>
       <c r="M123" s="52" t="n">
-        <v>1.708866566</v>
+        <v>0</v>
       </c>
       <c r="N123" s="52" t="n">
         <v>0</v>
       </c>
-      <c r="O123" s="52" t="n">
-        <v>0</v>
-      </c>
-      <c r="P123" s="20" t="inlineStr">
+      <c r="O123" s="20" t="inlineStr">
         <is>
           <t>Rotación Normal en Campaña Q4</t>
         </is>
@@ -32337,32 +31986,29 @@
         <v>3765</v>
       </c>
       <c r="H124" s="34" t="n">
-        <v>5865</v>
+        <v>0</v>
       </c>
       <c r="I124" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="J124" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K124" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L124" s="36" t="inlineStr">
+      <c r="J124" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K124" s="36" t="inlineStr">
         <is>
           <t>🟢 Alta Rotación (0-3M Nac)</t>
         </is>
       </c>
+      <c r="L124" s="55" t="n">
+        <v>0</v>
+      </c>
       <c r="M124" s="55" t="n">
         <v>0</v>
       </c>
       <c r="N124" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="O124" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="P124" s="29" t="inlineStr">
+      <c r="O124" s="29" t="inlineStr">
         <is>
           <t>Rotación Normal en Campaña Q4</t>
         </is>
@@ -32397,32 +32043,29 @@
         <v>5040</v>
       </c>
       <c r="H125" s="25" t="n">
-        <v>9140</v>
+        <v>0</v>
       </c>
       <c r="I125" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="J125" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K125" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L125" s="36" t="inlineStr">
+      <c r="J125" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K125" s="36" t="inlineStr">
         <is>
           <t>🟢 Alta Rotación (0-3M Nac)</t>
         </is>
       </c>
+      <c r="L125" s="52" t="n">
+        <v>2.370023959</v>
+      </c>
       <c r="M125" s="52" t="n">
-        <v>2.370023959</v>
+        <v>0</v>
       </c>
       <c r="N125" s="52" t="n">
         <v>0</v>
       </c>
-      <c r="O125" s="52" t="n">
-        <v>0</v>
-      </c>
-      <c r="P125" s="20" t="inlineStr">
+      <c r="O125" s="20" t="inlineStr">
         <is>
           <t>Rotación Normal en Campaña Q4</t>
         </is>
@@ -32457,32 +32100,29 @@
         <v>945</v>
       </c>
       <c r="H126" s="34" t="n">
-        <v>3385</v>
+        <v>0</v>
       </c>
       <c r="I126" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="J126" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K126" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L126" s="36" t="inlineStr">
+      <c r="J126" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K126" s="36" t="inlineStr">
         <is>
           <t>🟢 Alta Rotación (0-3M Nac)</t>
         </is>
       </c>
+      <c r="L126" s="55" t="n">
+        <v>0.721216037</v>
+      </c>
       <c r="M126" s="55" t="n">
-        <v>0.721216037</v>
+        <v>0</v>
       </c>
       <c r="N126" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="O126" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="P126" s="29" t="inlineStr">
+      <c r="O126" s="29" t="inlineStr">
         <is>
           <t>Rotación Normal en Campaña Q4</t>
         </is>
@@ -32517,32 +32157,29 @@
         <v>675</v>
       </c>
       <c r="H127" s="25" t="n">
-        <v>895</v>
+        <v>0</v>
       </c>
       <c r="I127" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="J127" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K127" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L127" s="36" t="inlineStr">
+      <c r="J127" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K127" s="36" t="inlineStr">
         <is>
           <t>🟢 Alta Rotación (0-3M Nac)</t>
         </is>
       </c>
+      <c r="L127" s="52" t="n">
+        <v>2.978697502</v>
+      </c>
       <c r="M127" s="52" t="n">
-        <v>2.978697502</v>
+        <v>0</v>
       </c>
       <c r="N127" s="52" t="n">
         <v>0</v>
       </c>
-      <c r="O127" s="52" t="n">
-        <v>0</v>
-      </c>
-      <c r="P127" s="20" t="inlineStr">
+      <c r="O127" s="20" t="inlineStr">
         <is>
           <t>Rotación Normal en Campaña Q4</t>
         </is>
@@ -32577,32 +32214,29 @@
         <v>630</v>
       </c>
       <c r="H128" s="34" t="n">
-        <v>730</v>
+        <v>0</v>
       </c>
       <c r="I128" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="J128" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K128" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L128" s="36" t="inlineStr">
+      <c r="J128" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K128" s="36" t="inlineStr">
         <is>
           <t>🟢 Alta Rotación (0-3M Nac)</t>
         </is>
       </c>
+      <c r="L128" s="55" t="n">
+        <v>1.706891703</v>
+      </c>
       <c r="M128" s="55" t="n">
-        <v>1.706891703</v>
+        <v>0</v>
       </c>
       <c r="N128" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="O128" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="P128" s="29" t="inlineStr">
+      <c r="O128" s="29" t="inlineStr">
         <is>
           <t>Rotación Normal en Campaña Q4</t>
         </is>
@@ -32637,32 +32271,29 @@
         <v>3080</v>
       </c>
       <c r="H129" s="25" t="n">
-        <v>5640</v>
+        <v>0</v>
       </c>
       <c r="I129" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="J129" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K129" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L129" s="36" t="inlineStr">
+      <c r="J129" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K129" s="36" t="inlineStr">
         <is>
           <t>🟢 Alta Rotación (0-3M Nac)</t>
         </is>
       </c>
+      <c r="L129" s="52" t="n">
+        <v>1.791066572</v>
+      </c>
       <c r="M129" s="52" t="n">
-        <v>1.791066572</v>
+        <v>0</v>
       </c>
       <c r="N129" s="52" t="n">
         <v>0</v>
       </c>
-      <c r="O129" s="52" t="n">
-        <v>0</v>
-      </c>
-      <c r="P129" s="20" t="inlineStr">
+      <c r="O129" s="20" t="inlineStr">
         <is>
           <t>Rotación Normal en Campaña Q4</t>
         </is>
@@ -32697,32 +32328,29 @@
         <v>202</v>
       </c>
       <c r="H130" s="34" t="n">
-        <v>262</v>
+        <v>0</v>
       </c>
       <c r="I130" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="J130" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K130" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L130" s="36" t="inlineStr">
+      <c r="J130" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K130" s="36" t="inlineStr">
         <is>
           <t>🟢 Alta Rotación (0-3M Nac)</t>
         </is>
       </c>
+      <c r="L130" s="55" t="n">
+        <v>1.438211605</v>
+      </c>
       <c r="M130" s="55" t="n">
-        <v>1.438211605</v>
+        <v>0</v>
       </c>
       <c r="N130" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="O130" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="P130" s="29" t="inlineStr">
+      <c r="O130" s="29" t="inlineStr">
         <is>
           <t>Rotación Normal en Campaña Q4</t>
         </is>
@@ -32757,32 +32385,29 @@
         <v>0</v>
       </c>
       <c r="H131" s="25" t="n">
-        <v>9000</v>
+        <v>0</v>
       </c>
       <c r="I131" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="J131" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K131" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L131" s="36" t="inlineStr">
+      <c r="J131" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K131" s="36" t="inlineStr">
         <is>
           <t>🟢 Alta Rotación (0-3M Nac)</t>
         </is>
       </c>
+      <c r="L131" s="52" t="n">
+        <v>0.830397283</v>
+      </c>
       <c r="M131" s="52" t="n">
-        <v>0.830397283</v>
+        <v>0</v>
       </c>
       <c r="N131" s="52" t="n">
         <v>0</v>
       </c>
-      <c r="O131" s="52" t="n">
-        <v>0</v>
-      </c>
-      <c r="P131" s="20" t="inlineStr">
+      <c r="O131" s="20" t="inlineStr">
         <is>
           <t>Rotación Normal en Campaña Q4</t>
         </is>
@@ -32817,32 +32442,29 @@
         <v>10500</v>
       </c>
       <c r="H132" s="34" t="n">
-        <v>21780</v>
+        <v>0</v>
       </c>
       <c r="I132" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="J132" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K132" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L132" s="36" t="inlineStr">
+      <c r="J132" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K132" s="36" t="inlineStr">
         <is>
           <t>🟢 Alta Rotación (0-3M Nac)</t>
         </is>
       </c>
+      <c r="L132" s="55" t="n">
+        <v>0.776598329</v>
+      </c>
       <c r="M132" s="55" t="n">
-        <v>0.776598329</v>
+        <v>0</v>
       </c>
       <c r="N132" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="O132" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="P132" s="29" t="inlineStr">
+      <c r="O132" s="29" t="inlineStr">
         <is>
           <t>Rotación Normal en Campaña Q4</t>
         </is>
@@ -32877,32 +32499,29 @@
         <v>700</v>
       </c>
       <c r="H133" s="25" t="n">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="I133" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="J133" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K133" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L133" s="36" t="inlineStr">
+      <c r="J133" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K133" s="36" t="inlineStr">
         <is>
           <t>🟢 Alta Rotación (0-3M Nac)</t>
         </is>
       </c>
+      <c r="L133" s="52" t="n">
+        <v>1.031823456</v>
+      </c>
       <c r="M133" s="52" t="n">
-        <v>1.031823456</v>
+        <v>0</v>
       </c>
       <c r="N133" s="52" t="n">
         <v>0</v>
       </c>
-      <c r="O133" s="52" t="n">
-        <v>0</v>
-      </c>
-      <c r="P133" s="20" t="inlineStr">
+      <c r="O133" s="20" t="inlineStr">
         <is>
           <t>Rotación Normal en Campaña Q4</t>
         </is>
@@ -32937,32 +32556,29 @@
         <v>680</v>
       </c>
       <c r="H134" s="34" t="n">
-        <v>1320</v>
+        <v>0</v>
       </c>
       <c r="I134" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="J134" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K134" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L134" s="36" t="inlineStr">
+      <c r="J134" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K134" s="36" t="inlineStr">
         <is>
           <t>🟢 Alta Rotación (0-3M Nac)</t>
         </is>
       </c>
+      <c r="L134" s="55" t="n">
+        <v>1.013686477</v>
+      </c>
       <c r="M134" s="55" t="n">
-        <v>1.013686477</v>
+        <v>0</v>
       </c>
       <c r="N134" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="O134" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="P134" s="29" t="inlineStr">
+      <c r="O134" s="29" t="inlineStr">
         <is>
           <t>Rotación Normal en Campaña Q4</t>
         </is>
@@ -32997,32 +32613,29 @@
         <v>3240</v>
       </c>
       <c r="H135" s="25" t="n">
-        <v>6240</v>
+        <v>0</v>
       </c>
       <c r="I135" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="J135" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K135" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L135" s="36" t="inlineStr">
+      <c r="J135" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K135" s="36" t="inlineStr">
         <is>
           <t>🟢 Alta Rotación (0-3M Nac)</t>
         </is>
       </c>
+      <c r="L135" s="52" t="n">
+        <v>1.181316594</v>
+      </c>
       <c r="M135" s="52" t="n">
-        <v>1.181316594</v>
+        <v>0</v>
       </c>
       <c r="N135" s="52" t="n">
         <v>0</v>
       </c>
-      <c r="O135" s="52" t="n">
-        <v>0</v>
-      </c>
-      <c r="P135" s="20" t="inlineStr">
+      <c r="O135" s="20" t="inlineStr">
         <is>
           <t>Rotación Normal en Campaña Q4</t>
         </is>
@@ -33057,32 +32670,29 @@
         <v>2885</v>
       </c>
       <c r="H136" s="34" t="n">
-        <v>4485</v>
+        <v>0</v>
       </c>
       <c r="I136" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="J136" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K136" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L136" s="36" t="inlineStr">
+      <c r="J136" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K136" s="36" t="inlineStr">
         <is>
           <t>🟢 Alta Rotación (0-3M Nac)</t>
         </is>
       </c>
+      <c r="L136" s="55" t="n">
+        <v>4.234440693</v>
+      </c>
       <c r="M136" s="55" t="n">
-        <v>4.234440693</v>
+        <v>0</v>
       </c>
       <c r="N136" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="O136" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="P136" s="29" t="inlineStr">
+      <c r="O136" s="29" t="inlineStr">
         <is>
           <t>Rotación Normal en Campaña Q4</t>
         </is>
@@ -33117,32 +32727,29 @@
         <v>2000</v>
       </c>
       <c r="H137" s="25" t="n">
-        <v>6000</v>
+        <v>0</v>
       </c>
       <c r="I137" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="J137" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K137" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L137" s="36" t="inlineStr">
+      <c r="J137" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K137" s="36" t="inlineStr">
         <is>
           <t>🟢 Alta Rotación (0-3M Nac)</t>
         </is>
       </c>
+      <c r="L137" s="52" t="n">
+        <v>0.7345970000000001</v>
+      </c>
       <c r="M137" s="52" t="n">
-        <v>0.7345970000000001</v>
+        <v>0</v>
       </c>
       <c r="N137" s="52" t="n">
         <v>0</v>
       </c>
-      <c r="O137" s="52" t="n">
-        <v>0</v>
-      </c>
-      <c r="P137" s="20" t="inlineStr">
+      <c r="O137" s="20" t="inlineStr">
         <is>
           <t>Rotación Normal en Campaña Q4</t>
         </is>
@@ -33177,32 +32784,29 @@
         <v>4080</v>
       </c>
       <c r="H138" s="34" t="n">
-        <v>6640</v>
+        <v>0</v>
       </c>
       <c r="I138" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="J138" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K138" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L138" s="36" t="inlineStr">
+      <c r="J138" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K138" s="36" t="inlineStr">
         <is>
           <t>🟢 Alta Rotación (0-3M Nac)</t>
         </is>
       </c>
+      <c r="L138" s="55" t="n">
+        <v>0.5633151199999999</v>
+      </c>
       <c r="M138" s="55" t="n">
-        <v>0.5633151199999999</v>
+        <v>0</v>
       </c>
       <c r="N138" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="O138" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="P138" s="29" t="inlineStr">
+      <c r="O138" s="29" t="inlineStr">
         <is>
           <t>Rotación Normal en Campaña Q4</t>
         </is>
@@ -33237,32 +32841,29 @@
         <v>800</v>
       </c>
       <c r="H139" s="25" t="n">
-        <v>2080</v>
+        <v>0</v>
       </c>
       <c r="I139" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="J139" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K139" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L139" s="36" t="inlineStr">
+      <c r="J139" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K139" s="36" t="inlineStr">
         <is>
           <t>🟢 Alta Rotación (0-3M Nac)</t>
         </is>
       </c>
+      <c r="L139" s="52" t="n">
+        <v>1.100219136</v>
+      </c>
       <c r="M139" s="52" t="n">
-        <v>1.100219136</v>
+        <v>0</v>
       </c>
       <c r="N139" s="52" t="n">
         <v>0</v>
       </c>
-      <c r="O139" s="52" t="n">
-        <v>0</v>
-      </c>
-      <c r="P139" s="20" t="inlineStr">
+      <c r="O139" s="20" t="inlineStr">
         <is>
           <t>Rotación Normal en Campaña Q4</t>
         </is>
@@ -33304,24 +32905,20 @@
         <f>SUM(J9:J139)</f>
         <v/>
       </c>
-      <c r="K140" s="39">
-        <f>SUM(K9:K139)</f>
+      <c r="K140" s="40" t="inlineStr"/>
+      <c r="L140" s="40" t="inlineStr"/>
+      <c r="M140" s="59">
+        <f>SUM(M9:M139)</f>
         <v/>
       </c>
-      <c r="L140" s="40" t="inlineStr"/>
-      <c r="M140" s="40" t="inlineStr"/>
       <c r="N140" s="59">
         <f>SUM(N9:N139)</f>
         <v/>
       </c>
-      <c r="O140" s="59">
-        <f>SUM(O9:O139)</f>
-        <v/>
-      </c>
-      <c r="P140" s="60" t="inlineStr"/>
+      <c r="O140" s="60" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A8:P139"/>
+  <autoFilter ref="A8:O139"/>
   <mergeCells count="15">
     <mergeCell ref="M5:P5"/>
     <mergeCell ref="A5:D5"/>
@@ -33329,11 +32926,11 @@
     <mergeCell ref="D7:E7"/>
     <mergeCell ref="A1:P1"/>
     <mergeCell ref="A4:D4"/>
-    <mergeCell ref="I7:P7"/>
+    <mergeCell ref="H7:O7"/>
     <mergeCell ref="E4:H4"/>
     <mergeCell ref="I4:L4"/>
+    <mergeCell ref="F7:G7"/>
     <mergeCell ref="A140:C140"/>
-    <mergeCell ref="F7:H7"/>
     <mergeCell ref="A7:C7"/>
     <mergeCell ref="E5:H5"/>
     <mergeCell ref="I5:L5"/>

--- a/web_dashboard/Orden_Fabricacion_MRP_Codiagro.xlsx
+++ b/web_dashboard/Orden_Fabricacion_MRP_Codiagro.xlsx
@@ -845,7 +845,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Horizonte: Oct 26 (N) + Nov 26 + Dic 26 (3 meses)  |  Ámbito: Global (Nacional + Exportación)  |  Exportación: Siempre Sobre Pedido  |  Fecha Emisión: 08/10/2026 07:30</t>
+          <t xml:space="preserve">  Horizonte: Oct 26 (N) + Nov 26 + Dic 26 (3 meses)  |  Ámbito: Global (Nacional + Exportación)  |  Exportación: Siempre Sobre Pedido  |  Fecha Emisión: 13/10/2026 07:21</t>
         </is>
       </c>
     </row>
@@ -20782,7 +20782,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Horizonte: Octubre 2026 - Diciembre 2026  |  Total Graneles Químicos a Fabricar en Planta  |  Fecha Emisión: 08/10/2026 07:30</t>
+          <t xml:space="preserve">  Horizonte: Octubre 2026 - Diciembre 2026  |  Total Graneles Químicos a Fabricar en Planta  |  Fecha Emisión: 13/10/2026 07:21</t>
         </is>
       </c>
     </row>
@@ -25229,7 +25229,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Premisa de Gestión: Previsiones exclusivamente del Mercado Nacional (España). La exportación se fabricará siempre sobre pedido.  |  Fecha: 08/10/2026 07:30</t>
+          <t xml:space="preserve">  Premisa de Gestión: Previsiones exclusivamente del Mercado Nacional (España). La exportación se fabricará siempre sobre pedido.  |  Fecha: 13/10/2026 07:21</t>
         </is>
       </c>
     </row>

--- a/web_dashboard/Orden_Fabricacion_MRP_Codiagro.xlsx
+++ b/web_dashboard/Orden_Fabricacion_MRP_Codiagro.xlsx
@@ -845,7 +845,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Horizonte: Oct 26 (N) + Nov 26 + Dic 26 (3 meses)  |  Ámbito: Global (Nacional + Exportación)  |  Exportación: Siempre Sobre Pedido  |  Fecha Emisión: 20/10/2026 08:14</t>
+          <t xml:space="preserve">  Horizonte: Oct 26 (N) + Nov 26 + Dic 26 (3 meses)  |  Ámbito: Global (Nacional + Exportación)  |  Exportación: Siempre Sobre Pedido  |  Fecha Emisión: 21/10/2026 08:19</t>
         </is>
       </c>
     </row>
@@ -896,13 +896,13 @@
     <row r="5" ht="24" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>1.221.048 L</t>
+          <t>1.221.398 L</t>
         </is>
       </c>
       <c r="B5" s="4" t="n"/>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>1.221.048 u</t>
+          <t>1.221.398 u</t>
         </is>
       </c>
       <c r="D5" s="4" t="n"/>
@@ -928,7 +928,7 @@
       <c r="L5" s="4" t="n"/>
       <c r="M5" s="8" t="inlineStr">
         <is>
-          <t>248.170 u</t>
+          <t>244.220 u</t>
         </is>
       </c>
       <c r="N5" s="4" t="n"/>
@@ -1277,7 +1277,7 @@
         </is>
       </c>
       <c r="H12" s="33" t="n">
-        <v>20060</v>
+        <v>21340</v>
       </c>
       <c r="I12" s="33" t="n">
         <v>8280</v>
@@ -1298,10 +1298,10 @@
         <v>60880</v>
       </c>
       <c r="O12" s="34" t="n">
-        <v>40820</v>
+        <v>39540</v>
       </c>
       <c r="P12" s="34" t="n">
-        <v>40820</v>
+        <v>39540</v>
       </c>
       <c r="Q12" s="26" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
         </is>
       </c>
       <c r="H36" s="33" t="n">
-        <v>1590</v>
+        <v>1640</v>
       </c>
       <c r="I36" s="33" t="n">
         <v>0</v>
@@ -2906,10 +2906,10 @@
         <v>10000</v>
       </c>
       <c r="O36" s="34" t="n">
-        <v>8410</v>
+        <v>8360</v>
       </c>
       <c r="P36" s="34" t="n">
-        <v>8410</v>
+        <v>8360</v>
       </c>
       <c r="Q36" s="26" t="inlineStr">
         <is>
@@ -3957,7 +3957,7 @@
         </is>
       </c>
       <c r="H52" s="33" t="n">
-        <v>13980</v>
+        <v>13880</v>
       </c>
       <c r="I52" s="33" t="n">
         <v>3000</v>
@@ -3978,10 +3978,10 @@
         <v>18660</v>
       </c>
       <c r="O52" s="34" t="n">
-        <v>4680</v>
+        <v>4780</v>
       </c>
       <c r="P52" s="34" t="n">
-        <v>4680</v>
+        <v>4780</v>
       </c>
       <c r="Q52" s="26" t="inlineStr">
         <is>
@@ -4126,17 +4126,17 @@
     <row r="55" ht="19" customHeight="1">
       <c r="A55" s="18" t="inlineStr">
         <is>
-          <t>SS0020</t>
-        </is>
-      </c>
-      <c r="B55" s="19" t="inlineStr">
-        <is>
-          <t>SS0020MA</t>
+          <t>AN0020</t>
+        </is>
+      </c>
+      <c r="B55" s="22" t="inlineStr">
+        <is>
+          <t>AN0020</t>
         </is>
       </c>
       <c r="C55" s="20" t="inlineStr">
         <is>
-          <t>SAL-WAX-Ca sólido, 20 KG</t>
+          <t>ALCAPLANT NEW, 20 KG</t>
         </is>
       </c>
       <c r="D55" s="21" t="n">
@@ -4149,74 +4149,74 @@
       </c>
       <c r="F55" s="22" t="inlineStr">
         <is>
-          <t>MARRUECOS</t>
-        </is>
-      </c>
-      <c r="G55" s="23" t="inlineStr">
-        <is>
-          <t>Sobre Pedido (Export)</t>
+          <t>ESPAÑA</t>
+        </is>
+      </c>
+      <c r="G55" s="22" t="inlineStr">
+        <is>
+          <t>Para Previsión (Nac)</t>
         </is>
       </c>
       <c r="H55" s="24" t="n">
-        <v>0</v>
+        <v>25900</v>
       </c>
       <c r="I55" s="24" t="n">
         <v>0</v>
       </c>
       <c r="J55" s="24" t="n">
-        <v>2000</v>
+        <v>12000</v>
       </c>
       <c r="K55" s="24" t="n">
-        <v>0</v>
+        <v>17000</v>
       </c>
       <c r="L55" s="24" t="n">
-        <v>2000</v>
+        <v>1100</v>
       </c>
       <c r="M55" s="25" t="n">
-        <v>4000</v>
+        <v>30100</v>
       </c>
       <c r="N55" s="25" t="n">
-        <v>4000</v>
+        <v>30100</v>
       </c>
       <c r="O55" s="25" t="n">
-        <v>4000</v>
+        <v>4200</v>
       </c>
       <c r="P55" s="25" t="n">
-        <v>4000</v>
+        <v>4200</v>
       </c>
       <c r="Q55" s="26" t="inlineStr">
         <is>
-          <t>SOBRE PEDIDO (EXP)</t>
+          <t>FABRICACIÓN URGENTE</t>
         </is>
       </c>
     </row>
     <row r="56" ht="19" customHeight="1">
       <c r="A56" s="27" t="inlineStr">
         <is>
-          <t>GRE10005</t>
+          <t>SS0020</t>
         </is>
       </c>
       <c r="B56" s="28" t="inlineStr">
         <is>
-          <t>GRE10005GR</t>
+          <t>SS0020MA</t>
         </is>
       </c>
       <c r="C56" s="29" t="inlineStr">
         <is>
-          <t>TONAZ</t>
+          <t>SAL-WAX-Ca sólido, 20 KG</t>
         </is>
       </c>
       <c r="D56" s="30" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E56" s="29" t="inlineStr">
         <is>
-          <t>Garrafas 5L</t>
+          <t>Bolsas 20 Kg</t>
         </is>
       </c>
       <c r="F56" s="31" t="inlineStr">
         <is>
-          <t>GRECIA</t>
+          <t>MARRUECOS</t>
         </is>
       </c>
       <c r="G56" s="32" t="inlineStr">
@@ -4231,13 +4231,13 @@
         <v>0</v>
       </c>
       <c r="J56" s="33" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="K56" s="33" t="n">
         <v>0</v>
       </c>
       <c r="L56" s="33" t="n">
-        <v>4000</v>
+        <v>2000</v>
       </c>
       <c r="M56" s="34" t="n">
         <v>4000</v>
@@ -4260,17 +4260,17 @@
     <row r="57" ht="19" customHeight="1">
       <c r="A57" s="18" t="inlineStr">
         <is>
-          <t>SS0005</t>
+          <t>GRE10005</t>
         </is>
       </c>
       <c r="B57" s="19" t="inlineStr">
         <is>
-          <t>SS0005MX</t>
+          <t>GRE10005GR</t>
         </is>
       </c>
       <c r="C57" s="20" t="inlineStr">
         <is>
-          <t>SALWAX-CA, 5 KG</t>
+          <t>TONAZ</t>
         </is>
       </c>
       <c r="D57" s="21" t="n">
@@ -4278,12 +4278,12 @@
       </c>
       <c r="E57" s="20" t="inlineStr">
         <is>
-          <t>Bolsas 5 Kg</t>
+          <t>Garrafas 5L</t>
         </is>
       </c>
       <c r="F57" s="22" t="inlineStr">
         <is>
-          <t>NETHERLANS</t>
+          <t>GRECIA</t>
         </is>
       </c>
       <c r="G57" s="23" t="inlineStr">
@@ -4292,7 +4292,7 @@
         </is>
       </c>
       <c r="H57" s="24" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="I57" s="24" t="n">
         <v>0</v>
@@ -4301,10 +4301,10 @@
         <v>0</v>
       </c>
       <c r="K57" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" s="24" t="n">
         <v>4000</v>
-      </c>
-      <c r="L57" s="24" t="n">
-        <v>0</v>
       </c>
       <c r="M57" s="25" t="n">
         <v>4000</v>
@@ -4313,10 +4313,10 @@
         <v>4000</v>
       </c>
       <c r="O57" s="25" t="n">
-        <v>3880</v>
+        <v>4000</v>
       </c>
       <c r="P57" s="25" t="n">
-        <v>3880</v>
+        <v>4000</v>
       </c>
       <c r="Q57" s="26" t="inlineStr">
         <is>
@@ -4327,45 +4327,45 @@
     <row r="58" ht="19" customHeight="1">
       <c r="A58" s="27" t="inlineStr">
         <is>
-          <t>SS0020</t>
-        </is>
-      </c>
-      <c r="B58" s="31" t="inlineStr">
-        <is>
-          <t>SS0020</t>
+          <t>SS0005</t>
+        </is>
+      </c>
+      <c r="B58" s="28" t="inlineStr">
+        <is>
+          <t>SS0005MX</t>
         </is>
       </c>
       <c r="C58" s="29" t="inlineStr">
         <is>
-          <t>SAL-WAX-Ca sólido, 20 KG</t>
+          <t>SALWAX-CA, 5 KG</t>
         </is>
       </c>
       <c r="D58" s="30" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E58" s="29" t="inlineStr">
         <is>
-          <t>Bolsas 20 Kg</t>
+          <t>Bolsas 5 Kg</t>
         </is>
       </c>
       <c r="F58" s="31" t="inlineStr">
         <is>
-          <t>ESPAÑA</t>
-        </is>
-      </c>
-      <c r="G58" s="31" t="inlineStr">
-        <is>
-          <t>Para Previsión (Nac)</t>
+          <t>NETHERLANS</t>
+        </is>
+      </c>
+      <c r="G58" s="32" t="inlineStr">
+        <is>
+          <t>Sobre Pedido (Export)</t>
         </is>
       </c>
       <c r="H58" s="33" t="n">
-        <v>6240</v>
+        <v>120</v>
       </c>
       <c r="I58" s="33" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="J58" s="33" t="n">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="K58" s="33" t="n">
         <v>4000</v>
@@ -4374,117 +4374,117 @@
         <v>0</v>
       </c>
       <c r="M58" s="34" t="n">
-        <v>10000</v>
+        <v>4000</v>
       </c>
       <c r="N58" s="34" t="n">
-        <v>10000</v>
+        <v>4000</v>
       </c>
       <c r="O58" s="34" t="n">
-        <v>3760</v>
+        <v>3880</v>
       </c>
       <c r="P58" s="34" t="n">
-        <v>3760</v>
+        <v>3880</v>
       </c>
       <c r="Q58" s="26" t="inlineStr">
         <is>
-          <t>FABRICACIÓN URGENTE</t>
+          <t>SOBRE PEDIDO (EXP)</t>
         </is>
       </c>
     </row>
     <row r="59" ht="19" customHeight="1">
       <c r="A59" s="18" t="inlineStr">
         <is>
-          <t>BIO0005</t>
-        </is>
-      </c>
-      <c r="B59" s="19" t="inlineStr">
-        <is>
-          <t>BIO0005DO</t>
+          <t>SS0020</t>
+        </is>
+      </c>
+      <c r="B59" s="22" t="inlineStr">
+        <is>
+          <t>SS0020</t>
         </is>
       </c>
       <c r="C59" s="20" t="inlineStr">
         <is>
-          <t>BIORAD-20, 5L</t>
+          <t>SAL-WAX-Ca sólido, 20 KG</t>
         </is>
       </c>
       <c r="D59" s="21" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E59" s="20" t="inlineStr">
         <is>
-          <t>Garrafas 5L</t>
+          <t>Bolsas 20 Kg</t>
         </is>
       </c>
       <c r="F59" s="22" t="inlineStr">
         <is>
-          <t>DOMINICANA, REPÚBLICA</t>
-        </is>
-      </c>
-      <c r="G59" s="23" t="inlineStr">
-        <is>
-          <t>Sobre Pedido (Export)</t>
+          <t>ESPAÑA</t>
+        </is>
+      </c>
+      <c r="G59" s="22" t="inlineStr">
+        <is>
+          <t>Para Previsión (Nac)</t>
         </is>
       </c>
       <c r="H59" s="24" t="n">
-        <v>0</v>
+        <v>6240</v>
       </c>
       <c r="I59" s="24" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="J59" s="24" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="K59" s="24" t="n">
-        <v>3620</v>
+        <v>4000</v>
       </c>
       <c r="L59" s="24" t="n">
         <v>0</v>
       </c>
       <c r="M59" s="25" t="n">
-        <v>3620</v>
+        <v>10000</v>
       </c>
       <c r="N59" s="25" t="n">
-        <v>3620</v>
+        <v>10000</v>
       </c>
       <c r="O59" s="25" t="n">
-        <v>3620</v>
+        <v>3760</v>
       </c>
       <c r="P59" s="25" t="n">
-        <v>3620</v>
+        <v>3760</v>
       </c>
       <c r="Q59" s="26" t="inlineStr">
         <is>
-          <t>SOBRE PEDIDO (EXP)</t>
+          <t>FABRICACIÓN URGENTE</t>
         </is>
       </c>
     </row>
     <row r="60" ht="19" customHeight="1">
       <c r="A60" s="27" t="inlineStr">
         <is>
-          <t>SS0020</t>
+          <t>BIO0005</t>
         </is>
       </c>
       <c r="B60" s="28" t="inlineStr">
         <is>
-          <t>SS0020CR</t>
+          <t>BIO0005DO</t>
         </is>
       </c>
       <c r="C60" s="29" t="inlineStr">
         <is>
-          <t>SAL-WAX-Ca sólido, 20 KG</t>
+          <t>BIORAD-20, 5L</t>
         </is>
       </c>
       <c r="D60" s="30" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E60" s="29" t="inlineStr">
         <is>
-          <t>Bolsas 20 Kg</t>
+          <t>Garrafas 5L</t>
         </is>
       </c>
       <c r="F60" s="31" t="inlineStr">
         <is>
-          <t>COSTA RICA</t>
+          <t>DOMINICANA, REPÚBLICA</t>
         </is>
       </c>
       <c r="G60" s="32" t="inlineStr">
@@ -4499,25 +4499,25 @@
         <v>0</v>
       </c>
       <c r="J60" s="33" t="n">
-        <v>2760</v>
+        <v>0</v>
       </c>
       <c r="K60" s="33" t="n">
-        <v>0</v>
+        <v>3620</v>
       </c>
       <c r="L60" s="33" t="n">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="M60" s="34" t="n">
-        <v>3560</v>
+        <v>3620</v>
       </c>
       <c r="N60" s="34" t="n">
-        <v>3560</v>
+        <v>3620</v>
       </c>
       <c r="O60" s="34" t="n">
-        <v>3560</v>
+        <v>3620</v>
       </c>
       <c r="P60" s="34" t="n">
-        <v>3560</v>
+        <v>3620</v>
       </c>
       <c r="Q60" s="26" t="inlineStr">
         <is>
@@ -4528,30 +4528,30 @@
     <row r="61" ht="19" customHeight="1">
       <c r="A61" s="18" t="inlineStr">
         <is>
-          <t>AN0005</t>
+          <t>SS0020</t>
         </is>
       </c>
       <c r="B61" s="19" t="inlineStr">
         <is>
-          <t>AN0005DO</t>
+          <t>SS0020CR</t>
         </is>
       </c>
       <c r="C61" s="20" t="inlineStr">
         <is>
-          <t>ALCAPLANT NEW, 5 KG</t>
+          <t>SAL-WAX-Ca sólido, 20 KG</t>
         </is>
       </c>
       <c r="D61" s="21" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E61" s="20" t="inlineStr">
         <is>
-          <t>Bolsas 5 Kg</t>
+          <t>Bolsas 20 Kg</t>
         </is>
       </c>
       <c r="F61" s="22" t="inlineStr">
         <is>
-          <t>DOMINICANA, REPÚBLICA</t>
+          <t>COSTA RICA</t>
         </is>
       </c>
       <c r="G61" s="23" t="inlineStr">
@@ -4566,25 +4566,25 @@
         <v>0</v>
       </c>
       <c r="J61" s="24" t="n">
-        <v>0</v>
+        <v>2760</v>
       </c>
       <c r="K61" s="24" t="n">
-        <v>3300</v>
+        <v>0</v>
       </c>
       <c r="L61" s="24" t="n">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="M61" s="25" t="n">
-        <v>3300</v>
+        <v>3560</v>
       </c>
       <c r="N61" s="25" t="n">
-        <v>3300</v>
+        <v>3560</v>
       </c>
       <c r="O61" s="25" t="n">
-        <v>3300</v>
+        <v>3560</v>
       </c>
       <c r="P61" s="25" t="n">
-        <v>3300</v>
+        <v>3560</v>
       </c>
       <c r="Q61" s="26" t="inlineStr">
         <is>
@@ -4595,191 +4595,191 @@
     <row r="62" ht="19" customHeight="1">
       <c r="A62" s="27" t="inlineStr">
         <is>
-          <t>BIO0020</t>
-        </is>
-      </c>
-      <c r="B62" s="31" t="inlineStr">
-        <is>
-          <t>BIO0020</t>
+          <t>AN0005</t>
+        </is>
+      </c>
+      <c r="B62" s="28" t="inlineStr">
+        <is>
+          <t>AN0005DO</t>
         </is>
       </c>
       <c r="C62" s="29" t="inlineStr">
         <is>
-          <t>BIORAD-20, 20 L</t>
+          <t>ALCAPLANT NEW, 5 KG</t>
         </is>
       </c>
       <c r="D62" s="30" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E62" s="29" t="inlineStr">
         <is>
-          <t>Garrafas 20L</t>
+          <t>Bolsas 5 Kg</t>
         </is>
       </c>
       <c r="F62" s="31" t="inlineStr">
         <is>
-          <t>ESPAÑA</t>
-        </is>
-      </c>
-      <c r="G62" s="31" t="inlineStr">
-        <is>
-          <t>Para Previsión (Nac)</t>
+          <t>DOMINICANA, REPÚBLICA</t>
+        </is>
+      </c>
+      <c r="G62" s="32" t="inlineStr">
+        <is>
+          <t>Sobre Pedido (Export)</t>
         </is>
       </c>
       <c r="H62" s="33" t="n">
-        <v>10640</v>
+        <v>0</v>
       </c>
       <c r="I62" s="33" t="n">
-        <v>640</v>
+        <v>0</v>
       </c>
       <c r="J62" s="33" t="n">
-        <v>4720</v>
+        <v>0</v>
       </c>
       <c r="K62" s="33" t="n">
-        <v>5520</v>
+        <v>3300</v>
       </c>
       <c r="L62" s="33" t="n">
-        <v>2840</v>
+        <v>0</v>
       </c>
       <c r="M62" s="34" t="n">
-        <v>13720</v>
+        <v>3300</v>
       </c>
       <c r="N62" s="34" t="n">
-        <v>13720</v>
+        <v>3300</v>
       </c>
       <c r="O62" s="34" t="n">
-        <v>3080</v>
+        <v>3300</v>
       </c>
       <c r="P62" s="34" t="n">
-        <v>3080</v>
+        <v>3300</v>
       </c>
       <c r="Q62" s="26" t="inlineStr">
         <is>
-          <t>FABRICACIÓN URGENTE</t>
+          <t>SOBRE PEDIDO (EXP)</t>
         </is>
       </c>
     </row>
     <row r="63" ht="19" customHeight="1">
       <c r="A63" s="18" t="inlineStr">
         <is>
-          <t>AVAN0005</t>
-        </is>
-      </c>
-      <c r="B63" s="19" t="inlineStr">
-        <is>
-          <t>AVAN0005AZ</t>
+          <t>BIO0020</t>
+        </is>
+      </c>
+      <c r="B63" s="22" t="inlineStr">
+        <is>
+          <t>BIO0020</t>
         </is>
       </c>
       <c r="C63" s="20" t="inlineStr">
         <is>
-          <t>FLORAMEC AVANCE, 5 L</t>
+          <t>BIORAD-20, 20 L</t>
         </is>
       </c>
       <c r="D63" s="21" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E63" s="20" t="inlineStr">
         <is>
-          <t>Garrafas 5L</t>
+          <t>Garrafas 20L</t>
         </is>
       </c>
       <c r="F63" s="22" t="inlineStr">
         <is>
-          <t>AZERBAIYÁN</t>
-        </is>
-      </c>
-      <c r="G63" s="23" t="inlineStr">
-        <is>
-          <t>Sobre Pedido (Export)</t>
+          <t>ESPAÑA</t>
+        </is>
+      </c>
+      <c r="G63" s="22" t="inlineStr">
+        <is>
+          <t>Para Previsión (Nac)</t>
         </is>
       </c>
       <c r="H63" s="24" t="n">
-        <v>0</v>
+        <v>10440</v>
       </c>
       <c r="I63" s="24" t="n">
-        <v>0</v>
+        <v>640</v>
       </c>
       <c r="J63" s="24" t="n">
-        <v>0</v>
+        <v>4720</v>
       </c>
       <c r="K63" s="24" t="n">
-        <v>0</v>
+        <v>5520</v>
       </c>
       <c r="L63" s="24" t="n">
-        <v>3000</v>
+        <v>2840</v>
       </c>
       <c r="M63" s="25" t="n">
-        <v>3000</v>
+        <v>13720</v>
       </c>
       <c r="N63" s="25" t="n">
-        <v>3000</v>
+        <v>13720</v>
       </c>
       <c r="O63" s="25" t="n">
-        <v>3000</v>
+        <v>3280</v>
       </c>
       <c r="P63" s="25" t="n">
-        <v>3000</v>
+        <v>3280</v>
       </c>
       <c r="Q63" s="26" t="inlineStr">
         <is>
-          <t>SOBRE PEDIDO (EXP)</t>
+          <t>FABRICACIÓN URGENTE</t>
         </is>
       </c>
     </row>
     <row r="64" ht="19" customHeight="1">
       <c r="A64" s="27" t="inlineStr">
         <is>
-          <t>CPLUS1000</t>
-        </is>
-      </c>
-      <c r="B64" s="31" t="inlineStr">
-        <is>
-          <t>CPLUS1000</t>
+          <t>AVAN0005</t>
+        </is>
+      </c>
+      <c r="B64" s="28" t="inlineStr">
+        <is>
+          <t>AVAN0005AZ</t>
         </is>
       </c>
       <c r="C64" s="29" t="inlineStr">
         <is>
-          <t>CALCIPLUS, 1000 L</t>
+          <t>FLORAMEC AVANCE, 5 L</t>
         </is>
       </c>
       <c r="D64" s="30" t="n">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="E64" s="29" t="inlineStr">
         <is>
-          <t>Depósito 1000 L</t>
+          <t>Garrafas 5L</t>
         </is>
       </c>
       <c r="F64" s="31" t="inlineStr">
         <is>
-          <t>ESPAÑA</t>
-        </is>
-      </c>
-      <c r="G64" s="31" t="inlineStr">
-        <is>
-          <t>Para Previsión (Nac)</t>
+          <t>AZERBAIYÁN</t>
+        </is>
+      </c>
+      <c r="G64" s="32" t="inlineStr">
+        <is>
+          <t>Sobre Pedido (Export)</t>
         </is>
       </c>
       <c r="H64" s="33" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="I64" s="33" t="n">
         <v>0</v>
       </c>
       <c r="J64" s="33" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="K64" s="33" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="L64" s="33" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="M64" s="34" t="n">
-        <v>4000</v>
+        <v>3000</v>
       </c>
       <c r="N64" s="34" t="n">
-        <v>4000</v>
+        <v>3000</v>
       </c>
       <c r="O64" s="34" t="n">
         <v>3000</v>
@@ -4789,24 +4789,24 @@
       </c>
       <c r="Q64" s="26" t="inlineStr">
         <is>
-          <t>FABRICACIÓN URGENTE</t>
+          <t>SOBRE PEDIDO (EXP)</t>
         </is>
       </c>
     </row>
     <row r="65" ht="19" customHeight="1">
       <c r="A65" s="18" t="inlineStr">
         <is>
-          <t>CODIR1000</t>
-        </is>
-      </c>
-      <c r="B65" s="19" t="inlineStr">
-        <is>
-          <t>CODIR1000CR</t>
+          <t>CPLUS1000</t>
+        </is>
+      </c>
+      <c r="B65" s="22" t="inlineStr">
+        <is>
+          <t>CPLUS1000</t>
         </is>
       </c>
       <c r="C65" s="20" t="inlineStr">
         <is>
-          <t>CODIRESIST</t>
+          <t>CALCIPLUS, 1000 L</t>
         </is>
       </c>
       <c r="D65" s="21" t="n">
@@ -4819,34 +4819,34 @@
       </c>
       <c r="F65" s="22" t="inlineStr">
         <is>
-          <t>COSTA RICA</t>
-        </is>
-      </c>
-      <c r="G65" s="23" t="inlineStr">
-        <is>
-          <t>Sobre Pedido (Export)</t>
+          <t>ESPAÑA</t>
+        </is>
+      </c>
+      <c r="G65" s="22" t="inlineStr">
+        <is>
+          <t>Para Previsión (Nac)</t>
         </is>
       </c>
       <c r="H65" s="24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I65" s="24" t="n">
         <v>0</v>
       </c>
       <c r="J65" s="24" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="K65" s="24" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="L65" s="24" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="M65" s="25" t="n">
-        <v>3000</v>
+        <v>4000</v>
       </c>
       <c r="N65" s="25" t="n">
-        <v>3000</v>
+        <v>4000</v>
       </c>
       <c r="O65" s="25" t="n">
         <v>3000</v>
@@ -4856,24 +4856,24 @@
       </c>
       <c r="Q65" s="26" t="inlineStr">
         <is>
-          <t>SOBRE PEDIDO (EXP)</t>
+          <t>FABRICACIÓN URGENTE</t>
         </is>
       </c>
     </row>
     <row r="66" ht="19" customHeight="1">
       <c r="A66" s="27" t="inlineStr">
         <is>
-          <t>FIORI1000</t>
+          <t>CODIR1000</t>
         </is>
       </c>
       <c r="B66" s="28" t="inlineStr">
         <is>
-          <t>FIORI1000IT</t>
+          <t>CODIR1000CR</t>
         </is>
       </c>
       <c r="C66" s="29" t="inlineStr">
         <is>
-          <t>RADIFIORI, 1000 L</t>
+          <t>CODIRESIST</t>
         </is>
       </c>
       <c r="D66" s="30" t="n">
@@ -4886,7 +4886,7 @@
       </c>
       <c r="F66" s="31" t="inlineStr">
         <is>
-          <t>ITALIA</t>
+          <t>COSTA RICA</t>
         </is>
       </c>
       <c r="G66" s="32" t="inlineStr">
@@ -4901,13 +4901,13 @@
         <v>0</v>
       </c>
       <c r="J66" s="33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="K66" s="33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="L66" s="33" t="n">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="M66" s="34" t="n">
         <v>3000</v>
@@ -4930,51 +4930,51 @@
     <row r="67" ht="19" customHeight="1">
       <c r="A67" s="18" t="inlineStr">
         <is>
-          <t>DECA0020</t>
-        </is>
-      </c>
-      <c r="B67" s="22" t="inlineStr">
-        <is>
-          <t>DECA0020</t>
+          <t>FIORI1000</t>
+        </is>
+      </c>
+      <c r="B67" s="19" t="inlineStr">
+        <is>
+          <t>FIORI1000IT</t>
         </is>
       </c>
       <c r="C67" s="20" t="inlineStr">
         <is>
-          <t>DEFENS-CA-AE, 20 KG</t>
+          <t>RADIFIORI, 1000 L</t>
         </is>
       </c>
       <c r="D67" s="21" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="E67" s="20" t="inlineStr">
         <is>
-          <t>Bolsas 20 Kg</t>
+          <t>Depósito 1000 L</t>
         </is>
       </c>
       <c r="F67" s="22" t="inlineStr">
         <is>
-          <t>ESPAÑA</t>
-        </is>
-      </c>
-      <c r="G67" s="22" t="inlineStr">
-        <is>
-          <t>Para Previsión (Nac)</t>
+          <t>ITALIA</t>
+        </is>
+      </c>
+      <c r="G67" s="23" t="inlineStr">
+        <is>
+          <t>Sobre Pedido (Export)</t>
         </is>
       </c>
       <c r="H67" s="24" t="n">
         <v>0</v>
       </c>
       <c r="I67" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L67" s="24" t="n">
         <v>3000</v>
-      </c>
-      <c r="J67" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K67" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L67" s="24" t="n">
-        <v>0</v>
       </c>
       <c r="M67" s="25" t="n">
         <v>3000</v>
@@ -4990,32 +4990,32 @@
       </c>
       <c r="Q67" s="26" t="inlineStr">
         <is>
-          <t>FABRICACIÓN URGENTE</t>
+          <t>SOBRE PEDIDO (EXP)</t>
         </is>
       </c>
     </row>
     <row r="68" ht="19" customHeight="1">
       <c r="A68" s="27" t="inlineStr">
         <is>
-          <t>PREZN0005</t>
+          <t>DECA0020</t>
         </is>
       </c>
       <c r="B68" s="31" t="inlineStr">
         <is>
-          <t>PREZN0005</t>
+          <t>DECA0020</t>
         </is>
       </c>
       <c r="C68" s="29" t="inlineStr">
         <is>
-          <t>PREZINC, 5 kg</t>
+          <t>DEFENS-CA-AE, 20 KG</t>
         </is>
       </c>
       <c r="D68" s="30" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E68" s="29" t="inlineStr">
         <is>
-          <t>Bolsas 5 Kg</t>
+          <t>Bolsas 20 Kg</t>
         </is>
       </c>
       <c r="F68" s="31" t="inlineStr">
@@ -5029,10 +5029,10 @@
         </is>
       </c>
       <c r="H68" s="33" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="I68" s="33" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="J68" s="33" t="n">
         <v>0</v>
@@ -5041,7 +5041,7 @@
         <v>0</v>
       </c>
       <c r="L68" s="33" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="M68" s="34" t="n">
         <v>3000</v>
@@ -5050,10 +5050,10 @@
         <v>3000</v>
       </c>
       <c r="O68" s="34" t="n">
-        <v>2860</v>
+        <v>3000</v>
       </c>
       <c r="P68" s="34" t="n">
-        <v>2860</v>
+        <v>3000</v>
       </c>
       <c r="Q68" s="26" t="inlineStr">
         <is>
@@ -5064,51 +5064,51 @@
     <row r="69" ht="19" customHeight="1">
       <c r="A69" s="18" t="inlineStr">
         <is>
-          <t>A-50(2)0020</t>
-        </is>
-      </c>
-      <c r="B69" s="19" t="inlineStr">
-        <is>
-          <t>A-50(2)0020MA</t>
+          <t>PREZN0005</t>
+        </is>
+      </c>
+      <c r="B69" s="22" t="inlineStr">
+        <is>
+          <t>PREZN0005</t>
         </is>
       </c>
       <c r="C69" s="20" t="inlineStr">
         <is>
-          <t>CODIORGAN A-50, 20 KG</t>
+          <t>PREZINC, 5 kg</t>
         </is>
       </c>
       <c r="D69" s="21" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E69" s="20" t="inlineStr">
         <is>
-          <t>Bolsas 20 Kg</t>
+          <t>Bolsas 5 Kg</t>
         </is>
       </c>
       <c r="F69" s="22" t="inlineStr">
         <is>
-          <t>MARRUECOS</t>
-        </is>
-      </c>
-      <c r="G69" s="23" t="inlineStr">
-        <is>
-          <t>Sobre Pedido (Export)</t>
+          <t>ESPAÑA</t>
+        </is>
+      </c>
+      <c r="G69" s="22" t="inlineStr">
+        <is>
+          <t>Para Previsión (Nac)</t>
         </is>
       </c>
       <c r="H69" s="24" t="n">
-        <v>500</v>
+        <v>140</v>
       </c>
       <c r="I69" s="24" t="n">
         <v>0</v>
       </c>
       <c r="J69" s="24" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="K69" s="24" t="n">
         <v>0</v>
       </c>
       <c r="L69" s="24" t="n">
-        <v>1000</v>
+        <v>3000</v>
       </c>
       <c r="M69" s="25" t="n">
         <v>3000</v>
@@ -5117,178 +5117,178 @@
         <v>3000</v>
       </c>
       <c r="O69" s="25" t="n">
-        <v>2500</v>
+        <v>2860</v>
       </c>
       <c r="P69" s="25" t="n">
-        <v>2500</v>
+        <v>2860</v>
       </c>
       <c r="Q69" s="26" t="inlineStr">
         <is>
-          <t>SOBRE PEDIDO (EXP)</t>
+          <t>FABRICACIÓN URGENTE</t>
         </is>
       </c>
     </row>
     <row r="70" ht="19" customHeight="1">
       <c r="A70" s="27" t="inlineStr">
         <is>
-          <t>ANAE0005</t>
-        </is>
-      </c>
-      <c r="B70" s="31" t="inlineStr">
-        <is>
-          <t>ANAE0005</t>
+          <t>A-50(2)0020</t>
+        </is>
+      </c>
+      <c r="B70" s="28" t="inlineStr">
+        <is>
+          <t>A-50(2)0020MA</t>
         </is>
       </c>
       <c r="C70" s="29" t="inlineStr">
         <is>
-          <t>ALCAPLANT NEW AE, 5 KG</t>
+          <t>CODIORGAN A-50, 20 KG</t>
         </is>
       </c>
       <c r="D70" s="30" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E70" s="29" t="inlineStr">
         <is>
-          <t>Bolsas 5 Kg</t>
+          <t>Bolsas 20 Kg</t>
         </is>
       </c>
       <c r="F70" s="31" t="inlineStr">
         <is>
-          <t>ESPAÑA</t>
-        </is>
-      </c>
-      <c r="G70" s="31" t="inlineStr">
-        <is>
-          <t>Para Previsión (Nac)</t>
+          <t>MARRUECOS</t>
+        </is>
+      </c>
+      <c r="G70" s="32" t="inlineStr">
+        <is>
+          <t>Sobre Pedido (Export)</t>
         </is>
       </c>
       <c r="H70" s="33" t="n">
-        <v>10760</v>
+        <v>500</v>
       </c>
       <c r="I70" s="33" t="n">
-        <v>2200</v>
+        <v>0</v>
       </c>
       <c r="J70" s="33" t="n">
-        <v>4400</v>
+        <v>2000</v>
       </c>
       <c r="K70" s="33" t="n">
-        <v>6650</v>
+        <v>0</v>
       </c>
       <c r="L70" s="33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="M70" s="34" t="n">
-        <v>13250</v>
+        <v>3000</v>
       </c>
       <c r="N70" s="34" t="n">
-        <v>13250</v>
+        <v>3000</v>
       </c>
       <c r="O70" s="34" t="n">
-        <v>2490</v>
+        <v>2500</v>
       </c>
       <c r="P70" s="34" t="n">
-        <v>2490</v>
+        <v>2500</v>
       </c>
       <c r="Q70" s="26" t="inlineStr">
         <is>
-          <t>FABRICACIÓN URGENTE</t>
+          <t>SOBRE PEDIDO (EXP)</t>
         </is>
       </c>
     </row>
     <row r="71" ht="19" customHeight="1">
       <c r="A71" s="18" t="inlineStr">
         <is>
-          <t>CBROT0020</t>
-        </is>
-      </c>
-      <c r="B71" s="19" t="inlineStr">
-        <is>
-          <t>CBROT0020AZ</t>
+          <t>ANAE0005</t>
+        </is>
+      </c>
+      <c r="B71" s="22" t="inlineStr">
+        <is>
+          <t>ANAE0005</t>
         </is>
       </c>
       <c r="C71" s="20" t="inlineStr">
         <is>
-          <t>CODIBROT, 20 L</t>
+          <t>ALCAPLANT NEW AE, 5 KG</t>
         </is>
       </c>
       <c r="D71" s="21" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E71" s="20" t="inlineStr">
         <is>
-          <t>Garrafas 20L</t>
+          <t>Bolsas 5 Kg</t>
         </is>
       </c>
       <c r="F71" s="22" t="inlineStr">
         <is>
-          <t>AZERBAIYÁN</t>
-        </is>
-      </c>
-      <c r="G71" s="23" t="inlineStr">
-        <is>
-          <t>Sobre Pedido (Export)</t>
+          <t>ESPAÑA</t>
+        </is>
+      </c>
+      <c r="G71" s="22" t="inlineStr">
+        <is>
+          <t>Para Previsión (Nac)</t>
         </is>
       </c>
       <c r="H71" s="24" t="n">
-        <v>620</v>
+        <v>10760</v>
       </c>
       <c r="I71" s="24" t="n">
-        <v>0</v>
+        <v>2200</v>
       </c>
       <c r="J71" s="24" t="n">
-        <v>0</v>
+        <v>4400</v>
       </c>
       <c r="K71" s="24" t="n">
-        <v>0</v>
+        <v>6650</v>
       </c>
       <c r="L71" s="24" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="M71" s="25" t="n">
-        <v>3000</v>
+        <v>13250</v>
       </c>
       <c r="N71" s="25" t="n">
-        <v>3000</v>
+        <v>13250</v>
       </c>
       <c r="O71" s="25" t="n">
-        <v>2380</v>
+        <v>2490</v>
       </c>
       <c r="P71" s="25" t="n">
-        <v>2380</v>
+        <v>2490</v>
       </c>
       <c r="Q71" s="26" t="inlineStr">
         <is>
-          <t>SOBRE PEDIDO (EXP)</t>
+          <t>FABRICACIÓN URGENTE</t>
         </is>
       </c>
     </row>
     <row r="72" ht="19" customHeight="1">
       <c r="A72" s="27" t="inlineStr">
         <is>
-          <t>C-CU0001</t>
+          <t>CBROT0020</t>
         </is>
       </c>
       <c r="B72" s="28" t="inlineStr">
         <is>
-          <t>C-CU0001EC</t>
+          <t>CBROT0020AZ</t>
         </is>
       </c>
       <c r="C72" s="29" t="inlineStr">
         <is>
-          <t>CODICOBRE</t>
+          <t>CODIBROT, 20 L</t>
         </is>
       </c>
       <c r="D72" s="30" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E72" s="29" t="inlineStr">
         <is>
-          <t>Botellas 1L</t>
+          <t>Garrafas 20L</t>
         </is>
       </c>
       <c r="F72" s="31" t="inlineStr">
         <is>
-          <t>ECUADOR (INCLUIDAS LAS ISLAS GALÁPAGOS)</t>
+          <t>AZERBAIYÁN</t>
         </is>
       </c>
       <c r="G72" s="32" t="inlineStr">
@@ -5297,31 +5297,31 @@
         </is>
       </c>
       <c r="H72" s="33" t="n">
-        <v>0</v>
+        <v>620</v>
       </c>
       <c r="I72" s="33" t="n">
         <v>0</v>
       </c>
       <c r="J72" s="33" t="n">
-        <v>2376</v>
+        <v>0</v>
       </c>
       <c r="K72" s="33" t="n">
         <v>0</v>
       </c>
       <c r="L72" s="33" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="M72" s="34" t="n">
-        <v>2376</v>
+        <v>3000</v>
       </c>
       <c r="N72" s="34" t="n">
-        <v>2376</v>
+        <v>3000</v>
       </c>
       <c r="O72" s="34" t="n">
-        <v>2376</v>
+        <v>2380</v>
       </c>
       <c r="P72" s="34" t="n">
-        <v>2376</v>
+        <v>2380</v>
       </c>
       <c r="Q72" s="26" t="inlineStr">
         <is>
@@ -5332,30 +5332,30 @@
     <row r="73" ht="19" customHeight="1">
       <c r="A73" s="18" t="inlineStr">
         <is>
-          <t>DECA0005</t>
+          <t>C-CU0001</t>
         </is>
       </c>
       <c r="B73" s="19" t="inlineStr">
         <is>
-          <t>DECA0005CR</t>
+          <t>C-CU0001EC</t>
         </is>
       </c>
       <c r="C73" s="20" t="inlineStr">
         <is>
-          <t>DEFENS-CA-AE</t>
+          <t>CODICOBRE</t>
         </is>
       </c>
       <c r="D73" s="21" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E73" s="20" t="inlineStr">
         <is>
-          <t>Bolsas 5 Kg</t>
+          <t>Botellas 1L</t>
         </is>
       </c>
       <c r="F73" s="22" t="inlineStr">
         <is>
-          <t>COSTA RICA</t>
+          <t>ECUADOR (INCLUIDAS LAS ISLAS GALÁPAGOS)</t>
         </is>
       </c>
       <c r="G73" s="23" t="inlineStr">
@@ -5364,31 +5364,31 @@
         </is>
       </c>
       <c r="H73" s="24" t="n">
-        <v>960</v>
+        <v>0</v>
       </c>
       <c r="I73" s="24" t="n">
         <v>0</v>
       </c>
       <c r="J73" s="24" t="n">
-        <v>1100</v>
+        <v>2376</v>
       </c>
       <c r="K73" s="24" t="n">
-        <v>1100</v>
+        <v>0</v>
       </c>
       <c r="L73" s="24" t="n">
-        <v>1100</v>
+        <v>0</v>
       </c>
       <c r="M73" s="25" t="n">
-        <v>3300</v>
+        <v>2376</v>
       </c>
       <c r="N73" s="25" t="n">
-        <v>3300</v>
+        <v>2376</v>
       </c>
       <c r="O73" s="25" t="n">
-        <v>2340</v>
+        <v>2376</v>
       </c>
       <c r="P73" s="25" t="n">
-        <v>2340</v>
+        <v>2376</v>
       </c>
       <c r="Q73" s="26" t="inlineStr">
         <is>
@@ -5399,30 +5399,30 @@
     <row r="74" ht="19" customHeight="1">
       <c r="A74" s="27" t="inlineStr">
         <is>
-          <t>FTK0020</t>
+          <t>DECA0005</t>
         </is>
       </c>
       <c r="B74" s="28" t="inlineStr">
         <is>
-          <t>FTK0020RS</t>
+          <t>DECA0005CR</t>
         </is>
       </c>
       <c r="C74" s="29" t="inlineStr">
         <is>
-          <t>FITOKONTROL CA FLOW, 20 KG</t>
+          <t>DEFENS-CA-AE</t>
         </is>
       </c>
       <c r="D74" s="30" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E74" s="29" t="inlineStr">
         <is>
-          <t>Bolsas 20 Kg</t>
+          <t>Bolsas 5 Kg</t>
         </is>
       </c>
       <c r="F74" s="31" t="inlineStr">
         <is>
-          <t>SERBIA</t>
+          <t>COSTA RICA</t>
         </is>
       </c>
       <c r="G74" s="32" t="inlineStr">
@@ -5431,31 +5431,31 @@
         </is>
       </c>
       <c r="H74" s="33" t="n">
-        <v>0</v>
+        <v>960</v>
       </c>
       <c r="I74" s="33" t="n">
         <v>0</v>
       </c>
       <c r="J74" s="33" t="n">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="K74" s="33" t="n">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="L74" s="33" t="n">
-        <v>2200</v>
+        <v>1100</v>
       </c>
       <c r="M74" s="34" t="n">
-        <v>2200</v>
+        <v>3300</v>
       </c>
       <c r="N74" s="34" t="n">
-        <v>2200</v>
+        <v>3300</v>
       </c>
       <c r="O74" s="34" t="n">
-        <v>2200</v>
+        <v>2340</v>
       </c>
       <c r="P74" s="34" t="n">
-        <v>2200</v>
+        <v>2340</v>
       </c>
       <c r="Q74" s="26" t="inlineStr">
         <is>
@@ -5466,30 +5466,30 @@
     <row r="75" ht="19" customHeight="1">
       <c r="A75" s="18" t="inlineStr">
         <is>
-          <t>GRE20005</t>
+          <t>FTK0020</t>
         </is>
       </c>
       <c r="B75" s="19" t="inlineStr">
         <is>
-          <t>GRE20005GR</t>
+          <t>FTK0020RS</t>
         </is>
       </c>
       <c r="C75" s="20" t="inlineStr">
         <is>
-          <t>EGERSIS</t>
+          <t>FITOKONTROL CA FLOW, 20 KG</t>
         </is>
       </c>
       <c r="D75" s="21" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E75" s="20" t="inlineStr">
         <is>
-          <t>Garrafas 5L</t>
+          <t>Bolsas 20 Kg</t>
         </is>
       </c>
       <c r="F75" s="22" t="inlineStr">
         <is>
-          <t>GRECIA</t>
+          <t>SERBIA</t>
         </is>
       </c>
       <c r="G75" s="23" t="inlineStr">
@@ -5510,19 +5510,19 @@
         <v>0</v>
       </c>
       <c r="L75" s="24" t="n">
-        <v>2000</v>
+        <v>2200</v>
       </c>
       <c r="M75" s="25" t="n">
-        <v>2000</v>
+        <v>2200</v>
       </c>
       <c r="N75" s="25" t="n">
-        <v>2000</v>
+        <v>2200</v>
       </c>
       <c r="O75" s="25" t="n">
-        <v>2000</v>
+        <v>2200</v>
       </c>
       <c r="P75" s="25" t="n">
-        <v>2000</v>
+        <v>2200</v>
       </c>
       <c r="Q75" s="26" t="inlineStr">
         <is>
@@ -5533,17 +5533,17 @@
     <row r="76" ht="19" customHeight="1">
       <c r="A76" s="27" t="inlineStr">
         <is>
-          <t>A-500005</t>
+          <t>GRE20005</t>
         </is>
       </c>
       <c r="B76" s="28" t="inlineStr">
         <is>
-          <t>A-500005CR</t>
+          <t>GRE20005GR</t>
         </is>
       </c>
       <c r="C76" s="29" t="inlineStr">
         <is>
-          <t>CODIORGAN  A-50</t>
+          <t>EGERSIS</t>
         </is>
       </c>
       <c r="D76" s="30" t="n">
@@ -5551,12 +5551,12 @@
       </c>
       <c r="E76" s="29" t="inlineStr">
         <is>
-          <t>Bolsas 5 Kg</t>
+          <t>Garrafas 5L</t>
         </is>
       </c>
       <c r="F76" s="31" t="inlineStr">
         <is>
-          <t>COSTA RICA</t>
+          <t>GRECIA</t>
         </is>
       </c>
       <c r="G76" s="32" t="inlineStr">
@@ -5571,13 +5571,13 @@
         <v>0</v>
       </c>
       <c r="J76" s="33" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="K76" s="33" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="L76" s="33" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="M76" s="34" t="n">
         <v>2000</v>
@@ -5600,30 +5600,30 @@
     <row r="77" ht="19" customHeight="1">
       <c r="A77" s="18" t="inlineStr">
         <is>
-          <t>CM3M0001</t>
+          <t>A-500005</t>
         </is>
       </c>
       <c r="B77" s="19" t="inlineStr">
         <is>
-          <t>CM3M0001AZ</t>
+          <t>A-500005CR</t>
         </is>
       </c>
       <c r="C77" s="20" t="inlineStr">
         <is>
-          <t>TENSOLINE-MAX, 1 L</t>
+          <t>CODIORGAN  A-50</t>
         </is>
       </c>
       <c r="D77" s="21" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E77" s="20" t="inlineStr">
         <is>
-          <t>Botellas 1L</t>
+          <t>Bolsas 5 Kg</t>
         </is>
       </c>
       <c r="F77" s="22" t="inlineStr">
         <is>
-          <t>AZERBAIYÁN</t>
+          <t>COSTA RICA</t>
         </is>
       </c>
       <c r="G77" s="23" t="inlineStr">
@@ -5638,13 +5638,13 @@
         <v>0</v>
       </c>
       <c r="J77" s="24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="K77" s="24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="L77" s="24" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="M77" s="25" t="n">
         <v>2000</v>
@@ -5667,17 +5667,17 @@
     <row r="78" ht="19" customHeight="1">
       <c r="A78" s="27" t="inlineStr">
         <is>
-          <t>A-50(2)0001</t>
+          <t>CM3M0001</t>
         </is>
       </c>
       <c r="B78" s="28" t="inlineStr">
         <is>
-          <t>A-50(2)0001RS</t>
+          <t>CM3M0001AZ</t>
         </is>
       </c>
       <c r="C78" s="29" t="inlineStr">
         <is>
-          <t>CODIORGAN-A50</t>
+          <t>TENSOLINE-MAX, 1 L</t>
         </is>
       </c>
       <c r="D78" s="30" t="n">
@@ -5685,12 +5685,12 @@
       </c>
       <c r="E78" s="29" t="inlineStr">
         <is>
-          <t>Bolsas 1 Kg</t>
+          <t>Botellas 1L</t>
         </is>
       </c>
       <c r="F78" s="31" t="inlineStr">
         <is>
-          <t>SERBIA</t>
+          <t>AZERBAIYÁN</t>
         </is>
       </c>
       <c r="G78" s="32" t="inlineStr">
@@ -5734,30 +5734,30 @@
     <row r="79" ht="19" customHeight="1">
       <c r="A79" s="18" t="inlineStr">
         <is>
-          <t>CZNMNES1000</t>
+          <t>A-50(2)0001</t>
         </is>
       </c>
       <c r="B79" s="19" t="inlineStr">
         <is>
-          <t>CZNMNES1000TR</t>
+          <t>A-50(2)0001RS</t>
         </is>
       </c>
       <c r="C79" s="20" t="inlineStr">
         <is>
-          <t>CODIFOL ZN-MN, 1000 KG</t>
+          <t>CODIORGAN-A50</t>
         </is>
       </c>
       <c r="D79" s="21" t="n">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="E79" s="20" t="inlineStr">
         <is>
-          <t>Big Bag 1000 Kg</t>
+          <t>Bolsas 1 Kg</t>
         </is>
       </c>
       <c r="F79" s="22" t="inlineStr">
         <is>
-          <t>TURQUÍA</t>
+          <t>SERBIA</t>
         </is>
       </c>
       <c r="G79" s="23" t="inlineStr">
@@ -5801,17 +5801,17 @@
     <row r="80" ht="19" customHeight="1">
       <c r="A80" s="27" t="inlineStr">
         <is>
-          <t>A-501000</t>
+          <t>CZNMNES1000</t>
         </is>
       </c>
       <c r="B80" s="28" t="inlineStr">
         <is>
-          <t>A-501000TR</t>
+          <t>CZNMNES1000TR</t>
         </is>
       </c>
       <c r="C80" s="29" t="inlineStr">
         <is>
-          <t>CODIORGAN-A50, 1000 KG</t>
+          <t>CODIFOL ZN-MN, 1000 KG</t>
         </is>
       </c>
       <c r="D80" s="30" t="n">
@@ -5868,30 +5868,30 @@
     <row r="81" ht="19" customHeight="1">
       <c r="A81" s="18" t="inlineStr">
         <is>
-          <t>LP0001</t>
+          <t>A-501000</t>
         </is>
       </c>
       <c r="B81" s="19" t="inlineStr">
         <is>
-          <t>LP0001DO</t>
+          <t>A-501000TR</t>
         </is>
       </c>
       <c r="C81" s="20" t="inlineStr">
         <is>
-          <t>LAVAPLANT GRANEL</t>
+          <t>CODIORGAN-A50, 1000 KG</t>
         </is>
       </c>
       <c r="D81" s="21" t="n">
-        <v>1</v>
+        <v>1000</v>
       </c>
       <c r="E81" s="20" t="inlineStr">
         <is>
-          <t>Botellas 1L</t>
+          <t>Big Bag 1000 Kg</t>
         </is>
       </c>
       <c r="F81" s="22" t="inlineStr">
         <is>
-          <t>DOMINICANA, REPÚBLICA</t>
+          <t>TURQUÍA</t>
         </is>
       </c>
       <c r="G81" s="23" t="inlineStr">
@@ -5909,10 +5909,10 @@
         <v>0</v>
       </c>
       <c r="K81" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L81" s="24" t="n">
         <v>2000</v>
-      </c>
-      <c r="L81" s="24" t="n">
-        <v>0</v>
       </c>
       <c r="M81" s="25" t="n">
         <v>2000</v>
@@ -5935,17 +5935,17 @@
     <row r="82" ht="19" customHeight="1">
       <c r="A82" s="27" t="inlineStr">
         <is>
-          <t>START20001</t>
+          <t>LP0001</t>
         </is>
       </c>
       <c r="B82" s="28" t="inlineStr">
         <is>
-          <t>START20001DO</t>
+          <t>LP0001DO</t>
         </is>
       </c>
       <c r="C82" s="29" t="inlineStr">
         <is>
-          <t>RADISOL</t>
+          <t>LAVAPLANT GRANEL</t>
         </is>
       </c>
       <c r="D82" s="30" t="n">
@@ -6002,17 +6002,17 @@
     <row r="83" ht="19" customHeight="1">
       <c r="A83" s="18" t="inlineStr">
         <is>
-          <t>A-500001</t>
+          <t>START20001</t>
         </is>
       </c>
       <c r="B83" s="19" t="inlineStr">
         <is>
-          <t>A-500001GE</t>
+          <t>START20001DO</t>
         </is>
       </c>
       <c r="C83" s="20" t="inlineStr">
         <is>
-          <t>CODIORGAN-A50, 1 KG</t>
+          <t>RADISOL</t>
         </is>
       </c>
       <c r="D83" s="21" t="n">
@@ -6020,12 +6020,12 @@
       </c>
       <c r="E83" s="20" t="inlineStr">
         <is>
-          <t>Bolsas 1 Kg</t>
+          <t>Botellas 1L</t>
         </is>
       </c>
       <c r="F83" s="22" t="inlineStr">
         <is>
-          <t>GEORGIA</t>
+          <t>DOMINICANA, REPÚBLICA</t>
         </is>
       </c>
       <c r="G83" s="23" t="inlineStr">
@@ -6043,22 +6043,22 @@
         <v>0</v>
       </c>
       <c r="K83" s="24" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="L83" s="24" t="n">
-        <v>1920</v>
+        <v>0</v>
       </c>
       <c r="M83" s="25" t="n">
-        <v>1920</v>
+        <v>2000</v>
       </c>
       <c r="N83" s="25" t="n">
-        <v>1920</v>
+        <v>2000</v>
       </c>
       <c r="O83" s="25" t="n">
-        <v>1920</v>
+        <v>2000</v>
       </c>
       <c r="P83" s="25" t="n">
-        <v>1920</v>
+        <v>2000</v>
       </c>
       <c r="Q83" s="26" t="inlineStr">
         <is>
@@ -6069,17 +6069,17 @@
     <row r="84" ht="19" customHeight="1">
       <c r="A84" s="27" t="inlineStr">
         <is>
-          <t>AGZNP0001</t>
+          <t>A-500001</t>
         </is>
       </c>
       <c r="B84" s="28" t="inlineStr">
         <is>
-          <t>AGZNP0001EG</t>
+          <t>A-500001GE</t>
         </is>
       </c>
       <c r="C84" s="29" t="inlineStr">
         <is>
-          <t>AGROXILATO-ZN PLUS</t>
+          <t>CODIORGAN-A50, 1 KG</t>
         </is>
       </c>
       <c r="D84" s="30" t="n">
@@ -6092,7 +6092,7 @@
       </c>
       <c r="F84" s="31" t="inlineStr">
         <is>
-          <t>EGIPTO</t>
+          <t>GEORGIA</t>
         </is>
       </c>
       <c r="G84" s="32" t="inlineStr">
@@ -6101,31 +6101,31 @@
         </is>
       </c>
       <c r="H84" s="33" t="n">
-        <v>128</v>
+        <v>0</v>
       </c>
       <c r="I84" s="33" t="n">
         <v>0</v>
       </c>
       <c r="J84" s="33" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="K84" s="33" t="n">
         <v>0</v>
       </c>
       <c r="L84" s="33" t="n">
-        <v>0</v>
+        <v>1920</v>
       </c>
       <c r="M84" s="34" t="n">
-        <v>2000</v>
+        <v>1920</v>
       </c>
       <c r="N84" s="34" t="n">
-        <v>2000</v>
+        <v>1920</v>
       </c>
       <c r="O84" s="34" t="n">
-        <v>1872</v>
+        <v>1920</v>
       </c>
       <c r="P84" s="34" t="n">
-        <v>1872</v>
+        <v>1920</v>
       </c>
       <c r="Q84" s="26" t="inlineStr">
         <is>
@@ -6136,30 +6136,30 @@
     <row r="85" ht="19" customHeight="1">
       <c r="A85" s="18" t="inlineStr">
         <is>
-          <t>PHD0005</t>
+          <t>AGZNP0001</t>
         </is>
       </c>
       <c r="B85" s="19" t="inlineStr">
         <is>
-          <t>PHD0005MA</t>
+          <t>AGZNP0001EG</t>
         </is>
       </c>
       <c r="C85" s="20" t="inlineStr">
         <is>
-          <t>PH-DOWNER, 5 L</t>
+          <t>AGROXILATO-ZN PLUS</t>
         </is>
       </c>
       <c r="D85" s="21" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E85" s="20" t="inlineStr">
         <is>
-          <t>Garrafas 5L</t>
+          <t>Bolsas 1 Kg</t>
         </is>
       </c>
       <c r="F85" s="22" t="inlineStr">
         <is>
-          <t>MARRUECOS</t>
+          <t>EGIPTO</t>
         </is>
       </c>
       <c r="G85" s="23" t="inlineStr">
@@ -6168,13 +6168,13 @@
         </is>
       </c>
       <c r="H85" s="24" t="n">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="I85" s="24" t="n">
         <v>0</v>
       </c>
       <c r="J85" s="24" t="n">
-        <v>1600</v>
+        <v>2000</v>
       </c>
       <c r="K85" s="24" t="n">
         <v>0</v>
@@ -6183,16 +6183,16 @@
         <v>0</v>
       </c>
       <c r="M85" s="25" t="n">
-        <v>1600</v>
+        <v>2000</v>
       </c>
       <c r="N85" s="25" t="n">
-        <v>1600</v>
+        <v>2000</v>
       </c>
       <c r="O85" s="25" t="n">
-        <v>1600</v>
+        <v>1872</v>
       </c>
       <c r="P85" s="25" t="n">
-        <v>1600</v>
+        <v>1872</v>
       </c>
       <c r="Q85" s="26" t="inlineStr">
         <is>
@@ -6203,30 +6203,30 @@
     <row r="86" ht="19" customHeight="1">
       <c r="A86" s="27" t="inlineStr">
         <is>
-          <t>CODIR0001</t>
+          <t>PHD0005</t>
         </is>
       </c>
       <c r="B86" s="28" t="inlineStr">
         <is>
-          <t>CODIR0001PA</t>
+          <t>PHD0005MA</t>
         </is>
       </c>
       <c r="C86" s="29" t="inlineStr">
         <is>
-          <t>CODIRESIST, 1 L</t>
+          <t>PH-DOWNER, 5 L</t>
         </is>
       </c>
       <c r="D86" s="30" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E86" s="29" t="inlineStr">
         <is>
-          <t>Botellas 1L</t>
+          <t>Garrafas 5L</t>
         </is>
       </c>
       <c r="F86" s="31" t="inlineStr">
         <is>
-          <t>PANAMÁ</t>
+          <t>MARRUECOS</t>
         </is>
       </c>
       <c r="G86" s="32" t="inlineStr">
@@ -6235,31 +6235,31 @@
         </is>
       </c>
       <c r="H86" s="33" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="I86" s="33" t="n">
         <v>0</v>
       </c>
       <c r="J86" s="33" t="n">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="K86" s="33" t="n">
         <v>0</v>
       </c>
       <c r="L86" s="33" t="n">
-        <v>1584</v>
+        <v>0</v>
       </c>
       <c r="M86" s="34" t="n">
-        <v>1584</v>
+        <v>1600</v>
       </c>
       <c r="N86" s="34" t="n">
-        <v>1584</v>
+        <v>1600</v>
       </c>
       <c r="O86" s="34" t="n">
-        <v>1561</v>
+        <v>1600</v>
       </c>
       <c r="P86" s="34" t="n">
-        <v>1561</v>
+        <v>1600</v>
       </c>
       <c r="Q86" s="26" t="inlineStr">
         <is>
@@ -6270,39 +6270,39 @@
     <row r="87" ht="19" customHeight="1">
       <c r="A87" s="18" t="inlineStr">
         <is>
-          <t>FROST-P0020</t>
-        </is>
-      </c>
-      <c r="B87" s="22" t="inlineStr">
-        <is>
-          <t>FROST-P0020</t>
+          <t>CODIR0001</t>
+        </is>
+      </c>
+      <c r="B87" s="19" t="inlineStr">
+        <is>
+          <t>CODIR0001PA</t>
         </is>
       </c>
       <c r="C87" s="20" t="inlineStr">
         <is>
-          <t>CODIFROST PLUS, 20 L</t>
+          <t>CODIRESIST, 1 L</t>
         </is>
       </c>
       <c r="D87" s="21" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="E87" s="20" t="inlineStr">
         <is>
-          <t>Garrafas 20L</t>
+          <t>Botellas 1L</t>
         </is>
       </c>
       <c r="F87" s="22" t="inlineStr">
         <is>
-          <t>ESPAÑA</t>
-        </is>
-      </c>
-      <c r="G87" s="22" t="inlineStr">
-        <is>
-          <t>Para Previsión (Nac)</t>
+          <t>PANAMÁ</t>
+        </is>
+      </c>
+      <c r="G87" s="23" t="inlineStr">
+        <is>
+          <t>Sobre Pedido (Export)</t>
         </is>
       </c>
       <c r="H87" s="24" t="n">
-        <v>280</v>
+        <v>23</v>
       </c>
       <c r="I87" s="24" t="n">
         <v>0</v>
@@ -6311,43 +6311,43 @@
         <v>0</v>
       </c>
       <c r="K87" s="24" t="n">
-        <v>1580</v>
+        <v>0</v>
       </c>
       <c r="L87" s="24" t="n">
-        <v>200</v>
+        <v>1584</v>
       </c>
       <c r="M87" s="25" t="n">
-        <v>1780</v>
+        <v>1584</v>
       </c>
       <c r="N87" s="25" t="n">
-        <v>1780</v>
+        <v>1584</v>
       </c>
       <c r="O87" s="25" t="n">
-        <v>1500</v>
+        <v>1561</v>
       </c>
       <c r="P87" s="25" t="n">
-        <v>1500</v>
+        <v>1561</v>
       </c>
       <c r="Q87" s="26" t="inlineStr">
         <is>
-          <t>FABRICACIÓN URGENTE</t>
+          <t>SOBRE PEDIDO (EXP)</t>
         </is>
       </c>
     </row>
     <row r="88" ht="19" customHeight="1">
       <c r="A88" s="27" t="inlineStr">
         <is>
-          <t>A-500020</t>
+          <t>FROST-P0020</t>
         </is>
       </c>
       <c r="B88" s="31" t="inlineStr">
         <is>
-          <t>A-500020</t>
+          <t>FROST-P0020</t>
         </is>
       </c>
       <c r="C88" s="29" t="inlineStr">
         <is>
-          <t>CODIORGAN  A-50</t>
+          <t>CODIFROST PLUS, 20 L</t>
         </is>
       </c>
       <c r="D88" s="30" t="n">
@@ -6355,7 +6355,7 @@
       </c>
       <c r="E88" s="29" t="inlineStr">
         <is>
-          <t>Bolsas 20 Kg</t>
+          <t>Garrafas 20L</t>
         </is>
       </c>
       <c r="F88" s="31" t="inlineStr">
@@ -6369,25 +6369,25 @@
         </is>
       </c>
       <c r="H88" s="33" t="n">
-        <v>0</v>
+        <v>280</v>
       </c>
       <c r="I88" s="33" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="J88" s="33" t="n">
         <v>0</v>
       </c>
       <c r="K88" s="33" t="n">
-        <v>0</v>
+        <v>1580</v>
       </c>
       <c r="L88" s="33" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="M88" s="34" t="n">
-        <v>1500</v>
+        <v>1780</v>
       </c>
       <c r="N88" s="34" t="n">
-        <v>1500</v>
+        <v>1780</v>
       </c>
       <c r="O88" s="34" t="n">
         <v>1500</v>
@@ -6404,51 +6404,51 @@
     <row r="89" ht="19" customHeight="1">
       <c r="A89" s="18" t="inlineStr">
         <is>
-          <t>AGZN0005</t>
-        </is>
-      </c>
-      <c r="B89" s="19" t="inlineStr">
-        <is>
-          <t>AGZN0005CR</t>
+          <t>A-500020</t>
+        </is>
+      </c>
+      <c r="B89" s="22" t="inlineStr">
+        <is>
+          <t>A-500020</t>
         </is>
       </c>
       <c r="C89" s="20" t="inlineStr">
         <is>
-          <t>AGROXILATO-ZN 16%,  5 KG (EXPORT)</t>
+          <t>CODIORGAN  A-50</t>
         </is>
       </c>
       <c r="D89" s="21" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E89" s="20" t="inlineStr">
         <is>
-          <t>Bolsas 5 Kg</t>
+          <t>Bolsas 20 Kg</t>
         </is>
       </c>
       <c r="F89" s="22" t="inlineStr">
         <is>
-          <t>COSTA RICA</t>
-        </is>
-      </c>
-      <c r="G89" s="23" t="inlineStr">
-        <is>
-          <t>Sobre Pedido (Export)</t>
+          <t>ESPAÑA</t>
+        </is>
+      </c>
+      <c r="G89" s="22" t="inlineStr">
+        <is>
+          <t>Para Previsión (Nac)</t>
         </is>
       </c>
       <c r="H89" s="24" t="n">
         <v>0</v>
       </c>
       <c r="I89" s="24" t="n">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="J89" s="24" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="K89" s="24" t="n">
         <v>0</v>
       </c>
       <c r="L89" s="24" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="M89" s="25" t="n">
         <v>1500</v>
@@ -6464,32 +6464,32 @@
       </c>
       <c r="Q89" s="26" t="inlineStr">
         <is>
-          <t>SOBRE PEDIDO (EXP)</t>
+          <t>FABRICACIÓN URGENTE</t>
         </is>
       </c>
     </row>
     <row r="90" ht="19" customHeight="1">
       <c r="A90" s="27" t="inlineStr">
         <is>
-          <t>G1000CRCO</t>
-        </is>
-      </c>
-      <c r="B90" s="31" t="inlineStr">
-        <is>
-          <t>G1000CRCO</t>
+          <t>AGZN0005</t>
+        </is>
+      </c>
+      <c r="B90" s="28" t="inlineStr">
+        <is>
+          <t>AGZN0005CR</t>
         </is>
       </c>
       <c r="C90" s="29" t="inlineStr">
         <is>
-          <t>TRANSLOCADOR</t>
+          <t>AGROXILATO-ZN 16%,  5 KG (EXPORT)</t>
         </is>
       </c>
       <c r="D90" s="30" t="n">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="E90" s="29" t="inlineStr">
         <is>
-          <t>Depósito 1000 L</t>
+          <t>Bolsas 5 Kg</t>
         </is>
       </c>
       <c r="F90" s="31" t="inlineStr">
@@ -6538,218 +6538,218 @@
     <row r="91" ht="19" customHeight="1">
       <c r="A91" s="18" t="inlineStr">
         <is>
-          <t>AVAN0005</t>
+          <t>G1000CRCO</t>
         </is>
       </c>
       <c r="B91" s="22" t="inlineStr">
         <is>
-          <t>AVAN0005</t>
+          <t>G1000CRCO</t>
         </is>
       </c>
       <c r="C91" s="20" t="inlineStr">
         <is>
-          <t>FLORAMEC AVANCE, 5 L</t>
+          <t>TRANSLOCADOR</t>
         </is>
       </c>
       <c r="D91" s="21" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="E91" s="20" t="inlineStr">
         <is>
-          <t>Garrafas 5L</t>
+          <t>Depósito 1000 L</t>
         </is>
       </c>
       <c r="F91" s="22" t="inlineStr">
         <is>
-          <t>ESPAÑA</t>
-        </is>
-      </c>
-      <c r="G91" s="22" t="inlineStr">
-        <is>
-          <t>Para Previsión (Nac)</t>
+          <t>COSTA RICA</t>
+        </is>
+      </c>
+      <c r="G91" s="23" t="inlineStr">
+        <is>
+          <t>Sobre Pedido (Export)</t>
         </is>
       </c>
       <c r="H91" s="24" t="n">
-        <v>2640</v>
+        <v>0</v>
       </c>
       <c r="I91" s="24" t="n">
         <v>0</v>
       </c>
       <c r="J91" s="24" t="n">
-        <v>2200</v>
+        <v>1000</v>
       </c>
       <c r="K91" s="24" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="L91" s="24" t="n">
+        <v>500</v>
+      </c>
+      <c r="M91" s="25" t="n">
         <v>1500</v>
       </c>
-      <c r="M91" s="25" t="n">
-        <v>4100</v>
-      </c>
       <c r="N91" s="25" t="n">
-        <v>4100</v>
+        <v>1500</v>
       </c>
       <c r="O91" s="25" t="n">
-        <v>1460</v>
+        <v>1500</v>
       </c>
       <c r="P91" s="25" t="n">
-        <v>1460</v>
+        <v>1500</v>
       </c>
       <c r="Q91" s="26" t="inlineStr">
         <is>
-          <t>FABRICACIÓN URGENTE</t>
+          <t>SOBRE PEDIDO (EXP)</t>
         </is>
       </c>
     </row>
     <row r="92" ht="19" customHeight="1">
       <c r="A92" s="27" t="inlineStr">
         <is>
-          <t>SS0001</t>
-        </is>
-      </c>
-      <c r="B92" s="28" t="inlineStr">
-        <is>
-          <t>SS0001CR</t>
+          <t>AVAN0005</t>
+        </is>
+      </c>
+      <c r="B92" s="31" t="inlineStr">
+        <is>
+          <t>AVAN0005</t>
         </is>
       </c>
       <c r="C92" s="29" t="inlineStr">
         <is>
-          <t>SAL-WAX Ca</t>
+          <t>FLORAMEC AVANCE, 5 L</t>
         </is>
       </c>
       <c r="D92" s="30" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E92" s="29" t="inlineStr">
         <is>
-          <t>Bolsas 1 Kg</t>
+          <t>Garrafas 5L</t>
         </is>
       </c>
       <c r="F92" s="31" t="inlineStr">
         <is>
-          <t>COSTA RICA</t>
-        </is>
-      </c>
-      <c r="G92" s="32" t="inlineStr">
-        <is>
-          <t>Sobre Pedido (Export)</t>
+          <t>ESPAÑA</t>
+        </is>
+      </c>
+      <c r="G92" s="31" t="inlineStr">
+        <is>
+          <t>Para Previsión (Nac)</t>
         </is>
       </c>
       <c r="H92" s="33" t="n">
-        <v>0</v>
+        <v>2640</v>
       </c>
       <c r="I92" s="33" t="n">
         <v>0</v>
       </c>
       <c r="J92" s="33" t="n">
-        <v>1056</v>
+        <v>2200</v>
       </c>
       <c r="K92" s="33" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="L92" s="33" t="n">
-        <v>400</v>
+        <v>1500</v>
       </c>
       <c r="M92" s="34" t="n">
-        <v>1456</v>
+        <v>4100</v>
       </c>
       <c r="N92" s="34" t="n">
-        <v>1456</v>
+        <v>4100</v>
       </c>
       <c r="O92" s="34" t="n">
-        <v>1456</v>
+        <v>1460</v>
       </c>
       <c r="P92" s="34" t="n">
-        <v>1456</v>
+        <v>1460</v>
       </c>
       <c r="Q92" s="26" t="inlineStr">
         <is>
-          <t>SOBRE PEDIDO (EXP)</t>
+          <t>FABRICACIÓN URGENTE</t>
         </is>
       </c>
     </row>
     <row r="93" ht="19" customHeight="1">
       <c r="A93" s="18" t="inlineStr">
         <is>
-          <t>JF0020</t>
-        </is>
-      </c>
-      <c r="B93" s="22" t="inlineStr">
-        <is>
-          <t>JF0020</t>
+          <t>SS0001</t>
+        </is>
+      </c>
+      <c r="B93" s="19" t="inlineStr">
+        <is>
+          <t>SS0001CR</t>
         </is>
       </c>
       <c r="C93" s="20" t="inlineStr">
         <is>
-          <t>DRAGO-FOS, 20 L</t>
+          <t>SAL-WAX Ca</t>
         </is>
       </c>
       <c r="D93" s="21" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="E93" s="20" t="inlineStr">
         <is>
-          <t>Garrafas 20L</t>
+          <t>Bolsas 1 Kg</t>
         </is>
       </c>
       <c r="F93" s="22" t="inlineStr">
         <is>
-          <t>ESPAÑA</t>
-        </is>
-      </c>
-      <c r="G93" s="22" t="inlineStr">
-        <is>
-          <t>Para Previsión (Nac)</t>
+          <t>COSTA RICA</t>
+        </is>
+      </c>
+      <c r="G93" s="23" t="inlineStr">
+        <is>
+          <t>Sobre Pedido (Export)</t>
         </is>
       </c>
       <c r="H93" s="24" t="n">
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="I93" s="24" t="n">
         <v>0</v>
       </c>
       <c r="J93" s="24" t="n">
-        <v>0</v>
+        <v>1056</v>
       </c>
       <c r="K93" s="24" t="n">
-        <v>2560</v>
+        <v>0</v>
       </c>
       <c r="L93" s="24" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="M93" s="25" t="n">
-        <v>2560</v>
+        <v>1456</v>
       </c>
       <c r="N93" s="25" t="n">
-        <v>2560</v>
+        <v>1456</v>
       </c>
       <c r="O93" s="25" t="n">
-        <v>1360</v>
+        <v>1456</v>
       </c>
       <c r="P93" s="25" t="n">
-        <v>1360</v>
+        <v>1456</v>
       </c>
       <c r="Q93" s="26" t="inlineStr">
         <is>
-          <t>FABRICACIÓN URGENTE</t>
+          <t>SOBRE PEDIDO (EXP)</t>
         </is>
       </c>
     </row>
     <row r="94" ht="19" customHeight="1">
       <c r="A94" s="27" t="inlineStr">
         <is>
-          <t>PHD0020</t>
+          <t>JF0020</t>
         </is>
       </c>
       <c r="B94" s="31" t="inlineStr">
         <is>
-          <t>PHD0020</t>
+          <t>JF0020</t>
         </is>
       </c>
       <c r="C94" s="29" t="inlineStr">
         <is>
-          <t>PH-DOWNER</t>
+          <t>DRAGO-FOS, 20 L</t>
         </is>
       </c>
       <c r="D94" s="30" t="n">
@@ -6771,31 +6771,31 @@
         </is>
       </c>
       <c r="H94" s="33" t="n">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="I94" s="33" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="J94" s="33" t="n">
         <v>0</v>
       </c>
       <c r="K94" s="33" t="n">
-        <v>0</v>
+        <v>2560</v>
       </c>
       <c r="L94" s="33" t="n">
-        <v>640</v>
+        <v>0</v>
       </c>
       <c r="M94" s="34" t="n">
-        <v>1240</v>
+        <v>2560</v>
       </c>
       <c r="N94" s="34" t="n">
-        <v>1240</v>
+        <v>2560</v>
       </c>
       <c r="O94" s="34" t="n">
-        <v>1240</v>
+        <v>1360</v>
       </c>
       <c r="P94" s="34" t="n">
-        <v>1240</v>
+        <v>1360</v>
       </c>
       <c r="Q94" s="26" t="inlineStr">
         <is>
@@ -6806,17 +6806,17 @@
     <row r="95" ht="19" customHeight="1">
       <c r="A95" s="18" t="inlineStr">
         <is>
-          <t>SSEG0020</t>
+          <t>PHD0020</t>
         </is>
       </c>
       <c r="B95" s="22" t="inlineStr">
         <is>
-          <t>SSEG0020</t>
+          <t>PHD0020</t>
         </is>
       </c>
       <c r="C95" s="20" t="inlineStr">
         <is>
-          <t>SAL-WAX Ca</t>
+          <t>PH-DOWNER</t>
         </is>
       </c>
       <c r="D95" s="21" t="n">
@@ -6824,24 +6824,24 @@
       </c>
       <c r="E95" s="20" t="inlineStr">
         <is>
-          <t>Bolsas 20 Kg</t>
+          <t>Garrafas 20L</t>
         </is>
       </c>
       <c r="F95" s="22" t="inlineStr">
         <is>
-          <t>EXPORT</t>
-        </is>
-      </c>
-      <c r="G95" s="23" t="inlineStr">
-        <is>
-          <t>Sobre Pedido (Export)</t>
+          <t>ESPAÑA</t>
+        </is>
+      </c>
+      <c r="G95" s="22" t="inlineStr">
+        <is>
+          <t>Para Previsión (Nac)</t>
         </is>
       </c>
       <c r="H95" s="24" t="n">
         <v>0</v>
       </c>
       <c r="I95" s="24" t="n">
-        <v>1200</v>
+        <v>600</v>
       </c>
       <c r="J95" s="24" t="n">
         <v>0</v>
@@ -6850,40 +6850,40 @@
         <v>0</v>
       </c>
       <c r="L95" s="24" t="n">
-        <v>0</v>
+        <v>640</v>
       </c>
       <c r="M95" s="25" t="n">
-        <v>1200</v>
+        <v>1240</v>
       </c>
       <c r="N95" s="25" t="n">
-        <v>1200</v>
+        <v>1240</v>
       </c>
       <c r="O95" s="25" t="n">
-        <v>1200</v>
+        <v>1240</v>
       </c>
       <c r="P95" s="25" t="n">
-        <v>1200</v>
+        <v>1240</v>
       </c>
       <c r="Q95" s="26" t="inlineStr">
         <is>
-          <t>SOBRE PEDIDO (EXP)</t>
+          <t>FABRICACIÓN URGENTE</t>
         </is>
       </c>
     </row>
     <row r="96" ht="19" customHeight="1">
       <c r="A96" s="27" t="inlineStr">
         <is>
-          <t>AN0020</t>
-        </is>
-      </c>
-      <c r="B96" s="28" t="inlineStr">
-        <is>
-          <t>AN0020RO</t>
+          <t>SSEG0020</t>
+        </is>
+      </c>
+      <c r="B96" s="31" t="inlineStr">
+        <is>
+          <t>SSEG0020</t>
         </is>
       </c>
       <c r="C96" s="29" t="inlineStr">
         <is>
-          <t>ALCAPLANT NEW, 20 KG</t>
+          <t>SAL-WAX Ca</t>
         </is>
       </c>
       <c r="D96" s="30" t="n">
@@ -6896,7 +6896,7 @@
       </c>
       <c r="F96" s="31" t="inlineStr">
         <is>
-          <t>RUMANÍA</t>
+          <t>EXPORT</t>
         </is>
       </c>
       <c r="G96" s="32" t="inlineStr">
@@ -6908,28 +6908,28 @@
         <v>0</v>
       </c>
       <c r="I96" s="33" t="n">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="J96" s="33" t="n">
         <v>0</v>
       </c>
       <c r="K96" s="33" t="n">
-        <v>1100</v>
+        <v>0</v>
       </c>
       <c r="L96" s="33" t="n">
         <v>0</v>
       </c>
       <c r="M96" s="34" t="n">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="N96" s="34" t="n">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="O96" s="34" t="n">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="P96" s="34" t="n">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="Q96" s="26" t="inlineStr">
         <is>
@@ -6945,7 +6945,7 @@
       </c>
       <c r="B97" s="19" t="inlineStr">
         <is>
-          <t>AN0020PE</t>
+          <t>AN0020RO</t>
         </is>
       </c>
       <c r="C97" s="20" t="inlineStr">
@@ -6963,7 +6963,7 @@
       </c>
       <c r="F97" s="22" t="inlineStr">
         <is>
-          <t>PERÚ</t>
+          <t>RUMANÍA</t>
         </is>
       </c>
       <c r="G97" s="23" t="inlineStr">
@@ -6975,13 +6975,13 @@
         <v>0</v>
       </c>
       <c r="I97" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K97" s="24" t="n">
         <v>1100</v>
-      </c>
-      <c r="J97" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K97" s="24" t="n">
-        <v>0</v>
       </c>
       <c r="L97" s="24" t="n">
         <v>0</v>
@@ -7007,30 +7007,30 @@
     <row r="98" ht="19" customHeight="1">
       <c r="A98" s="27" t="inlineStr">
         <is>
-          <t>A-500001</t>
+          <t>AN0020</t>
         </is>
       </c>
       <c r="B98" s="28" t="inlineStr">
         <is>
-          <t>A-500001RO</t>
+          <t>AN0020PE</t>
         </is>
       </c>
       <c r="C98" s="29" t="inlineStr">
         <is>
-          <t>CODIORGAN-A50, 1 KG</t>
+          <t>ALCAPLANT NEW, 20 KG</t>
         </is>
       </c>
       <c r="D98" s="30" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E98" s="29" t="inlineStr">
         <is>
-          <t>Bolsas 1 Kg</t>
+          <t>Bolsas 20 Kg</t>
         </is>
       </c>
       <c r="F98" s="31" t="inlineStr">
         <is>
-          <t>RUMANÍA</t>
+          <t>PERÚ</t>
         </is>
       </c>
       <c r="G98" s="32" t="inlineStr">
@@ -7042,10 +7042,10 @@
         <v>0</v>
       </c>
       <c r="I98" s="33" t="n">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="J98" s="33" t="n">
-        <v>1056</v>
+        <v>0</v>
       </c>
       <c r="K98" s="33" t="n">
         <v>0</v>
@@ -7054,16 +7054,16 @@
         <v>0</v>
       </c>
       <c r="M98" s="34" t="n">
-        <v>1056</v>
+        <v>1100</v>
       </c>
       <c r="N98" s="34" t="n">
-        <v>1056</v>
+        <v>1100</v>
       </c>
       <c r="O98" s="34" t="n">
-        <v>1056</v>
+        <v>1100</v>
       </c>
       <c r="P98" s="34" t="n">
-        <v>1056</v>
+        <v>1100</v>
       </c>
       <c r="Q98" s="26" t="inlineStr">
         <is>
@@ -7074,17 +7074,17 @@
     <row r="99" ht="19" customHeight="1">
       <c r="A99" s="18" t="inlineStr">
         <is>
-          <t>SS0001</t>
+          <t>A-500001</t>
         </is>
       </c>
       <c r="B99" s="19" t="inlineStr">
         <is>
-          <t>SS0001RO</t>
+          <t>A-500001RO</t>
         </is>
       </c>
       <c r="C99" s="20" t="inlineStr">
         <is>
-          <t>SAL-WAX Ca</t>
+          <t>CODIORGAN-A50, 1 KG</t>
         </is>
       </c>
       <c r="D99" s="21" t="n">
@@ -7141,17 +7141,17 @@
     <row r="100" ht="19" customHeight="1">
       <c r="A100" s="27" t="inlineStr">
         <is>
-          <t>AGZN0001</t>
+          <t>SS0001</t>
         </is>
       </c>
       <c r="B100" s="28" t="inlineStr">
         <is>
-          <t>AGZN0001CR</t>
+          <t>SS0001RO</t>
         </is>
       </c>
       <c r="C100" s="29" t="inlineStr">
         <is>
-          <t>AGROXILATO Zn</t>
+          <t>SAL-WAX Ca</t>
         </is>
       </c>
       <c r="D100" s="30" t="n">
@@ -7164,7 +7164,7 @@
       </c>
       <c r="F100" s="31" t="inlineStr">
         <is>
-          <t>COSTA RICA</t>
+          <t>RUMANÍA</t>
         </is>
       </c>
       <c r="G100" s="32" t="inlineStr">
@@ -7179,10 +7179,10 @@
         <v>0</v>
       </c>
       <c r="J100" s="33" t="n">
-        <v>0</v>
+        <v>1056</v>
       </c>
       <c r="K100" s="33" t="n">
-        <v>1056</v>
+        <v>0</v>
       </c>
       <c r="L100" s="33" t="n">
         <v>0</v>
@@ -7208,30 +7208,30 @@
     <row r="101" ht="19" customHeight="1">
       <c r="A101" s="18" t="inlineStr">
         <is>
-          <t>JF0005</t>
+          <t>AGZN0001</t>
         </is>
       </c>
       <c r="B101" s="19" t="inlineStr">
         <is>
-          <t>JF0005MA</t>
+          <t>AGZN0001CR</t>
         </is>
       </c>
       <c r="C101" s="20" t="inlineStr">
         <is>
-          <t>CODIGIN-FOS, 5 L</t>
+          <t>AGROXILATO Zn</t>
         </is>
       </c>
       <c r="D101" s="21" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E101" s="20" t="inlineStr">
         <is>
-          <t>Garrafas 5L</t>
+          <t>Bolsas 1 Kg</t>
         </is>
       </c>
       <c r="F101" s="22" t="inlineStr">
         <is>
-          <t>MARRUECOS</t>
+          <t>COSTA RICA</t>
         </is>
       </c>
       <c r="G101" s="23" t="inlineStr">
@@ -7249,22 +7249,22 @@
         <v>0</v>
       </c>
       <c r="K101" s="24" t="n">
-        <v>0</v>
+        <v>1056</v>
       </c>
       <c r="L101" s="24" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="M101" s="25" t="n">
-        <v>1000</v>
+        <v>1056</v>
       </c>
       <c r="N101" s="25" t="n">
-        <v>1000</v>
+        <v>1056</v>
       </c>
       <c r="O101" s="25" t="n">
-        <v>1000</v>
+        <v>1056</v>
       </c>
       <c r="P101" s="25" t="n">
-        <v>1000</v>
+        <v>1056</v>
       </c>
       <c r="Q101" s="26" t="inlineStr">
         <is>
@@ -7275,17 +7275,17 @@
     <row r="102" ht="19" customHeight="1">
       <c r="A102" s="27" t="inlineStr">
         <is>
-          <t>CZNMNES0005</t>
+          <t>JF0005</t>
         </is>
       </c>
       <c r="B102" s="28" t="inlineStr">
         <is>
-          <t>CZNMNES0005GE</t>
+          <t>JF0005MA</t>
         </is>
       </c>
       <c r="C102" s="29" t="inlineStr">
         <is>
-          <t>CODIFOL ZN-MN, 5 KG</t>
+          <t>CODIGIN-FOS, 5 L</t>
         </is>
       </c>
       <c r="D102" s="30" t="n">
@@ -7293,12 +7293,12 @@
       </c>
       <c r="E102" s="29" t="inlineStr">
         <is>
-          <t>Bolsas 5 Kg</t>
+          <t>Garrafas 5L</t>
         </is>
       </c>
       <c r="F102" s="31" t="inlineStr">
         <is>
-          <t>GEORGIA</t>
+          <t>MARRUECOS</t>
         </is>
       </c>
       <c r="G102" s="32" t="inlineStr">
@@ -7342,17 +7342,17 @@
     <row r="103" ht="19" customHeight="1">
       <c r="A103" s="18" t="inlineStr">
         <is>
-          <t>CALCIO0005</t>
+          <t>CZNMNES0005</t>
         </is>
       </c>
       <c r="B103" s="19" t="inlineStr">
         <is>
-          <t>CALCIO0005MA</t>
+          <t>CZNMNES0005GE</t>
         </is>
       </c>
       <c r="C103" s="20" t="inlineStr">
         <is>
-          <t>CALCIAMEC, 5 KG</t>
+          <t>CODIFOL ZN-MN, 5 KG</t>
         </is>
       </c>
       <c r="D103" s="21" t="n">
@@ -7365,7 +7365,7 @@
       </c>
       <c r="F103" s="22" t="inlineStr">
         <is>
-          <t>MARRUECOS</t>
+          <t>GEORGIA</t>
         </is>
       </c>
       <c r="G103" s="23" t="inlineStr">
@@ -7409,17 +7409,17 @@
     <row r="104" ht="19" customHeight="1">
       <c r="A104" s="27" t="inlineStr">
         <is>
-          <t>AGMG0005</t>
+          <t>CALCIO0005</t>
         </is>
       </c>
       <c r="B104" s="28" t="inlineStr">
         <is>
-          <t>AGMG0005CR</t>
+          <t>CALCIO0005MA</t>
         </is>
       </c>
       <c r="C104" s="29" t="inlineStr">
         <is>
-          <t>AGROXILATO-MG, 5 KG (EXPORT)</t>
+          <t>CALCIAMEC, 5 KG</t>
         </is>
       </c>
       <c r="D104" s="30" t="n">
@@ -7432,7 +7432,7 @@
       </c>
       <c r="F104" s="31" t="inlineStr">
         <is>
-          <t>COSTA RICA</t>
+          <t>MARRUECOS</t>
         </is>
       </c>
       <c r="G104" s="32" t="inlineStr">
@@ -7447,13 +7447,13 @@
         <v>0</v>
       </c>
       <c r="J104" s="33" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="K104" s="33" t="n">
         <v>0</v>
       </c>
       <c r="L104" s="33" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="M104" s="34" t="n">
         <v>1000</v>
@@ -7476,17 +7476,17 @@
     <row r="105" ht="19" customHeight="1">
       <c r="A105" s="18" t="inlineStr">
         <is>
-          <t>BPLUS0005</t>
+          <t>AGMG0005</t>
         </is>
       </c>
       <c r="B105" s="19" t="inlineStr">
         <is>
-          <t>BPLUS0005LB</t>
+          <t>AGMG0005CR</t>
         </is>
       </c>
       <c r="C105" s="20" t="inlineStr">
         <is>
-          <t>BOROCAL PLUS, 5 KG</t>
+          <t>AGROXILATO-MG, 5 KG (EXPORT)</t>
         </is>
       </c>
       <c r="D105" s="21" t="n">
@@ -7499,7 +7499,7 @@
       </c>
       <c r="F105" s="22" t="inlineStr">
         <is>
-          <t>LÍBANO</t>
+          <t>COSTA RICA</t>
         </is>
       </c>
       <c r="G105" s="23" t="inlineStr">
@@ -7514,13 +7514,13 @@
         <v>0</v>
       </c>
       <c r="J105" s="24" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="K105" s="24" t="n">
         <v>0</v>
       </c>
       <c r="L105" s="24" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="M105" s="25" t="n">
         <v>1000</v>
@@ -7543,30 +7543,30 @@
     <row r="106" ht="19" customHeight="1">
       <c r="A106" s="27" t="inlineStr">
         <is>
-          <t>F-MIX0020</t>
+          <t>BPLUS0005</t>
         </is>
       </c>
       <c r="B106" s="28" t="inlineStr">
         <is>
-          <t>F-MIX0020MA</t>
+          <t>BPLUS0005LB</t>
         </is>
       </c>
       <c r="C106" s="29" t="inlineStr">
         <is>
-          <t>FITOLIN-MIX, 20 L</t>
+          <t>BOROCAL PLUS, 5 KG</t>
         </is>
       </c>
       <c r="D106" s="30" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E106" s="29" t="inlineStr">
         <is>
-          <t>Garrafas 20L</t>
+          <t>Bolsas 5 Kg</t>
         </is>
       </c>
       <c r="F106" s="31" t="inlineStr">
         <is>
-          <t>MARRUECOS</t>
+          <t>LÍBANO</t>
         </is>
       </c>
       <c r="G106" s="32" t="inlineStr">
@@ -7584,10 +7584,10 @@
         <v>0</v>
       </c>
       <c r="K106" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L106" s="33" t="n">
         <v>1000</v>
-      </c>
-      <c r="L106" s="33" t="n">
-        <v>0</v>
       </c>
       <c r="M106" s="34" t="n">
         <v>1000</v>
@@ -7610,17 +7610,17 @@
     <row r="107" ht="19" customHeight="1">
       <c r="A107" s="18" t="inlineStr">
         <is>
-          <t>A-500020</t>
+          <t>F-MIX0020</t>
         </is>
       </c>
       <c r="B107" s="19" t="inlineStr">
         <is>
-          <t>A-500020CR</t>
+          <t>F-MIX0020MA</t>
         </is>
       </c>
       <c r="C107" s="20" t="inlineStr">
         <is>
-          <t>CODIORGAN  A-50</t>
+          <t>FITOLIN-MIX, 20 L</t>
         </is>
       </c>
       <c r="D107" s="21" t="n">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="E107" s="20" t="inlineStr">
         <is>
-          <t>Bolsas 20 Kg</t>
+          <t>Garrafas 20L</t>
         </is>
       </c>
       <c r="F107" s="22" t="inlineStr">
         <is>
-          <t>COSTA RICA</t>
+          <t>MARRUECOS</t>
         </is>
       </c>
       <c r="G107" s="23" t="inlineStr">
@@ -7677,48 +7677,48 @@
     <row r="108" ht="19" customHeight="1">
       <c r="A108" s="27" t="inlineStr">
         <is>
-          <t>JF1000</t>
-        </is>
-      </c>
-      <c r="B108" s="31" t="inlineStr">
-        <is>
-          <t>JF1000</t>
+          <t>A-500020</t>
+        </is>
+      </c>
+      <c r="B108" s="28" t="inlineStr">
+        <is>
+          <t>A-500020CR</t>
         </is>
       </c>
       <c r="C108" s="29" t="inlineStr">
         <is>
-          <t>CODIGIN-FOS, 1000 L</t>
+          <t>CODIORGAN  A-50</t>
         </is>
       </c>
       <c r="D108" s="30" t="n">
+        <v>20</v>
+      </c>
+      <c r="E108" s="29" t="inlineStr">
+        <is>
+          <t>Bolsas 20 Kg</t>
+        </is>
+      </c>
+      <c r="F108" s="31" t="inlineStr">
+        <is>
+          <t>COSTA RICA</t>
+        </is>
+      </c>
+      <c r="G108" s="32" t="inlineStr">
+        <is>
+          <t>Sobre Pedido (Export)</t>
+        </is>
+      </c>
+      <c r="H108" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I108" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J108" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K108" s="33" t="n">
         <v>1000</v>
-      </c>
-      <c r="E108" s="29" t="inlineStr">
-        <is>
-          <t>Depósito 1000 L</t>
-        </is>
-      </c>
-      <c r="F108" s="31" t="inlineStr">
-        <is>
-          <t>ESPAÑA</t>
-        </is>
-      </c>
-      <c r="G108" s="31" t="inlineStr">
-        <is>
-          <t>Para Previsión (Nac)</t>
-        </is>
-      </c>
-      <c r="H108" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="I108" s="33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J108" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="K108" s="33" t="n">
-        <v>0</v>
       </c>
       <c r="L108" s="33" t="n">
         <v>0</v>
@@ -7737,49 +7737,49 @@
       </c>
       <c r="Q108" s="26" t="inlineStr">
         <is>
-          <t>FABRICACIÓN URGENTE</t>
+          <t>SOBRE PEDIDO (EXP)</t>
         </is>
       </c>
     </row>
     <row r="109" ht="19" customHeight="1">
       <c r="A109" s="18" t="inlineStr">
         <is>
-          <t>A-500005</t>
-        </is>
-      </c>
-      <c r="B109" s="19" t="inlineStr">
-        <is>
-          <t>A-500005GE</t>
+          <t>JF1000</t>
+        </is>
+      </c>
+      <c r="B109" s="22" t="inlineStr">
+        <is>
+          <t>JF1000</t>
         </is>
       </c>
       <c r="C109" s="20" t="inlineStr">
         <is>
-          <t>CODIORGAN  A-50</t>
+          <t>CODIGIN-FOS, 1000 L</t>
         </is>
       </c>
       <c r="D109" s="21" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="E109" s="20" t="inlineStr">
         <is>
-          <t>Bolsas 5 Kg</t>
+          <t>Depósito 1000 L</t>
         </is>
       </c>
       <c r="F109" s="22" t="inlineStr">
         <is>
-          <t>GEORGIA</t>
-        </is>
-      </c>
-      <c r="G109" s="23" t="inlineStr">
-        <is>
-          <t>Sobre Pedido (Export)</t>
+          <t>ESPAÑA</t>
+        </is>
+      </c>
+      <c r="G109" s="22" t="inlineStr">
+        <is>
+          <t>Para Previsión (Nac)</t>
         </is>
       </c>
       <c r="H109" s="24" t="n">
         <v>0</v>
       </c>
       <c r="I109" s="24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J109" s="24" t="n">
         <v>0</v>
@@ -7788,7 +7788,7 @@
         <v>0</v>
       </c>
       <c r="L109" s="24" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="M109" s="25" t="n">
         <v>1000</v>
@@ -7804,37 +7804,37 @@
       </c>
       <c r="Q109" s="26" t="inlineStr">
         <is>
-          <t>SOBRE PEDIDO (EXP)</t>
+          <t>FABRICACIÓN URGENTE</t>
         </is>
       </c>
     </row>
     <row r="110" ht="19" customHeight="1">
       <c r="A110" s="27" t="inlineStr">
         <is>
-          <t>CZNMNES0001</t>
+          <t>A-500005</t>
         </is>
       </c>
       <c r="B110" s="28" t="inlineStr">
         <is>
-          <t>CZNMNES0001AZ</t>
+          <t>A-500005GE</t>
         </is>
       </c>
       <c r="C110" s="29" t="inlineStr">
         <is>
-          <t>CODIFOL ZN-MN, 1 KG</t>
+          <t>CODIORGAN  A-50</t>
         </is>
       </c>
       <c r="D110" s="30" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E110" s="29" t="inlineStr">
         <is>
-          <t>Bolsas 1 Kg</t>
+          <t>Bolsas 5 Kg</t>
         </is>
       </c>
       <c r="F110" s="31" t="inlineStr">
         <is>
-          <t>AZERBAIYÁN</t>
+          <t>GEORGIA</t>
         </is>
       </c>
       <c r="G110" s="32" t="inlineStr">
@@ -7883,7 +7883,7 @@
       </c>
       <c r="B111" s="19" t="inlineStr">
         <is>
-          <t>CZNMNES0001GE</t>
+          <t>CZNMNES0001AZ</t>
         </is>
       </c>
       <c r="C111" s="20" t="inlineStr">
@@ -7901,7 +7901,7 @@
       </c>
       <c r="F111" s="22" t="inlineStr">
         <is>
-          <t>GEORGIA</t>
+          <t>AZERBAIYÁN</t>
         </is>
       </c>
       <c r="G111" s="23" t="inlineStr">
@@ -7945,25 +7945,25 @@
     <row r="112" ht="19" customHeight="1">
       <c r="A112" s="27" t="inlineStr">
         <is>
-          <t>CM30005</t>
+          <t>CZNMNES0001</t>
         </is>
       </c>
       <c r="B112" s="28" t="inlineStr">
         <is>
-          <t>CM30005GE</t>
+          <t>CZNMNES0001GE</t>
         </is>
       </c>
       <c r="C112" s="29" t="inlineStr">
         <is>
-          <t>TENSOLINE, 5 L</t>
+          <t>CODIFOL ZN-MN, 1 KG</t>
         </is>
       </c>
       <c r="D112" s="30" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E112" s="29" t="inlineStr">
         <is>
-          <t>Garrafas 5L</t>
+          <t>Bolsas 1 Kg</t>
         </is>
       </c>
       <c r="F112" s="31" t="inlineStr">
@@ -8012,17 +8012,17 @@
     <row r="113" ht="19" customHeight="1">
       <c r="A113" s="18" t="inlineStr">
         <is>
-          <t>CZNMNES0005</t>
+          <t>CM30005</t>
         </is>
       </c>
       <c r="B113" s="19" t="inlineStr">
         <is>
-          <t>CZNMNES0005AZ</t>
+          <t>CM30005GE</t>
         </is>
       </c>
       <c r="C113" s="20" t="inlineStr">
         <is>
-          <t>CODIFOL ZN-MN, 5 KG</t>
+          <t>TENSOLINE, 5 L</t>
         </is>
       </c>
       <c r="D113" s="21" t="n">
@@ -8030,12 +8030,12 @@
       </c>
       <c r="E113" s="20" t="inlineStr">
         <is>
-          <t>Bolsas 5 Kg</t>
+          <t>Garrafas 5L</t>
         </is>
       </c>
       <c r="F113" s="22" t="inlineStr">
         <is>
-          <t>AZERBAIYÁN</t>
+          <t>GEORGIA</t>
         </is>
       </c>
       <c r="G113" s="23" t="inlineStr">
@@ -8044,7 +8044,7 @@
         </is>
       </c>
       <c r="H113" s="24" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I113" s="24" t="n">
         <v>0</v>
@@ -8065,10 +8065,10 @@
         <v>1000</v>
       </c>
       <c r="O113" s="25" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="P113" s="25" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="Q113" s="26" t="inlineStr">
         <is>
@@ -8079,67 +8079,67 @@
     <row r="114" ht="19" customHeight="1">
       <c r="A114" s="27" t="inlineStr">
         <is>
-          <t>AN0020</t>
-        </is>
-      </c>
-      <c r="B114" s="31" t="inlineStr">
-        <is>
-          <t>AN0020</t>
+          <t>CZNMNES0005</t>
+        </is>
+      </c>
+      <c r="B114" s="28" t="inlineStr">
+        <is>
+          <t>CZNMNES0005AZ</t>
         </is>
       </c>
       <c r="C114" s="29" t="inlineStr">
         <is>
-          <t>ALCAPLANT NEW, 20 KG</t>
+          <t>CODIFOL ZN-MN, 5 KG</t>
         </is>
       </c>
       <c r="D114" s="30" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E114" s="29" t="inlineStr">
         <is>
-          <t>Bolsas 20 Kg</t>
+          <t>Bolsas 5 Kg</t>
         </is>
       </c>
       <c r="F114" s="31" t="inlineStr">
         <is>
-          <t>ESPAÑA</t>
-        </is>
-      </c>
-      <c r="G114" s="31" t="inlineStr">
-        <is>
-          <t>Para Previsión (Nac)</t>
+          <t>AZERBAIYÁN</t>
+        </is>
+      </c>
+      <c r="G114" s="32" t="inlineStr">
+        <is>
+          <t>Sobre Pedido (Export)</t>
         </is>
       </c>
       <c r="H114" s="33" t="n">
-        <v>29200</v>
+        <v>50</v>
       </c>
       <c r="I114" s="33" t="n">
         <v>0</v>
       </c>
       <c r="J114" s="33" t="n">
-        <v>12000</v>
+        <v>0</v>
       </c>
       <c r="K114" s="33" t="n">
-        <v>17000</v>
+        <v>0</v>
       </c>
       <c r="L114" s="33" t="n">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="M114" s="34" t="n">
-        <v>30100</v>
+        <v>1000</v>
       </c>
       <c r="N114" s="34" t="n">
-        <v>30100</v>
+        <v>1000</v>
       </c>
       <c r="O114" s="34" t="n">
-        <v>900</v>
+        <v>950</v>
       </c>
       <c r="P114" s="34" t="n">
-        <v>900</v>
+        <v>950</v>
       </c>
       <c r="Q114" s="26" t="inlineStr">
         <is>
-          <t>FABRICACIÓN URGENTE</t>
+          <t>SOBRE PEDIDO (EXP)</t>
         </is>
       </c>
     </row>
@@ -11362,97 +11362,97 @@
     <row r="163" ht="19" customHeight="1">
       <c r="A163" s="18" t="inlineStr">
         <is>
-          <t>S0020</t>
-        </is>
-      </c>
-      <c r="B163" s="22" t="inlineStr">
-        <is>
-          <t>S0020</t>
+          <t>C-L0005</t>
+        </is>
+      </c>
+      <c r="B163" s="19" t="inlineStr">
+        <is>
+          <t>C-L0005AZ</t>
         </is>
       </c>
       <c r="C163" s="20" t="inlineStr">
         <is>
-          <t>SALWAX STAR, 20 L</t>
+          <t>CODIBOR-L, 5 L</t>
         </is>
       </c>
       <c r="D163" s="21" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E163" s="20" t="inlineStr">
         <is>
-          <t>Garrafas 20L</t>
+          <t>Garrafas 5L</t>
         </is>
       </c>
       <c r="F163" s="22" t="inlineStr">
         <is>
-          <t>ESPAÑA</t>
-        </is>
-      </c>
-      <c r="G163" s="22" t="inlineStr">
-        <is>
-          <t>Para Previsión (Nac)</t>
+          <t>AZERBAIYÁN</t>
+        </is>
+      </c>
+      <c r="G163" s="23" t="inlineStr">
+        <is>
+          <t>Sobre Pedido (Export)</t>
         </is>
       </c>
       <c r="H163" s="24" t="n">
-        <v>3160</v>
+        <v>340</v>
       </c>
       <c r="I163" s="24" t="n">
         <v>0</v>
       </c>
       <c r="J163" s="24" t="n">
-        <v>2560</v>
+        <v>0</v>
       </c>
       <c r="K163" s="24" t="n">
-        <v>3200</v>
+        <v>0</v>
       </c>
       <c r="L163" s="24" t="n">
-        <v>640</v>
+        <v>3000</v>
       </c>
       <c r="M163" s="25" t="n">
-        <v>6400</v>
+        <v>3000</v>
       </c>
       <c r="N163" s="25" t="n">
-        <v>6400</v>
+        <v>3000</v>
       </c>
       <c r="O163" s="25" t="n">
-        <v>3240</v>
+        <v>2660</v>
       </c>
       <c r="P163" s="25" t="n">
-        <v>3240</v>
+        <v>2660</v>
       </c>
       <c r="Q163" s="35" t="inlineStr">
         <is>
-          <t>SOLO ENVASAR</t>
+          <t>SOBRE PEDIDO (EXP)</t>
         </is>
       </c>
     </row>
     <row r="164" ht="19" customHeight="1">
       <c r="A164" s="27" t="inlineStr">
         <is>
-          <t>C-L0005</t>
+          <t>BIO0020</t>
         </is>
       </c>
       <c r="B164" s="28" t="inlineStr">
         <is>
-          <t>C-L0005AZ</t>
+          <t>BIO0020DO</t>
         </is>
       </c>
       <c r="C164" s="29" t="inlineStr">
         <is>
-          <t>CODIBOR-L, 5 L</t>
+          <t>BIORAD-20, 20 L</t>
         </is>
       </c>
       <c r="D164" s="30" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E164" s="29" t="inlineStr">
         <is>
-          <t>Garrafas 5L</t>
+          <t>Garrafas 20L</t>
         </is>
       </c>
       <c r="F164" s="31" t="inlineStr">
         <is>
-          <t>AZERBAIYÁN</t>
+          <t>DOMINICANA, REPÚBLICA</t>
         </is>
       </c>
       <c r="G164" s="32" t="inlineStr">
@@ -11461,7 +11461,7 @@
         </is>
       </c>
       <c r="H164" s="33" t="n">
-        <v>340</v>
+        <v>0</v>
       </c>
       <c r="I164" s="33" t="n">
         <v>0</v>
@@ -11470,22 +11470,22 @@
         <v>0</v>
       </c>
       <c r="K164" s="33" t="n">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="L164" s="33" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="M164" s="34" t="n">
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="N164" s="34" t="n">
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="O164" s="34" t="n">
-        <v>2660</v>
+        <v>2500</v>
       </c>
       <c r="P164" s="34" t="n">
-        <v>2660</v>
+        <v>2500</v>
       </c>
       <c r="Q164" s="35" t="inlineStr">
         <is>
@@ -11496,17 +11496,17 @@
     <row r="165" ht="19" customHeight="1">
       <c r="A165" s="18" t="inlineStr">
         <is>
-          <t>BIO0020</t>
+          <t>C-L0020</t>
         </is>
       </c>
       <c r="B165" s="19" t="inlineStr">
         <is>
-          <t>BIO0020DO</t>
+          <t>C-L0020AZ</t>
         </is>
       </c>
       <c r="C165" s="20" t="inlineStr">
         <is>
-          <t>BIORAD-20, 20 L</t>
+          <t>CODIBOR-L, 20 L</t>
         </is>
       </c>
       <c r="D165" s="21" t="n">
@@ -11519,7 +11519,7 @@
       </c>
       <c r="F165" s="22" t="inlineStr">
         <is>
-          <t>DOMINICANA, REPÚBLICA</t>
+          <t>AZERBAIYÁN</t>
         </is>
       </c>
       <c r="G165" s="23" t="inlineStr">
@@ -11537,22 +11537,22 @@
         <v>0</v>
       </c>
       <c r="K165" s="24" t="n">
-        <v>2500</v>
+        <v>0</v>
       </c>
       <c r="L165" s="24" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="M165" s="25" t="n">
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="N165" s="25" t="n">
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="O165" s="25" t="n">
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="P165" s="25" t="n">
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="Q165" s="35" t="inlineStr">
         <is>
@@ -11563,17 +11563,17 @@
     <row r="166" ht="19" customHeight="1">
       <c r="A166" s="27" t="inlineStr">
         <is>
-          <t>C-L0020</t>
+          <t>AGXCR0020</t>
         </is>
       </c>
       <c r="B166" s="28" t="inlineStr">
         <is>
-          <t>C-L0020AZ</t>
+          <t>AGXCR0020CO</t>
         </is>
       </c>
       <c r="C166" s="29" t="inlineStr">
         <is>
-          <t>CODIBOR-L, 20 L</t>
+          <t>AGROXILATO-K, (0-5-20), 20 LtS.</t>
         </is>
       </c>
       <c r="D166" s="30" t="n">
@@ -11586,7 +11586,7 @@
       </c>
       <c r="F166" s="31" t="inlineStr">
         <is>
-          <t>AZERBAIYÁN</t>
+          <t>COLOMBIA</t>
         </is>
       </c>
       <c r="G166" s="32" t="inlineStr">
@@ -11598,7 +11598,7 @@
         <v>0</v>
       </c>
       <c r="I166" s="33" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="J166" s="33" t="n">
         <v>0</v>
@@ -11607,7 +11607,7 @@
         <v>0</v>
       </c>
       <c r="L166" s="33" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="M166" s="34" t="n">
         <v>2000</v>
@@ -11630,30 +11630,30 @@
     <row r="167" ht="19" customHeight="1">
       <c r="A167" s="18" t="inlineStr">
         <is>
-          <t>AGXCR0020</t>
+          <t>F-A1000</t>
         </is>
       </c>
       <c r="B167" s="19" t="inlineStr">
         <is>
-          <t>AGXCR0020CO</t>
+          <t>F-A1000CR</t>
         </is>
       </c>
       <c r="C167" s="20" t="inlineStr">
         <is>
-          <t>AGROXILATO-K, (0-5-20), 20 LtS.</t>
+          <t>FITOLIN AGRO</t>
         </is>
       </c>
       <c r="D167" s="21" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="E167" s="20" t="inlineStr">
         <is>
-          <t>Garrafas 20L</t>
+          <t>Depósito 1000 L</t>
         </is>
       </c>
       <c r="F167" s="22" t="inlineStr">
         <is>
-          <t>COLOMBIA</t>
+          <t>COSTA RICA</t>
         </is>
       </c>
       <c r="G167" s="23" t="inlineStr">
@@ -11665,16 +11665,16 @@
         <v>0</v>
       </c>
       <c r="I167" s="24" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="J167" s="24" t="n">
         <v>0</v>
       </c>
       <c r="K167" s="24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="L167" s="24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="M167" s="25" t="n">
         <v>2000</v>
@@ -11697,30 +11697,30 @@
     <row r="168" ht="19" customHeight="1">
       <c r="A168" s="27" t="inlineStr">
         <is>
-          <t>F-A1000</t>
+          <t>AGXCR0001</t>
         </is>
       </c>
       <c r="B168" s="28" t="inlineStr">
         <is>
-          <t>F-A1000CR</t>
+          <t>AGXCR0001PA</t>
         </is>
       </c>
       <c r="C168" s="29" t="inlineStr">
         <is>
-          <t>FITOLIN AGRO</t>
+          <t>AGROXILATO-K</t>
         </is>
       </c>
       <c r="D168" s="30" t="n">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="E168" s="29" t="inlineStr">
         <is>
-          <t>Depósito 1000 L</t>
+          <t>Botellas 1L</t>
         </is>
       </c>
       <c r="F168" s="31" t="inlineStr">
         <is>
-          <t>COSTA RICA</t>
+          <t>PANAMÁ</t>
         </is>
       </c>
       <c r="G168" s="32" t="inlineStr">
@@ -11738,22 +11738,22 @@
         <v>0</v>
       </c>
       <c r="K168" s="33" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="L168" s="33" t="n">
-        <v>1000</v>
+        <v>1584</v>
       </c>
       <c r="M168" s="34" t="n">
-        <v>2000</v>
+        <v>1584</v>
       </c>
       <c r="N168" s="34" t="n">
-        <v>2000</v>
+        <v>1584</v>
       </c>
       <c r="O168" s="34" t="n">
-        <v>2000</v>
+        <v>1584</v>
       </c>
       <c r="P168" s="34" t="n">
-        <v>2000</v>
+        <v>1584</v>
       </c>
       <c r="Q168" s="35" t="inlineStr">
         <is>
@@ -11764,17 +11764,17 @@
     <row r="169" ht="19" customHeight="1">
       <c r="A169" s="18" t="inlineStr">
         <is>
-          <t>AGXCR0001</t>
+          <t>FLORCR0001</t>
         </is>
       </c>
       <c r="B169" s="19" t="inlineStr">
         <is>
-          <t>AGXCR0001PA</t>
+          <t>FLORCR0001PA</t>
         </is>
       </c>
       <c r="C169" s="20" t="inlineStr">
         <is>
-          <t>AGROXILATO-K</t>
+          <t>FLORAMEC CR, 1 L</t>
         </is>
       </c>
       <c r="D169" s="21" t="n">
@@ -11831,30 +11831,30 @@
     <row r="170" ht="19" customHeight="1">
       <c r="A170" s="27" t="inlineStr">
         <is>
-          <t>FLORCR0001</t>
+          <t>F-A0005</t>
         </is>
       </c>
       <c r="B170" s="28" t="inlineStr">
         <is>
-          <t>FLORCR0001PA</t>
+          <t>F-A0005DO</t>
         </is>
       </c>
       <c r="C170" s="29" t="inlineStr">
         <is>
-          <t>FLORAMEC CR, 1 L</t>
+          <t>FITOLIN-AGRO, 5 L</t>
         </is>
       </c>
       <c r="D170" s="30" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E170" s="29" t="inlineStr">
         <is>
-          <t>Botellas 1L</t>
+          <t>Garrafas 5L</t>
         </is>
       </c>
       <c r="F170" s="31" t="inlineStr">
         <is>
-          <t>PANAMÁ</t>
+          <t>DOMINICANA, REPÚBLICA</t>
         </is>
       </c>
       <c r="G170" s="32" t="inlineStr">
@@ -11872,22 +11872,22 @@
         <v>0</v>
       </c>
       <c r="K170" s="33" t="n">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="L170" s="33" t="n">
-        <v>1584</v>
+        <v>0</v>
       </c>
       <c r="M170" s="34" t="n">
-        <v>1584</v>
+        <v>1500</v>
       </c>
       <c r="N170" s="34" t="n">
-        <v>1584</v>
+        <v>1500</v>
       </c>
       <c r="O170" s="34" t="n">
-        <v>1584</v>
+        <v>1500</v>
       </c>
       <c r="P170" s="34" t="n">
-        <v>1584</v>
+        <v>1500</v>
       </c>
       <c r="Q170" s="35" t="inlineStr">
         <is>
@@ -11898,30 +11898,30 @@
     <row r="171" ht="19" customHeight="1">
       <c r="A171" s="18" t="inlineStr">
         <is>
-          <t>F-A0005</t>
+          <t>AGXCR0001</t>
         </is>
       </c>
       <c r="B171" s="19" t="inlineStr">
         <is>
-          <t>F-A0005DO</t>
+          <t>AGXCR0001CO</t>
         </is>
       </c>
       <c r="C171" s="20" t="inlineStr">
         <is>
-          <t>FITOLIN-AGRO, 5 L</t>
+          <t>AGROXILATO-K</t>
         </is>
       </c>
       <c r="D171" s="21" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E171" s="20" t="inlineStr">
         <is>
-          <t>Garrafas 5L</t>
+          <t>Botellas 1L</t>
         </is>
       </c>
       <c r="F171" s="22" t="inlineStr">
         <is>
-          <t>DOMINICANA, REPÚBLICA</t>
+          <t>COLOMBIA</t>
         </is>
       </c>
       <c r="G171" s="23" t="inlineStr">
@@ -11933,28 +11933,28 @@
         <v>0</v>
       </c>
       <c r="I171" s="24" t="n">
-        <v>0</v>
+        <v>840</v>
       </c>
       <c r="J171" s="24" t="n">
         <v>0</v>
       </c>
       <c r="K171" s="24" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="L171" s="24" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="M171" s="25" t="n">
-        <v>1500</v>
+        <v>1440</v>
       </c>
       <c r="N171" s="25" t="n">
-        <v>1500</v>
+        <v>1440</v>
       </c>
       <c r="O171" s="25" t="n">
-        <v>1500</v>
+        <v>1440</v>
       </c>
       <c r="P171" s="25" t="n">
-        <v>1500</v>
+        <v>1440</v>
       </c>
       <c r="Q171" s="35" t="inlineStr">
         <is>
@@ -11965,67 +11965,67 @@
     <row r="172" ht="19" customHeight="1">
       <c r="A172" s="27" t="inlineStr">
         <is>
-          <t>AGXCR0001</t>
-        </is>
-      </c>
-      <c r="B172" s="28" t="inlineStr">
-        <is>
-          <t>AGXCR0001CO</t>
+          <t>S0020</t>
+        </is>
+      </c>
+      <c r="B172" s="31" t="inlineStr">
+        <is>
+          <t>S0020</t>
         </is>
       </c>
       <c r="C172" s="29" t="inlineStr">
         <is>
-          <t>AGROXILATO-K</t>
+          <t>SALWAX STAR, 20 L</t>
         </is>
       </c>
       <c r="D172" s="30" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E172" s="29" t="inlineStr">
         <is>
-          <t>Botellas 1L</t>
+          <t>Garrafas 20L</t>
         </is>
       </c>
       <c r="F172" s="31" t="inlineStr">
         <is>
-          <t>COLOMBIA</t>
-        </is>
-      </c>
-      <c r="G172" s="32" t="inlineStr">
-        <is>
-          <t>Sobre Pedido (Export)</t>
+          <t>ESPAÑA</t>
+        </is>
+      </c>
+      <c r="G172" s="31" t="inlineStr">
+        <is>
+          <t>Para Previsión (Nac)</t>
         </is>
       </c>
       <c r="H172" s="33" t="n">
-        <v>0</v>
+        <v>5080</v>
       </c>
       <c r="I172" s="33" t="n">
-        <v>840</v>
+        <v>0</v>
       </c>
       <c r="J172" s="33" t="n">
-        <v>0</v>
+        <v>2560</v>
       </c>
       <c r="K172" s="33" t="n">
-        <v>0</v>
+        <v>3200</v>
       </c>
       <c r="L172" s="33" t="n">
-        <v>600</v>
+        <v>640</v>
       </c>
       <c r="M172" s="34" t="n">
-        <v>1440</v>
+        <v>6400</v>
       </c>
       <c r="N172" s="34" t="n">
-        <v>1440</v>
+        <v>6400</v>
       </c>
       <c r="O172" s="34" t="n">
-        <v>1440</v>
+        <v>1320</v>
       </c>
       <c r="P172" s="34" t="n">
-        <v>1440</v>
+        <v>1320</v>
       </c>
       <c r="Q172" s="35" t="inlineStr">
         <is>
-          <t>SOBRE PEDIDO (EXP)</t>
+          <t>SOLO ENVASAR</t>
         </is>
       </c>
     </row>
@@ -20782,7 +20782,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Horizonte: Octubre 2026 - Diciembre 2026  |  Total Graneles Químicos a Fabricar en Planta  |  Fecha Emisión: 20/10/2026 08:14</t>
+          <t xml:space="preserve">  Horizonte: Octubre 2026 - Diciembre 2026  |  Total Graneles Químicos a Fabricar en Planta  |  Fecha Emisión: 21/10/2026 08:19</t>
         </is>
       </c>
     </row>
@@ -20937,10 +20937,10 @@
         <v>0.01</v>
       </c>
       <c r="D7" s="24" t="n">
-        <v>57060</v>
+        <v>52660</v>
       </c>
       <c r="E7" s="25" t="n">
-        <v>57060.01</v>
+        <v>52660.01</v>
       </c>
       <c r="F7" s="24" t="n">
         <v>7320</v>
@@ -20958,10 +20958,10 @@
         <v>194370</v>
       </c>
       <c r="K7" s="24" t="n">
-        <v>-137309.99</v>
+        <v>-141709.99</v>
       </c>
       <c r="L7" s="25" t="n">
-        <v>137309.99</v>
+        <v>141709.99</v>
       </c>
       <c r="M7" s="26" t="inlineStr">
         <is>
@@ -20981,13 +20981,13 @@
         </is>
       </c>
       <c r="C8" s="33" t="n">
-        <v>22282</v>
+        <v>19722</v>
       </c>
       <c r="D8" s="33" t="n">
-        <v>20855</v>
+        <v>22135</v>
       </c>
       <c r="E8" s="34" t="n">
-        <v>43137</v>
+        <v>41857</v>
       </c>
       <c r="F8" s="33" t="n">
         <v>25080</v>
@@ -21005,10 +21005,10 @@
         <v>155316</v>
       </c>
       <c r="K8" s="33" t="n">
-        <v>-112179</v>
+        <v>-113459</v>
       </c>
       <c r="L8" s="34" t="n">
-        <v>112179</v>
+        <v>113459</v>
       </c>
       <c r="M8" s="26" t="inlineStr">
         <is>
@@ -21078,10 +21078,10 @@
         <v>2820</v>
       </c>
       <c r="D10" s="33" t="n">
-        <v>15480</v>
+        <v>15280</v>
       </c>
       <c r="E10" s="34" t="n">
-        <v>18300</v>
+        <v>18100</v>
       </c>
       <c r="F10" s="33" t="n">
         <v>21700</v>
@@ -21099,10 +21099,10 @@
         <v>95596</v>
       </c>
       <c r="K10" s="33" t="n">
-        <v>-77296</v>
+        <v>-77496</v>
       </c>
       <c r="L10" s="34" t="n">
-        <v>77296</v>
+        <v>77496</v>
       </c>
       <c r="M10" s="26" t="inlineStr">
         <is>
@@ -21266,10 +21266,10 @@
         <v>3106</v>
       </c>
       <c r="D14" s="33" t="n">
-        <v>16348</v>
+        <v>16248</v>
       </c>
       <c r="E14" s="34" t="n">
-        <v>19454</v>
+        <v>19354</v>
       </c>
       <c r="F14" s="33" t="n">
         <v>3000</v>
@@ -21287,10 +21287,10 @@
         <v>35488</v>
       </c>
       <c r="K14" s="33" t="n">
-        <v>-16034</v>
+        <v>-16134</v>
       </c>
       <c r="L14" s="34" t="n">
-        <v>16034</v>
+        <v>16134</v>
       </c>
       <c r="M14" s="26" t="inlineStr">
         <is>
@@ -21357,13 +21357,13 @@
         </is>
       </c>
       <c r="C16" s="33" t="n">
-        <v>17000</v>
+        <v>19340</v>
       </c>
       <c r="D16" s="33" t="n">
-        <v>20900</v>
+        <v>20420</v>
       </c>
       <c r="E16" s="34" t="n">
-        <v>37900</v>
+        <v>39760</v>
       </c>
       <c r="F16" s="33" t="n">
         <v>0</v>
@@ -21381,10 +21381,10 @@
         <v>51000</v>
       </c>
       <c r="K16" s="33" t="n">
-        <v>-13100</v>
+        <v>-11240</v>
       </c>
       <c r="L16" s="34" t="n">
-        <v>13100</v>
+        <v>11240</v>
       </c>
       <c r="M16" s="26" t="inlineStr">
         <is>
@@ -21407,10 +21407,10 @@
         <v>0</v>
       </c>
       <c r="D17" s="24" t="n">
-        <v>5690</v>
+        <v>5740</v>
       </c>
       <c r="E17" s="25" t="n">
-        <v>5690</v>
+        <v>5740</v>
       </c>
       <c r="F17" s="24" t="n">
         <v>0</v>
@@ -21428,10 +21428,10 @@
         <v>16300</v>
       </c>
       <c r="K17" s="24" t="n">
-        <v>-10610</v>
+        <v>-10560</v>
       </c>
       <c r="L17" s="25" t="n">
-        <v>10610</v>
+        <v>10560</v>
       </c>
       <c r="M17" s="26" t="inlineStr">
         <is>
@@ -23475,10 +23475,10 @@
         <v>0</v>
       </c>
       <c r="D61" s="24" t="n">
-        <v>6155</v>
+        <v>6055</v>
       </c>
       <c r="E61" s="25" t="n">
-        <v>6155</v>
+        <v>6055</v>
       </c>
       <c r="F61" s="24" t="n">
         <v>800</v>
@@ -23496,7 +23496,7 @@
         <v>1100</v>
       </c>
       <c r="K61" s="24" t="n">
-        <v>5055</v>
+        <v>4955</v>
       </c>
       <c r="L61" s="25" t="n">
         <v>0</v>
@@ -25299,7 +25299,7 @@
         <v>54</v>
       </c>
       <c r="C7" s="24" t="n">
-        <v>78150</v>
+        <v>81050</v>
       </c>
       <c r="D7" s="24" t="n">
         <v>28060</v>
@@ -25317,7 +25317,7 @@
         <v>269940</v>
       </c>
       <c r="I7" s="25" t="n">
-        <v>191790</v>
+        <v>188890</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
@@ -25330,7 +25330,7 @@
         <v>28</v>
       </c>
       <c r="C8" s="33" t="n">
-        <v>47020</v>
+        <v>43720</v>
       </c>
       <c r="D8" s="33" t="n">
         <v>32700</v>
@@ -25348,7 +25348,7 @@
         <v>557960</v>
       </c>
       <c r="I8" s="34" t="n">
-        <v>510940</v>
+        <v>514240</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
@@ -25392,7 +25392,7 @@
         <v>45</v>
       </c>
       <c r="C10" s="33" t="n">
-        <v>29800</v>
+        <v>29850</v>
       </c>
       <c r="D10" s="33" t="n">
         <v>32770</v>
@@ -25410,7 +25410,7 @@
         <v>205320</v>
       </c>
       <c r="I10" s="34" t="n">
-        <v>175520</v>
+        <v>175470</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
@@ -25558,7 +25558,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Premisa de Gestión: Previsiones exclusivamente del Mercado Nacional (España). La exportación se fabricará siempre sobre pedido.  |  Fecha: 20/10/2026 08:14</t>
+          <t xml:space="preserve">  Premisa de Gestión: Previsiones exclusivamente del Mercado Nacional (España). La exportación se fabricará siempre sobre pedido.  |  Fecha: 21/10/2026 08:19</t>
         </is>
       </c>
     </row>
@@ -25574,7 +25574,7 @@
       <c r="D4" s="4" t="n"/>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>🔴 NOMOVERS (&gt;6M NACIONAL) — 18.0%</t>
+          <t>🔴 NOMOVERS (&gt;6M NACIONAL) — 17.1%</t>
         </is>
       </c>
       <c r="F4" s="4" t="n"/>
@@ -25582,7 +25582,7 @@
       <c r="H4" s="4" t="n"/>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>🟡 SLOWMOVERS (3-6M NACIONAL) — 13.6%</t>
+          <t>🟡 SLOWMOVERS (3-6M NACIONAL) — 13.5%</t>
         </is>
       </c>
       <c r="J4" s="4" t="n"/>
@@ -25590,7 +25590,7 @@
       <c r="L4" s="4" t="n"/>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>🟢 ALTA ROTACIÓN (Q4 NACIONAL) — 68.5%</t>
+          <t>🟢 ALTA ROTACIÓN (Q4 NACIONAL) — 69.4%</t>
         </is>
       </c>
       <c r="N4" s="4" t="n"/>
@@ -25600,7 +25600,7 @@
     <row r="5" ht="24" customHeight="1">
       <c r="A5" s="46" t="inlineStr">
         <is>
-          <t>248.170 L/Kg  (232.300 €)</t>
+          <t>244.220 L/Kg  (232.604 €)</t>
         </is>
       </c>
       <c r="B5" s="4" t="n"/>
@@ -25608,7 +25608,7 @@
       <c r="D5" s="4" t="n"/>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>44.620 L/Kg  |  43.566.09 €</t>
+          <t>41.820 L/Kg  |  42.208.18 €</t>
         </is>
       </c>
       <c r="F5" s="4" t="n"/>
@@ -25616,7 +25616,7 @@
       <c r="H5" s="4" t="n"/>
       <c r="I5" s="6" t="inlineStr">
         <is>
-          <t>33.665 L/Kg  |  39.253.00 €</t>
+          <t>32.915 L/Kg  |  39.184.92 €</t>
         </is>
       </c>
       <c r="J5" s="4" t="n"/>
@@ -25624,7 +25624,7 @@
       <c r="L5" s="4" t="n"/>
       <c r="M5" s="8" t="inlineStr">
         <is>
-          <t>169.885 L/Kg  (43 SKUs)</t>
+          <t>169.485 L/Kg  (43 SKUs)</t>
         </is>
       </c>
       <c r="N5" s="4" t="n"/>
@@ -25774,7 +25774,7 @@
         </is>
       </c>
       <c r="L9" s="52" t="n">
-        <v>4.357037665</v>
+        <v>4.357037664566667</v>
       </c>
       <c r="M9" s="53" t="n">
         <v>8574.65</v>
@@ -25831,7 +25831,7 @@
         </is>
       </c>
       <c r="L10" s="55" t="n">
-        <v>5.496556791</v>
+        <v>5.4965567912</v>
       </c>
       <c r="M10" s="56" t="n">
         <v>4259.83</v>
@@ -25888,7 +25888,7 @@
         </is>
       </c>
       <c r="L11" s="52" t="n">
-        <v>0.519747475</v>
+        <v>0.51974747515</v>
       </c>
       <c r="M11" s="53" t="n">
         <v>3721.39</v>
@@ -25945,7 +25945,7 @@
         </is>
       </c>
       <c r="L12" s="55" t="n">
-        <v>0.376904316</v>
+        <v>0.3769043160700001</v>
       </c>
       <c r="M12" s="56" t="n">
         <v>3535.36</v>
@@ -26002,7 +26002,7 @@
         </is>
       </c>
       <c r="L13" s="52" t="n">
-        <v>1.808707836</v>
+        <v>1.80870783555</v>
       </c>
       <c r="M13" s="53" t="n">
         <v>1756.26</v>
@@ -26059,7 +26059,7 @@
         </is>
       </c>
       <c r="L14" s="55" t="n">
-        <v>1.436969766</v>
+        <v>1.4369697656875</v>
       </c>
       <c r="M14" s="56" t="n">
         <v>1533.25</v>
@@ -26116,7 +26116,7 @@
         </is>
       </c>
       <c r="L15" s="52" t="n">
-        <v>0.492659548</v>
+        <v>0.4926595484</v>
       </c>
       <c r="M15" s="53" t="n">
         <v>1337.57</v>
@@ -26173,7 +26173,7 @@
         </is>
       </c>
       <c r="L16" s="55" t="n">
-        <v>1.693123212</v>
+        <v>1.6931232119</v>
       </c>
       <c r="M16" s="56" t="n">
         <v>1239.37</v>
@@ -26230,7 +26230,7 @@
         </is>
       </c>
       <c r="L17" s="52" t="n">
-        <v>1.370831857</v>
+        <v>1.3708318574</v>
       </c>
       <c r="M17" s="53" t="n">
         <v>1096.67</v>
@@ -26287,7 +26287,7 @@
         </is>
       </c>
       <c r="L18" s="55" t="n">
-        <v>1.489240857</v>
+        <v>1.4892408571</v>
       </c>
       <c r="M18" s="56" t="n">
         <v>1058.85</v>
@@ -26304,39 +26304,39 @@
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="51" t="inlineStr">
         <is>
-          <t>BR-590005</t>
+          <t>FU1000</t>
         </is>
       </c>
       <c r="B19" s="20" t="inlineStr">
         <is>
-          <t>BR-59, 5 KG</t>
+          <t>FULVIGIN, 1000 L</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
         <is>
-          <t>Bolsas 5 Kg</t>
+          <t>Depósito 1000 L</t>
         </is>
       </c>
       <c r="D19" s="25" t="n">
-        <v>3440</v>
+        <v>1000</v>
       </c>
       <c r="E19" s="24" t="n">
-        <v>688</v>
+        <v>1</v>
       </c>
       <c r="F19" s="24" t="n">
         <v>0</v>
       </c>
       <c r="G19" s="24" t="n">
-        <v>1455</v>
+        <v>0</v>
       </c>
       <c r="H19" s="25" t="n">
-        <v>1455</v>
+        <v>0</v>
       </c>
       <c r="I19" s="25" t="n">
-        <v>1985</v>
+        <v>1000</v>
       </c>
       <c r="J19" s="24" t="n">
-        <v>397</v>
+        <v>1</v>
       </c>
       <c r="K19" s="26" t="inlineStr">
         <is>
@@ -26344,56 +26344,56 @@
         </is>
       </c>
       <c r="L19" s="52" t="n">
-        <v>0.524652074</v>
+        <v>1.0351194094</v>
       </c>
       <c r="M19" s="53" t="n">
-        <v>1041.43</v>
-      </c>
-      <c r="N19" s="58" t="n">
-        <v>763.37</v>
+        <v>1035.12</v>
+      </c>
+      <c r="N19" s="52" t="n">
+        <v>0</v>
       </c>
       <c r="O19" s="20" t="inlineStr">
         <is>
-          <t>Plan Choque Comercial Nac / Oferta</t>
+          <t>Sin Demanda Nacional (Inmovilizado Crítico)</t>
         </is>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="54" t="inlineStr">
         <is>
-          <t>FU1000</t>
+          <t>BR-590005</t>
         </is>
       </c>
       <c r="B20" s="29" t="inlineStr">
         <is>
-          <t>FULVIGIN, 1000 L</t>
+          <t>BR-59, 5 KG</t>
         </is>
       </c>
       <c r="C20" s="29" t="inlineStr">
         <is>
-          <t>Depósito 1000 L</t>
+          <t>Bolsas 5 Kg</t>
         </is>
       </c>
       <c r="D20" s="34" t="n">
-        <v>1000</v>
+        <v>3340</v>
       </c>
       <c r="E20" s="33" t="n">
-        <v>1</v>
+        <v>668</v>
       </c>
       <c r="F20" s="33" t="n">
         <v>0</v>
       </c>
       <c r="G20" s="33" t="n">
-        <v>0</v>
+        <v>1455</v>
       </c>
       <c r="H20" s="34" t="n">
-        <v>0</v>
+        <v>1455</v>
       </c>
       <c r="I20" s="34" t="n">
-        <v>1000</v>
+        <v>1885</v>
       </c>
       <c r="J20" s="33" t="n">
-        <v>1</v>
+        <v>377</v>
       </c>
       <c r="K20" s="26" t="inlineStr">
         <is>
@@ -26401,17 +26401,17 @@
         </is>
       </c>
       <c r="L20" s="55" t="n">
-        <v>1.035119409</v>
+        <v>0.5246520740285714</v>
       </c>
       <c r="M20" s="56" t="n">
-        <v>1035.12</v>
-      </c>
-      <c r="N20" s="55" t="n">
-        <v>0</v>
+        <v>988.97</v>
+      </c>
+      <c r="N20" s="57" t="n">
+        <v>763.37</v>
       </c>
       <c r="O20" s="29" t="inlineStr">
         <is>
-          <t>Sin Demanda Nacional (Inmovilizado Crítico)</t>
+          <t>Plan Choque Comercial Nac / Oferta</t>
         </is>
       </c>
     </row>
@@ -26458,7 +26458,7 @@
         </is>
       </c>
       <c r="L21" s="52" t="n">
-        <v>1.958383848</v>
+        <v>1.9583838483</v>
       </c>
       <c r="M21" s="53" t="n">
         <v>940.02</v>
@@ -26475,39 +26475,39 @@
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="54" t="inlineStr">
         <is>
-          <t>S0200</t>
+          <t>AQUOM0005</t>
         </is>
       </c>
       <c r="B22" s="29" t="inlineStr">
         <is>
-          <t>SAL-WAX STAR, 200 L</t>
+          <t>AQUOM, 5 L</t>
         </is>
       </c>
       <c r="C22" s="29" t="inlineStr">
         <is>
-          <t>Depósito 200 L</t>
+          <t>Garrafas 5L</t>
         </is>
       </c>
       <c r="D22" s="34" t="n">
-        <v>11200</v>
+        <v>860</v>
       </c>
       <c r="E22" s="33" t="n">
-        <v>56</v>
+        <v>172</v>
       </c>
       <c r="F22" s="33" t="n">
-        <v>5600</v>
+        <v>0</v>
       </c>
       <c r="G22" s="33" t="n">
-        <v>4000</v>
+        <v>530</v>
       </c>
       <c r="H22" s="34" t="n">
-        <v>4000</v>
+        <v>530</v>
       </c>
       <c r="I22" s="34" t="n">
-        <v>1600</v>
+        <v>330</v>
       </c>
       <c r="J22" s="33" t="n">
-        <v>8</v>
+        <v>66</v>
       </c>
       <c r="K22" s="26" t="inlineStr">
         <is>
@@ -26515,13 +26515,13 @@
         </is>
       </c>
       <c r="L22" s="55" t="n">
-        <v>0.534280133</v>
+        <v>2.37025205435</v>
       </c>
       <c r="M22" s="56" t="n">
-        <v>854.85</v>
+        <v>782.1799999999999</v>
       </c>
       <c r="N22" s="57" t="n">
-        <v>2137.12</v>
+        <v>1256.23</v>
       </c>
       <c r="O22" s="29" t="inlineStr">
         <is>
@@ -26532,39 +26532,39 @@
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="51" t="inlineStr">
         <is>
-          <t>AQUOM0005</t>
+          <t>AN0005</t>
         </is>
       </c>
       <c r="B23" s="20" t="inlineStr">
         <is>
-          <t>AQUOM, 5 L</t>
+          <t>ALCAPLANT NEW, 5 KG</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
         <is>
-          <t>Garrafas 5L</t>
+          <t>Bolsas 5 Kg</t>
         </is>
       </c>
       <c r="D23" s="25" t="n">
-        <v>860</v>
+        <v>3280</v>
       </c>
       <c r="E23" s="24" t="n">
-        <v>172</v>
+        <v>656</v>
       </c>
       <c r="F23" s="24" t="n">
         <v>0</v>
       </c>
       <c r="G23" s="24" t="n">
-        <v>530</v>
+        <v>0</v>
       </c>
       <c r="H23" s="25" t="n">
-        <v>530</v>
+        <v>0</v>
       </c>
       <c r="I23" s="25" t="n">
-        <v>330</v>
+        <v>3280</v>
       </c>
       <c r="J23" s="24" t="n">
-        <v>66</v>
+        <v>656</v>
       </c>
       <c r="K23" s="26" t="inlineStr">
         <is>
@@ -26572,29 +26572,29 @@
         </is>
       </c>
       <c r="L23" s="52" t="n">
-        <v>2.370252054</v>
+        <v>0.2326995786125</v>
       </c>
       <c r="M23" s="53" t="n">
-        <v>782.1799999999999</v>
-      </c>
-      <c r="N23" s="58" t="n">
-        <v>1256.23</v>
+        <v>763.25</v>
+      </c>
+      <c r="N23" s="52" t="n">
+        <v>0</v>
       </c>
       <c r="O23" s="20" t="inlineStr">
         <is>
-          <t>Plan Choque Comercial Nac / Oferta</t>
+          <t>Sin Demanda Nacional (Inmovilizado Crítico)</t>
         </is>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="54" t="inlineStr">
         <is>
-          <t>AN0005</t>
+          <t>AGZ-M0005</t>
         </is>
       </c>
       <c r="B24" s="29" t="inlineStr">
         <is>
-          <t>ALCAPLANT NEW, 5 KG</t>
+          <t>AGROXILATO-ZN-MN, 5 KG</t>
         </is>
       </c>
       <c r="C24" s="29" t="inlineStr">
@@ -26603,25 +26603,25 @@
         </is>
       </c>
       <c r="D24" s="34" t="n">
-        <v>3280</v>
+        <v>1125</v>
       </c>
       <c r="E24" s="33" t="n">
-        <v>656</v>
+        <v>225</v>
       </c>
       <c r="F24" s="33" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G24" s="33" t="n">
-        <v>0</v>
+        <v>580</v>
       </c>
       <c r="H24" s="34" t="n">
-        <v>0</v>
+        <v>580</v>
       </c>
       <c r="I24" s="34" t="n">
-        <v>3280</v>
+        <v>345</v>
       </c>
       <c r="J24" s="33" t="n">
-        <v>656</v>
+        <v>69</v>
       </c>
       <c r="K24" s="26" t="inlineStr">
         <is>
@@ -26629,56 +26629,56 @@
         </is>
       </c>
       <c r="L24" s="55" t="n">
-        <v>0.232699579</v>
+        <v>1.99008621435</v>
       </c>
       <c r="M24" s="56" t="n">
-        <v>763.25</v>
-      </c>
-      <c r="N24" s="55" t="n">
-        <v>0</v>
+        <v>686.58</v>
+      </c>
+      <c r="N24" s="57" t="n">
+        <v>1154.25</v>
       </c>
       <c r="O24" s="29" t="inlineStr">
         <is>
-          <t>Sin Demanda Nacional (Inmovilizado Crítico)</t>
+          <t>Plan Choque Comercial Nac / Oferta</t>
         </is>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="51" t="inlineStr">
         <is>
-          <t>AGZ-M0005</t>
+          <t>FU0005</t>
         </is>
       </c>
       <c r="B25" s="20" t="inlineStr">
         <is>
-          <t>AGROXILATO-ZN-MN, 5 KG</t>
+          <t>FULVIGIN, 5 L</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
         <is>
-          <t>Bolsas 5 Kg</t>
+          <t>Garrafas 5L</t>
         </is>
       </c>
       <c r="D25" s="25" t="n">
-        <v>1125</v>
+        <v>600</v>
       </c>
       <c r="E25" s="24" t="n">
-        <v>225</v>
+        <v>120</v>
       </c>
       <c r="F25" s="24" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="G25" s="24" t="n">
+        <v>20</v>
+      </c>
+      <c r="H25" s="25" t="n">
+        <v>20</v>
+      </c>
+      <c r="I25" s="25" t="n">
         <v>580</v>
       </c>
-      <c r="H25" s="25" t="n">
-        <v>580</v>
-      </c>
-      <c r="I25" s="25" t="n">
-        <v>345</v>
-      </c>
       <c r="J25" s="24" t="n">
-        <v>69</v>
+        <v>116</v>
       </c>
       <c r="K25" s="26" t="inlineStr">
         <is>
@@ -26686,13 +26686,13 @@
         </is>
       </c>
       <c r="L25" s="52" t="n">
-        <v>1.990086214</v>
+        <v>1.1795598635</v>
       </c>
       <c r="M25" s="53" t="n">
-        <v>686.58</v>
+        <v>684.14</v>
       </c>
       <c r="N25" s="58" t="n">
-        <v>1154.25</v>
+        <v>23.59</v>
       </c>
       <c r="O25" s="20" t="inlineStr">
         <is>
@@ -26703,39 +26703,39 @@
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="54" t="inlineStr">
         <is>
-          <t>FU0005</t>
+          <t>CBROT0020</t>
         </is>
       </c>
       <c r="B26" s="29" t="inlineStr">
         <is>
-          <t>FULVIGIN, 5 L</t>
+          <t>CODIBROT, 20 L</t>
         </is>
       </c>
       <c r="C26" s="29" t="inlineStr">
         <is>
-          <t>Garrafas 5L</t>
+          <t>Garrafas 20L</t>
         </is>
       </c>
       <c r="D26" s="34" t="n">
-        <v>600</v>
+        <v>620</v>
       </c>
       <c r="E26" s="33" t="n">
-        <v>120</v>
+        <v>31</v>
       </c>
       <c r="F26" s="33" t="n">
         <v>0</v>
       </c>
       <c r="G26" s="33" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="H26" s="34" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="I26" s="34" t="n">
-        <v>580</v>
+        <v>520</v>
       </c>
       <c r="J26" s="33" t="n">
-        <v>116</v>
+        <v>26</v>
       </c>
       <c r="K26" s="26" t="inlineStr">
         <is>
@@ -26743,13 +26743,13 @@
         </is>
       </c>
       <c r="L26" s="55" t="n">
-        <v>1.179559864</v>
+        <v>1.1661211405</v>
       </c>
       <c r="M26" s="56" t="n">
-        <v>684.14</v>
+        <v>606.38</v>
       </c>
       <c r="N26" s="57" t="n">
-        <v>23.59</v>
+        <v>116.61</v>
       </c>
       <c r="O26" s="29" t="inlineStr">
         <is>
@@ -26760,39 +26760,39 @@
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="51" t="inlineStr">
         <is>
-          <t>CBROT0020</t>
+          <t>SS0005</t>
         </is>
       </c>
       <c r="B27" s="20" t="inlineStr">
         <is>
-          <t>CODIBROT, 20 L</t>
+          <t>SALWAX-CA, 5 KG</t>
         </is>
       </c>
       <c r="C27" s="20" t="inlineStr">
         <is>
-          <t>Garrafas 20L</t>
+          <t>Bolsas 5 Kg</t>
         </is>
       </c>
       <c r="D27" s="25" t="n">
-        <v>620</v>
+        <v>2270</v>
       </c>
       <c r="E27" s="24" t="n">
-        <v>31</v>
+        <v>454</v>
       </c>
       <c r="F27" s="24" t="n">
-        <v>0</v>
+        <v>750</v>
       </c>
       <c r="G27" s="24" t="n">
-        <v>100</v>
+        <v>1055</v>
       </c>
       <c r="H27" s="25" t="n">
-        <v>100</v>
+        <v>1055</v>
       </c>
       <c r="I27" s="25" t="n">
-        <v>520</v>
+        <v>465</v>
       </c>
       <c r="J27" s="24" t="n">
-        <v>26</v>
+        <v>93</v>
       </c>
       <c r="K27" s="26" t="inlineStr">
         <is>
@@ -26800,13 +26800,13 @@
         </is>
       </c>
       <c r="L27" s="52" t="n">
-        <v>1.166121141</v>
+        <v>1.295598783446154</v>
       </c>
       <c r="M27" s="53" t="n">
-        <v>606.38</v>
+        <v>602.45</v>
       </c>
       <c r="N27" s="58" t="n">
-        <v>116.61</v>
+        <v>1366.86</v>
       </c>
       <c r="O27" s="20" t="inlineStr">
         <is>
@@ -26817,39 +26817,39 @@
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="54" t="inlineStr">
         <is>
-          <t>SS0005</t>
+          <t>CBROT0005</t>
         </is>
       </c>
       <c r="B28" s="29" t="inlineStr">
         <is>
-          <t>SALWAX-CA, 5 KG</t>
+          <t>CODIBROT, 5 L</t>
         </is>
       </c>
       <c r="C28" s="29" t="inlineStr">
         <is>
-          <t>Bolsas 5 Kg</t>
+          <t>Garrafas 5L</t>
         </is>
       </c>
       <c r="D28" s="34" t="n">
-        <v>2270</v>
+        <v>600</v>
       </c>
       <c r="E28" s="33" t="n">
-        <v>454</v>
+        <v>120</v>
       </c>
       <c r="F28" s="33" t="n">
-        <v>750</v>
+        <v>0</v>
       </c>
       <c r="G28" s="33" t="n">
-        <v>1055</v>
+        <v>215</v>
       </c>
       <c r="H28" s="34" t="n">
-        <v>1055</v>
+        <v>215</v>
       </c>
       <c r="I28" s="34" t="n">
-        <v>465</v>
+        <v>385</v>
       </c>
       <c r="J28" s="33" t="n">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="K28" s="26" t="inlineStr">
         <is>
@@ -26857,13 +26857,13 @@
         </is>
       </c>
       <c r="L28" s="55" t="n">
-        <v>1.295598783</v>
+        <v>1.29306175245</v>
       </c>
       <c r="M28" s="56" t="n">
-        <v>602.45</v>
+        <v>497.83</v>
       </c>
       <c r="N28" s="57" t="n">
-        <v>1366.86</v>
+        <v>278.01</v>
       </c>
       <c r="O28" s="29" t="inlineStr">
         <is>
@@ -26874,39 +26874,39 @@
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="51" t="inlineStr">
         <is>
-          <t>ANAE0020</t>
+          <t>DECA0005</t>
         </is>
       </c>
       <c r="B29" s="20" t="inlineStr">
         <is>
-          <t>ALCAPLANT NEW AE, 20 KG</t>
+          <t>DEFENS-CA-AE</t>
         </is>
       </c>
       <c r="C29" s="20" t="inlineStr">
         <is>
-          <t>Bolsas 20 Kg</t>
+          <t>Bolsas 5 Kg</t>
         </is>
       </c>
       <c r="D29" s="25" t="n">
-        <v>13820</v>
+        <v>960</v>
       </c>
       <c r="E29" s="24" t="n">
-        <v>691</v>
+        <v>192</v>
       </c>
       <c r="F29" s="24" t="n">
-        <v>7700</v>
+        <v>0</v>
       </c>
       <c r="G29" s="24" t="n">
-        <v>4800</v>
+        <v>0</v>
       </c>
       <c r="H29" s="25" t="n">
-        <v>4800</v>
+        <v>0</v>
       </c>
       <c r="I29" s="25" t="n">
-        <v>1320</v>
+        <v>960</v>
       </c>
       <c r="J29" s="24" t="n">
-        <v>66</v>
+        <v>192</v>
       </c>
       <c r="K29" s="26" t="inlineStr">
         <is>
@@ -26914,56 +26914,56 @@
         </is>
       </c>
       <c r="L29" s="52" t="n">
-        <v>0.409634067</v>
+        <v>0.4972459397666667</v>
       </c>
       <c r="M29" s="53" t="n">
-        <v>540.72</v>
-      </c>
-      <c r="N29" s="58" t="n">
-        <v>1966.24</v>
+        <v>477.36</v>
+      </c>
+      <c r="N29" s="52" t="n">
+        <v>0</v>
       </c>
       <c r="O29" s="20" t="inlineStr">
         <is>
-          <t>Plan Choque Comercial Nac / Oferta</t>
+          <t>Sin Demanda Nacional (Inmovilizado Crítico)</t>
         </is>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="54" t="inlineStr">
         <is>
-          <t>CBROT0005</t>
+          <t>SPCE2B0001</t>
         </is>
       </c>
       <c r="B30" s="29" t="inlineStr">
         <is>
-          <t>CODIBROT, 5 L</t>
+          <t>SPRINTENE CON BORO, 1 L</t>
         </is>
       </c>
       <c r="C30" s="29" t="inlineStr">
         <is>
-          <t>Garrafas 5L</t>
+          <t>Botellas 1L</t>
         </is>
       </c>
       <c r="D30" s="34" t="n">
-        <v>600</v>
+        <v>162</v>
       </c>
       <c r="E30" s="33" t="n">
-        <v>120</v>
+        <v>162</v>
       </c>
       <c r="F30" s="33" t="n">
         <v>0</v>
       </c>
       <c r="G30" s="33" t="n">
-        <v>215</v>
+        <v>78</v>
       </c>
       <c r="H30" s="34" t="n">
-        <v>215</v>
+        <v>78</v>
       </c>
       <c r="I30" s="34" t="n">
-        <v>385</v>
+        <v>84</v>
       </c>
       <c r="J30" s="33" t="n">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="K30" s="26" t="inlineStr">
         <is>
@@ -26971,13 +26971,13 @@
         </is>
       </c>
       <c r="L30" s="55" t="n">
-        <v>1.293061752</v>
+        <v>5.368841049257143</v>
       </c>
       <c r="M30" s="56" t="n">
-        <v>497.83</v>
+        <v>450.98</v>
       </c>
       <c r="N30" s="57" t="n">
-        <v>278.01</v>
+        <v>418.77</v>
       </c>
       <c r="O30" s="29" t="inlineStr">
         <is>
@@ -26988,24 +26988,24 @@
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="51" t="inlineStr">
         <is>
-          <t>DECA0005</t>
+          <t>AO0020</t>
         </is>
       </c>
       <c r="B31" s="20" t="inlineStr">
         <is>
-          <t>DEFENS-CA-AE</t>
+          <t>ALCAPLANT NEW</t>
         </is>
       </c>
       <c r="C31" s="20" t="inlineStr">
         <is>
-          <t>Bolsas 5 Kg</t>
+          <t>Bolsas 20 Kg</t>
         </is>
       </c>
       <c r="D31" s="25" t="n">
-        <v>960</v>
+        <v>1180</v>
       </c>
       <c r="E31" s="24" t="n">
-        <v>192</v>
+        <v>59</v>
       </c>
       <c r="F31" s="24" t="n">
         <v>0</v>
@@ -27017,10 +27017,10 @@
         <v>0</v>
       </c>
       <c r="I31" s="25" t="n">
-        <v>960</v>
+        <v>1180</v>
       </c>
       <c r="J31" s="24" t="n">
-        <v>192</v>
+        <v>59</v>
       </c>
       <c r="K31" s="26" t="inlineStr">
         <is>
@@ -27028,10 +27028,10 @@
         </is>
       </c>
       <c r="L31" s="52" t="n">
-        <v>0.49724594</v>
+        <v>0.3664046452166667</v>
       </c>
       <c r="M31" s="53" t="n">
-        <v>477.36</v>
+        <v>432.36</v>
       </c>
       <c r="N31" s="52" t="n">
         <v>0</v>
@@ -27045,39 +27045,39 @@
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="54" t="inlineStr">
         <is>
-          <t>SPCE2B0001</t>
+          <t>BC0005</t>
         </is>
       </c>
       <c r="B32" s="29" t="inlineStr">
         <is>
-          <t>SPRINTENE CON BORO, 1 L</t>
+          <t>BITTER-CAL, 5 KG</t>
         </is>
       </c>
       <c r="C32" s="29" t="inlineStr">
         <is>
-          <t>Botellas 1L</t>
+          <t>Bolsas 5 Kg</t>
         </is>
       </c>
       <c r="D32" s="34" t="n">
-        <v>162</v>
+        <v>370</v>
       </c>
       <c r="E32" s="33" t="n">
-        <v>162</v>
+        <v>74</v>
       </c>
       <c r="F32" s="33" t="n">
         <v>0</v>
       </c>
       <c r="G32" s="33" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="H32" s="34" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="I32" s="34" t="n">
-        <v>84</v>
+        <v>370</v>
       </c>
       <c r="J32" s="33" t="n">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="K32" s="26" t="inlineStr">
         <is>
@@ -27085,56 +27085,56 @@
         </is>
       </c>
       <c r="L32" s="55" t="n">
-        <v>5.368841049</v>
+        <v>1.1582183363</v>
       </c>
       <c r="M32" s="56" t="n">
-        <v>450.98</v>
-      </c>
-      <c r="N32" s="57" t="n">
-        <v>418.77</v>
+        <v>428.54</v>
+      </c>
+      <c r="N32" s="55" t="n">
+        <v>0</v>
       </c>
       <c r="O32" s="29" t="inlineStr">
         <is>
-          <t>Plan Choque Comercial Nac / Oferta</t>
+          <t>Sin Demanda Nacional (Inmovilizado Crítico)</t>
         </is>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="51" t="inlineStr">
         <is>
-          <t>AO0020</t>
+          <t>G30005</t>
         </is>
       </c>
       <c r="B33" s="20" t="inlineStr">
         <is>
-          <t>ALCAPLANT NEW</t>
+          <t>GREEN-UP, 5 L</t>
         </is>
       </c>
       <c r="C33" s="20" t="inlineStr">
         <is>
-          <t>Bolsas 20 Kg</t>
+          <t>Garrafas 5L</t>
         </is>
       </c>
       <c r="D33" s="25" t="n">
-        <v>1180</v>
+        <v>360</v>
       </c>
       <c r="E33" s="24" t="n">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="F33" s="24" t="n">
         <v>0</v>
       </c>
       <c r="G33" s="24" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H33" s="25" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="I33" s="25" t="n">
-        <v>1180</v>
+        <v>320</v>
       </c>
       <c r="J33" s="24" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="K33" s="26" t="inlineStr">
         <is>
@@ -27142,29 +27142,29 @@
         </is>
       </c>
       <c r="L33" s="52" t="n">
-        <v>0.366404645</v>
+        <v>1.2919829444</v>
       </c>
       <c r="M33" s="53" t="n">
-        <v>432.36</v>
-      </c>
-      <c r="N33" s="52" t="n">
-        <v>0</v>
+        <v>413.43</v>
+      </c>
+      <c r="N33" s="58" t="n">
+        <v>51.68</v>
       </c>
       <c r="O33" s="20" t="inlineStr">
         <is>
-          <t>Sin Demanda Nacional (Inmovilizado Crítico)</t>
+          <t>Plan Choque Comercial Nac / Oferta</t>
         </is>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="54" t="inlineStr">
         <is>
-          <t>BC0005</t>
+          <t>C-GLB0005</t>
         </is>
       </c>
       <c r="B34" s="29" t="inlineStr">
         <is>
-          <t>BITTER-CAL, 5 KG</t>
+          <t>CODIORGAN GLB, 5 KG</t>
         </is>
       </c>
       <c r="C34" s="29" t="inlineStr">
@@ -27173,10 +27173,10 @@
         </is>
       </c>
       <c r="D34" s="34" t="n">
-        <v>370</v>
+        <v>255</v>
       </c>
       <c r="E34" s="33" t="n">
-        <v>74</v>
+        <v>51</v>
       </c>
       <c r="F34" s="33" t="n">
         <v>0</v>
@@ -27188,10 +27188,10 @@
         <v>0</v>
       </c>
       <c r="I34" s="34" t="n">
-        <v>370</v>
+        <v>255</v>
       </c>
       <c r="J34" s="33" t="n">
-        <v>74</v>
+        <v>51</v>
       </c>
       <c r="K34" s="26" t="inlineStr">
         <is>
@@ -27199,10 +27199,10 @@
         </is>
       </c>
       <c r="L34" s="55" t="n">
-        <v>1.158218336</v>
+        <v>1.57523124345</v>
       </c>
       <c r="M34" s="56" t="n">
-        <v>428.54</v>
+        <v>401.68</v>
       </c>
       <c r="N34" s="55" t="n">
         <v>0</v>
@@ -27216,12 +27216,12 @@
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="51" t="inlineStr">
         <is>
-          <t>G30005</t>
+          <t>AGRMG0005</t>
         </is>
       </c>
       <c r="B35" s="20" t="inlineStr">
         <is>
-          <t>GREEN-UP, 5 L</t>
+          <t>AGROXIGREEN-MG, 5 L</t>
         </is>
       </c>
       <c r="C35" s="20" t="inlineStr">
@@ -27230,25 +27230,25 @@
         </is>
       </c>
       <c r="D35" s="25" t="n">
-        <v>360</v>
+        <v>775</v>
       </c>
       <c r="E35" s="24" t="n">
-        <v>72</v>
+        <v>155</v>
       </c>
       <c r="F35" s="24" t="n">
         <v>0</v>
       </c>
       <c r="G35" s="24" t="n">
-        <v>40</v>
+        <v>475</v>
       </c>
       <c r="H35" s="25" t="n">
-        <v>40</v>
+        <v>475</v>
       </c>
       <c r="I35" s="25" t="n">
-        <v>320</v>
+        <v>300</v>
       </c>
       <c r="J35" s="24" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="K35" s="26" t="inlineStr">
         <is>
@@ -27256,13 +27256,13 @@
         </is>
       </c>
       <c r="L35" s="52" t="n">
-        <v>1.291982944</v>
+        <v>1.221615085716667</v>
       </c>
       <c r="M35" s="53" t="n">
-        <v>413.43</v>
+        <v>366.48</v>
       </c>
       <c r="N35" s="58" t="n">
-        <v>51.68</v>
+        <v>580.27</v>
       </c>
       <c r="O35" s="20" t="inlineStr">
         <is>
@@ -27273,24 +27273,24 @@
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="54" t="inlineStr">
         <is>
-          <t>C-GLB0005</t>
+          <t>AGZNP0001</t>
         </is>
       </c>
       <c r="B36" s="29" t="inlineStr">
         <is>
-          <t>CODIORGAN GLB, 5 KG</t>
+          <t>AGROXILATO-ZN PLUS</t>
         </is>
       </c>
       <c r="C36" s="29" t="inlineStr">
         <is>
-          <t>Bolsas 5 Kg</t>
+          <t>Bolsas 1 Kg</t>
         </is>
       </c>
       <c r="D36" s="34" t="n">
-        <v>255</v>
+        <v>128</v>
       </c>
       <c r="E36" s="33" t="n">
-        <v>51</v>
+        <v>128</v>
       </c>
       <c r="F36" s="33" t="n">
         <v>0</v>
@@ -27302,10 +27302,10 @@
         <v>0</v>
       </c>
       <c r="I36" s="34" t="n">
-        <v>255</v>
+        <v>128</v>
       </c>
       <c r="J36" s="33" t="n">
-        <v>51</v>
+        <v>128</v>
       </c>
       <c r="K36" s="26" t="inlineStr">
         <is>
@@ -27313,10 +27313,10 @@
         </is>
       </c>
       <c r="L36" s="55" t="n">
-        <v>1.575231243</v>
+        <v>2.7749204597</v>
       </c>
       <c r="M36" s="56" t="n">
-        <v>401.68</v>
+        <v>355.19</v>
       </c>
       <c r="N36" s="55" t="n">
         <v>0</v>
@@ -27330,12 +27330,12 @@
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="51" t="inlineStr">
         <is>
-          <t>AGRMG0005</t>
+          <t>S0005</t>
         </is>
       </c>
       <c r="B37" s="20" t="inlineStr">
         <is>
-          <t>AGROXIGREEN-MG, 5 L</t>
+          <t>SAL-WAX STAR, 5 L</t>
         </is>
       </c>
       <c r="C37" s="20" t="inlineStr">
@@ -27344,25 +27344,25 @@
         </is>
       </c>
       <c r="D37" s="25" t="n">
-        <v>775</v>
+        <v>540</v>
       </c>
       <c r="E37" s="24" t="n">
-        <v>155</v>
+        <v>108</v>
       </c>
       <c r="F37" s="24" t="n">
         <v>0</v>
       </c>
       <c r="G37" s="24" t="n">
-        <v>475</v>
+        <v>90</v>
       </c>
       <c r="H37" s="25" t="n">
-        <v>475</v>
+        <v>90</v>
       </c>
       <c r="I37" s="25" t="n">
-        <v>300</v>
+        <v>450</v>
       </c>
       <c r="J37" s="24" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="K37" s="26" t="inlineStr">
         <is>
@@ -27370,13 +27370,13 @@
         </is>
       </c>
       <c r="L37" s="52" t="n">
-        <v>1.221615086</v>
+        <v>0.73153612874</v>
       </c>
       <c r="M37" s="53" t="n">
-        <v>366.48</v>
+        <v>329.19</v>
       </c>
       <c r="N37" s="58" t="n">
-        <v>580.27</v>
+        <v>65.84</v>
       </c>
       <c r="O37" s="20" t="inlineStr">
         <is>
@@ -27387,39 +27387,39 @@
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="54" t="inlineStr">
         <is>
-          <t>AGZNP0001</t>
+          <t>HST0001</t>
         </is>
       </c>
       <c r="B38" s="29" t="inlineStr">
         <is>
-          <t>AGROXILATO-ZN PLUS</t>
+          <t>HIDROSTRESS, 1 L</t>
         </is>
       </c>
       <c r="C38" s="29" t="inlineStr">
         <is>
-          <t>Bolsas 1 Kg</t>
+          <t>Botellas 1L</t>
         </is>
       </c>
       <c r="D38" s="34" t="n">
-        <v>128</v>
+        <v>156</v>
       </c>
       <c r="E38" s="33" t="n">
-        <v>128</v>
+        <v>156</v>
       </c>
       <c r="F38" s="33" t="n">
         <v>0</v>
       </c>
       <c r="G38" s="33" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H38" s="34" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="I38" s="34" t="n">
-        <v>128</v>
+        <v>81</v>
       </c>
       <c r="J38" s="33" t="n">
-        <v>128</v>
+        <v>81</v>
       </c>
       <c r="K38" s="26" t="inlineStr">
         <is>
@@ -27427,56 +27427,56 @@
         </is>
       </c>
       <c r="L38" s="55" t="n">
-        <v>2.77492046</v>
+        <v>3.51905143415</v>
       </c>
       <c r="M38" s="56" t="n">
-        <v>355.19</v>
-      </c>
-      <c r="N38" s="55" t="n">
-        <v>0</v>
+        <v>285.04</v>
+      </c>
+      <c r="N38" s="57" t="n">
+        <v>263.93</v>
       </c>
       <c r="O38" s="29" t="inlineStr">
         <is>
-          <t>Sin Demanda Nacional (Inmovilizado Crítico)</t>
+          <t>Plan Choque Comercial Nac / Oferta</t>
         </is>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="51" t="inlineStr">
         <is>
-          <t>S0005</t>
+          <t>AVAN0001</t>
         </is>
       </c>
       <c r="B39" s="20" t="inlineStr">
         <is>
-          <t>SAL-WAX STAR, 5 L</t>
+          <t>CODI-FLOR AVANCE, 1 L</t>
         </is>
       </c>
       <c r="C39" s="20" t="inlineStr">
         <is>
-          <t>Garrafas 5L</t>
+          <t>Botellas 1L</t>
         </is>
       </c>
       <c r="D39" s="25" t="n">
-        <v>540</v>
+        <v>156</v>
       </c>
       <c r="E39" s="24" t="n">
-        <v>108</v>
+        <v>156</v>
       </c>
       <c r="F39" s="24" t="n">
         <v>0</v>
       </c>
       <c r="G39" s="24" t="n">
-        <v>90</v>
+        <v>43</v>
       </c>
       <c r="H39" s="25" t="n">
-        <v>90</v>
+        <v>43</v>
       </c>
       <c r="I39" s="25" t="n">
-        <v>450</v>
+        <v>113</v>
       </c>
       <c r="J39" s="24" t="n">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="K39" s="26" t="inlineStr">
         <is>
@@ -27484,13 +27484,13 @@
         </is>
       </c>
       <c r="L39" s="52" t="n">
-        <v>0.731536129</v>
+        <v>2.353785689983333</v>
       </c>
       <c r="M39" s="53" t="n">
-        <v>329.19</v>
+        <v>265.98</v>
       </c>
       <c r="N39" s="58" t="n">
-        <v>65.84</v>
+        <v>101.21</v>
       </c>
       <c r="O39" s="20" t="inlineStr">
         <is>
@@ -27501,12 +27501,12 @@
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="54" t="inlineStr">
         <is>
-          <t>HST0001</t>
+          <t>N0001</t>
         </is>
       </c>
       <c r="B40" s="29" t="inlineStr">
         <is>
-          <t>HIDROSTRESS, 1 L</t>
+          <t>NUTRICALE, 1 L</t>
         </is>
       </c>
       <c r="C40" s="29" t="inlineStr">
@@ -27515,25 +27515,25 @@
         </is>
       </c>
       <c r="D40" s="34" t="n">
-        <v>156</v>
+        <v>132</v>
       </c>
       <c r="E40" s="33" t="n">
-        <v>156</v>
+        <v>132</v>
       </c>
       <c r="F40" s="33" t="n">
         <v>0</v>
       </c>
       <c r="G40" s="33" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="H40" s="34" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="I40" s="34" t="n">
-        <v>81</v>
+        <v>132</v>
       </c>
       <c r="J40" s="33" t="n">
-        <v>81</v>
+        <v>132</v>
       </c>
       <c r="K40" s="26" t="inlineStr">
         <is>
@@ -27541,29 +27541,29 @@
         </is>
       </c>
       <c r="L40" s="55" t="n">
-        <v>3.519051434</v>
+        <v>1.6063003934</v>
       </c>
       <c r="M40" s="56" t="n">
-        <v>285.04</v>
-      </c>
-      <c r="N40" s="57" t="n">
-        <v>263.93</v>
+        <v>212.03</v>
+      </c>
+      <c r="N40" s="55" t="n">
+        <v>0</v>
       </c>
       <c r="O40" s="29" t="inlineStr">
         <is>
-          <t>Plan Choque Comercial Nac / Oferta</t>
+          <t>Sin Demanda Nacional (Inmovilizado Crítico)</t>
         </is>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="51" t="inlineStr">
         <is>
-          <t>AVAN0001</t>
+          <t>AQUOM0001</t>
         </is>
       </c>
       <c r="B41" s="20" t="inlineStr">
         <is>
-          <t>CODI-FLOR AVANCE, 1 L</t>
+          <t>AQUOM, 1 L</t>
         </is>
       </c>
       <c r="C41" s="20" t="inlineStr">
@@ -27572,25 +27572,25 @@
         </is>
       </c>
       <c r="D41" s="25" t="n">
-        <v>156</v>
+        <v>36</v>
       </c>
       <c r="E41" s="24" t="n">
-        <v>156</v>
+        <v>36</v>
       </c>
       <c r="F41" s="24" t="n">
         <v>0</v>
       </c>
       <c r="G41" s="24" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="H41" s="25" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="I41" s="25" t="n">
-        <v>113</v>
+        <v>36</v>
       </c>
       <c r="J41" s="24" t="n">
-        <v>113</v>
+        <v>36</v>
       </c>
       <c r="K41" s="26" t="inlineStr">
         <is>
@@ -27598,41 +27598,41 @@
         </is>
       </c>
       <c r="L41" s="52" t="n">
-        <v>2.35378569</v>
+        <v>5.280834965166666</v>
       </c>
       <c r="M41" s="53" t="n">
-        <v>265.98</v>
-      </c>
-      <c r="N41" s="58" t="n">
-        <v>101.21</v>
+        <v>190.11</v>
+      </c>
+      <c r="N41" s="52" t="n">
+        <v>0</v>
       </c>
       <c r="O41" s="20" t="inlineStr">
         <is>
-          <t>Plan Choque Comercial Nac / Oferta</t>
+          <t>Sin Demanda Nacional (Inmovilizado Crítico)</t>
         </is>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="54" t="inlineStr">
         <is>
-          <t>N0001</t>
+          <t>PIV0005</t>
         </is>
       </c>
       <c r="B42" s="29" t="inlineStr">
         <is>
-          <t>NUTRICALE, 1 L</t>
+          <t>PGR IV, 5 L</t>
         </is>
       </c>
       <c r="C42" s="29" t="inlineStr">
         <is>
-          <t>Botellas 1L</t>
+          <t>Garrafas 5L</t>
         </is>
       </c>
       <c r="D42" s="34" t="n">
-        <v>132</v>
+        <v>200</v>
       </c>
       <c r="E42" s="33" t="n">
-        <v>132</v>
+        <v>40</v>
       </c>
       <c r="F42" s="33" t="n">
         <v>0</v>
@@ -27644,10 +27644,10 @@
         <v>0</v>
       </c>
       <c r="I42" s="34" t="n">
-        <v>132</v>
+        <v>200</v>
       </c>
       <c r="J42" s="33" t="n">
-        <v>132</v>
+        <v>40</v>
       </c>
       <c r="K42" s="26" t="inlineStr">
         <is>
@@ -27655,10 +27655,10 @@
         </is>
       </c>
       <c r="L42" s="55" t="n">
-        <v>1.606300393</v>
+        <v>0.91922331745</v>
       </c>
       <c r="M42" s="56" t="n">
-        <v>212.03</v>
+        <v>183.84</v>
       </c>
       <c r="N42" s="55" t="n">
         <v>0</v>
@@ -27672,39 +27672,39 @@
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="51" t="inlineStr">
         <is>
-          <t>AQUOM0001</t>
+          <t>CSIL0005</t>
         </is>
       </c>
       <c r="B43" s="20" t="inlineStr">
         <is>
-          <t>AQUOM, 1 L</t>
+          <t>FITOKONTROL-K, 5 L</t>
         </is>
       </c>
       <c r="C43" s="20" t="inlineStr">
         <is>
-          <t>Botellas 1L</t>
+          <t>Garrafas 5L</t>
         </is>
       </c>
       <c r="D43" s="25" t="n">
-        <v>36</v>
+        <v>200</v>
       </c>
       <c r="E43" s="24" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F43" s="24" t="n">
         <v>0</v>
       </c>
       <c r="G43" s="24" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="H43" s="25" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="I43" s="25" t="n">
-        <v>36</v>
+        <v>135</v>
       </c>
       <c r="J43" s="24" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="K43" s="26" t="inlineStr">
         <is>
@@ -27712,44 +27712,44 @@
         </is>
       </c>
       <c r="L43" s="52" t="n">
-        <v>5.280834965</v>
+        <v>1.3194997025</v>
       </c>
       <c r="M43" s="53" t="n">
-        <v>190.11</v>
-      </c>
-      <c r="N43" s="52" t="n">
-        <v>0</v>
+        <v>178.13</v>
+      </c>
+      <c r="N43" s="58" t="n">
+        <v>85.77</v>
       </c>
       <c r="O43" s="20" t="inlineStr">
         <is>
-          <t>Sin Demanda Nacional (Inmovilizado Crítico)</t>
+          <t>Plan Choque Comercial Nac / Oferta</t>
         </is>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="54" t="inlineStr">
         <is>
-          <t>PIV0005</t>
+          <t>CBASI0005</t>
         </is>
       </c>
       <c r="B44" s="29" t="inlineStr">
         <is>
-          <t>PGR IV, 5 L</t>
+          <t>BIOCULTURE BASI, 5 KG</t>
         </is>
       </c>
       <c r="C44" s="29" t="inlineStr">
         <is>
-          <t>Garrafas 5L</t>
+          <t>Bolsas 5 Kg</t>
         </is>
       </c>
       <c r="D44" s="34" t="n">
-        <v>200</v>
+        <v>770</v>
       </c>
       <c r="E44" s="33" t="n">
-        <v>40</v>
+        <v>154</v>
       </c>
       <c r="F44" s="33" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="G44" s="33" t="n">
         <v>0</v>
@@ -27758,10 +27758,10 @@
         <v>0</v>
       </c>
       <c r="I44" s="34" t="n">
-        <v>200</v>
+        <v>270</v>
       </c>
       <c r="J44" s="33" t="n">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="K44" s="26" t="inlineStr">
         <is>
@@ -27769,56 +27769,56 @@
         </is>
       </c>
       <c r="L44" s="55" t="n">
-        <v>0.919223317</v>
+        <v>0.6385284237333333</v>
       </c>
       <c r="M44" s="56" t="n">
-        <v>183.84</v>
+        <v>172.4</v>
       </c>
       <c r="N44" s="55" t="n">
         <v>0</v>
       </c>
       <c r="O44" s="29" t="inlineStr">
         <is>
-          <t>Sin Demanda Nacional (Inmovilizado Crítico)</t>
+          <t>Plan Choque Comercial Nac / Oferta</t>
         </is>
       </c>
     </row>
     <row r="45" ht="20" customHeight="1">
       <c r="A45" s="51" t="inlineStr">
         <is>
-          <t>CSIL0005</t>
+          <t>BEY0020</t>
         </is>
       </c>
       <c r="B45" s="20" t="inlineStr">
         <is>
-          <t>FITOKONTROL-K, 5 L</t>
+          <t>FLORAMEC PLUS 20 L</t>
         </is>
       </c>
       <c r="C45" s="20" t="inlineStr">
         <is>
-          <t>Garrafas 5L</t>
+          <t>Garrafas 20L</t>
         </is>
       </c>
       <c r="D45" s="25" t="n">
-        <v>200</v>
+        <v>320</v>
       </c>
       <c r="E45" s="24" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="F45" s="24" t="n">
         <v>0</v>
       </c>
       <c r="G45" s="24" t="n">
-        <v>65</v>
+        <v>220</v>
       </c>
       <c r="H45" s="25" t="n">
-        <v>65</v>
+        <v>220</v>
       </c>
       <c r="I45" s="25" t="n">
-        <v>135</v>
+        <v>100</v>
       </c>
       <c r="J45" s="24" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="K45" s="26" t="inlineStr">
         <is>
@@ -27826,13 +27826,13 @@
         </is>
       </c>
       <c r="L45" s="52" t="n">
-        <v>1.319499703</v>
+        <v>1.4727117819</v>
       </c>
       <c r="M45" s="53" t="n">
-        <v>178.13</v>
+        <v>147.27</v>
       </c>
       <c r="N45" s="58" t="n">
-        <v>85.77</v>
+        <v>324</v>
       </c>
       <c r="O45" s="20" t="inlineStr">
         <is>
@@ -27843,39 +27843,39 @@
     <row r="46" ht="20" customHeight="1">
       <c r="A46" s="54" t="inlineStr">
         <is>
-          <t>CBASI0005</t>
+          <t>AGFEL0005</t>
         </is>
       </c>
       <c r="B46" s="29" t="inlineStr">
         <is>
-          <t>BIOCULTURE BASI, 5 KG</t>
+          <t>AGROXILATO-FE-L, 5 L</t>
         </is>
       </c>
       <c r="C46" s="29" t="inlineStr">
         <is>
-          <t>Bolsas 5 Kg</t>
+          <t>Garrafas 5L</t>
         </is>
       </c>
       <c r="D46" s="34" t="n">
-        <v>770</v>
+        <v>120</v>
       </c>
       <c r="E46" s="33" t="n">
-        <v>154</v>
+        <v>24</v>
       </c>
       <c r="F46" s="33" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="G46" s="33" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H46" s="34" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="I46" s="34" t="n">
-        <v>270</v>
+        <v>75</v>
       </c>
       <c r="J46" s="33" t="n">
-        <v>54</v>
+        <v>15</v>
       </c>
       <c r="K46" s="26" t="inlineStr">
         <is>
@@ -27883,13 +27883,13 @@
         </is>
       </c>
       <c r="L46" s="55" t="n">
-        <v>0.638528424</v>
+        <v>1.8076118286</v>
       </c>
       <c r="M46" s="56" t="n">
-        <v>172.4</v>
-      </c>
-      <c r="N46" s="55" t="n">
-        <v>0</v>
+        <v>135.57</v>
+      </c>
+      <c r="N46" s="57" t="n">
+        <v>81.34</v>
       </c>
       <c r="O46" s="29" t="inlineStr">
         <is>
@@ -27900,12 +27900,12 @@
     <row r="47" ht="20" customHeight="1">
       <c r="A47" s="51" t="inlineStr">
         <is>
-          <t>BEY0020</t>
+          <t>FLOR0020</t>
         </is>
       </c>
       <c r="B47" s="20" t="inlineStr">
         <is>
-          <t>FLORAMEC PLUS 20 L</t>
+          <t>FLORAMEC, 20 L</t>
         </is>
       </c>
       <c r="C47" s="20" t="inlineStr">
@@ -27914,25 +27914,25 @@
         </is>
       </c>
       <c r="D47" s="25" t="n">
-        <v>320</v>
+        <v>140</v>
       </c>
       <c r="E47" s="24" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="F47" s="24" t="n">
         <v>0</v>
       </c>
       <c r="G47" s="24" t="n">
-        <v>220</v>
+        <v>0</v>
       </c>
       <c r="H47" s="25" t="n">
-        <v>220</v>
+        <v>0</v>
       </c>
       <c r="I47" s="25" t="n">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="J47" s="24" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K47" s="26" t="inlineStr">
         <is>
@@ -27940,56 +27940,56 @@
         </is>
       </c>
       <c r="L47" s="52" t="n">
-        <v>1.472711782</v>
+        <v>0.84296316745</v>
       </c>
       <c r="M47" s="53" t="n">
-        <v>147.27</v>
-      </c>
-      <c r="N47" s="58" t="n">
-        <v>324</v>
+        <v>118.01</v>
+      </c>
+      <c r="N47" s="52" t="n">
+        <v>0</v>
       </c>
       <c r="O47" s="20" t="inlineStr">
         <is>
-          <t>Plan Choque Comercial Nac / Oferta</t>
+          <t>Sin Demanda Nacional (Inmovilizado Crítico)</t>
         </is>
       </c>
     </row>
     <row r="48" ht="20" customHeight="1">
       <c r="A48" s="54" t="inlineStr">
         <is>
-          <t>AGFEL0005</t>
+          <t>CSIL0020</t>
         </is>
       </c>
       <c r="B48" s="29" t="inlineStr">
         <is>
-          <t>AGROXILATO-FE-L, 5 L</t>
+          <t>FITOKONTROL-K, 20 L</t>
         </is>
       </c>
       <c r="C48" s="29" t="inlineStr">
         <is>
-          <t>Garrafas 5L</t>
+          <t>Garrafas 20L</t>
         </is>
       </c>
       <c r="D48" s="34" t="n">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="E48" s="33" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="F48" s="33" t="n">
         <v>0</v>
       </c>
       <c r="G48" s="33" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="H48" s="34" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="I48" s="34" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="J48" s="33" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="K48" s="26" t="inlineStr">
         <is>
@@ -27997,56 +27997,56 @@
         </is>
       </c>
       <c r="L48" s="55" t="n">
-        <v>1.807611829</v>
+        <v>1.3788359114</v>
       </c>
       <c r="M48" s="56" t="n">
-        <v>135.57</v>
-      </c>
-      <c r="N48" s="57" t="n">
-        <v>81.34</v>
+        <v>110.31</v>
+      </c>
+      <c r="N48" s="55" t="n">
+        <v>0</v>
       </c>
       <c r="O48" s="29" t="inlineStr">
         <is>
-          <t>Plan Choque Comercial Nac / Oferta</t>
+          <t>Sin Demanda Nacional (Inmovilizado Crítico)</t>
         </is>
       </c>
     </row>
     <row r="49" ht="20" customHeight="1">
       <c r="A49" s="51" t="inlineStr">
         <is>
-          <t>FLOR0020</t>
+          <t>AMIMG0005</t>
         </is>
       </c>
       <c r="B49" s="20" t="inlineStr">
         <is>
-          <t>FLORAMEC, 20 L</t>
+          <t>AMINOSOIL-MG, 5L</t>
         </is>
       </c>
       <c r="C49" s="20" t="inlineStr">
         <is>
-          <t>Garrafas 20L</t>
+          <t>Garrafas 5L</t>
         </is>
       </c>
       <c r="D49" s="25" t="n">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="E49" s="24" t="n">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="F49" s="24" t="n">
         <v>0</v>
       </c>
       <c r="G49" s="24" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H49" s="25" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="I49" s="25" t="n">
-        <v>140</v>
+        <v>115</v>
       </c>
       <c r="J49" s="24" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="K49" s="26" t="inlineStr">
         <is>
@@ -28054,56 +28054,56 @@
         </is>
       </c>
       <c r="L49" s="52" t="n">
-        <v>0.842963167</v>
+        <v>0.8984652147000001</v>
       </c>
       <c r="M49" s="53" t="n">
-        <v>118.01</v>
-      </c>
-      <c r="N49" s="52" t="n">
-        <v>0</v>
+        <v>103.32</v>
+      </c>
+      <c r="N49" s="58" t="n">
+        <v>40.43</v>
       </c>
       <c r="O49" s="20" t="inlineStr">
         <is>
-          <t>Sin Demanda Nacional (Inmovilizado Crítico)</t>
+          <t>Plan Choque Comercial Nac / Oferta</t>
         </is>
       </c>
     </row>
     <row r="50" ht="20" customHeight="1">
       <c r="A50" s="54" t="inlineStr">
         <is>
-          <t>CSIL0020</t>
+          <t>BC0020</t>
         </is>
       </c>
       <c r="B50" s="29" t="inlineStr">
         <is>
-          <t>FITOKONTROL-K, 20 L</t>
+          <t>BITTER-CAL, 20 KG</t>
         </is>
       </c>
       <c r="C50" s="29" t="inlineStr">
         <is>
-          <t>Garrafas 20L</t>
+          <t>Bolsas 20 Kg</t>
         </is>
       </c>
       <c r="D50" s="34" t="n">
-        <v>80</v>
+        <v>200</v>
       </c>
       <c r="E50" s="33" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F50" s="33" t="n">
         <v>0</v>
       </c>
       <c r="G50" s="33" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H50" s="34" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I50" s="34" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="J50" s="33" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K50" s="26" t="inlineStr">
         <is>
@@ -28111,56 +28111,56 @@
         </is>
       </c>
       <c r="L50" s="55" t="n">
-        <v>1.378835911</v>
+        <v>1.0160069743</v>
       </c>
       <c r="M50" s="56" t="n">
-        <v>110.31</v>
-      </c>
-      <c r="N50" s="55" t="n">
-        <v>0</v>
+        <v>101.6</v>
+      </c>
+      <c r="N50" s="57" t="n">
+        <v>101.6</v>
       </c>
       <c r="O50" s="29" t="inlineStr">
         <is>
-          <t>Sin Demanda Nacional (Inmovilizado Crítico)</t>
+          <t>Plan Choque Comercial Nac / Oferta</t>
         </is>
       </c>
     </row>
     <row r="51" ht="20" customHeight="1">
       <c r="A51" s="51" t="inlineStr">
         <is>
-          <t>AMIMG0005</t>
+          <t>AGN0020</t>
         </is>
       </c>
       <c r="B51" s="20" t="inlineStr">
         <is>
-          <t>AMINOSOIL-MG, 5L</t>
+          <t>AGROXILATO N, 20 L</t>
         </is>
       </c>
       <c r="C51" s="20" t="inlineStr">
         <is>
-          <t>Garrafas 5L</t>
+          <t>Garrafas 20L</t>
         </is>
       </c>
       <c r="D51" s="25" t="n">
-        <v>160</v>
+        <v>200</v>
       </c>
       <c r="E51" s="24" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="F51" s="24" t="n">
         <v>0</v>
       </c>
       <c r="G51" s="24" t="n">
-        <v>45</v>
+        <v>100</v>
       </c>
       <c r="H51" s="25" t="n">
-        <v>45</v>
+        <v>100</v>
       </c>
       <c r="I51" s="25" t="n">
-        <v>115</v>
+        <v>100</v>
       </c>
       <c r="J51" s="24" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="K51" s="26" t="inlineStr">
         <is>
@@ -28168,13 +28168,13 @@
         </is>
       </c>
       <c r="L51" s="52" t="n">
-        <v>0.898465215</v>
+        <v>0.9350928853</v>
       </c>
       <c r="M51" s="53" t="n">
-        <v>103.32</v>
+        <v>93.51000000000001</v>
       </c>
       <c r="N51" s="58" t="n">
-        <v>40.43</v>
+        <v>93.51000000000001</v>
       </c>
       <c r="O51" s="20" t="inlineStr">
         <is>
@@ -28185,12 +28185,12 @@
     <row r="52" ht="20" customHeight="1">
       <c r="A52" s="54" t="inlineStr">
         <is>
-          <t>BC0020</t>
+          <t>ANAE0020</t>
         </is>
       </c>
       <c r="B52" s="29" t="inlineStr">
         <is>
-          <t>BITTER-CAL, 20 KG</t>
+          <t>ALCAPLANT NEW AE, 20 KG</t>
         </is>
       </c>
       <c r="C52" s="29" t="inlineStr">
@@ -28199,25 +28199,25 @@
         </is>
       </c>
       <c r="D52" s="34" t="n">
-        <v>200</v>
+        <v>12720</v>
       </c>
       <c r="E52" s="33" t="n">
-        <v>10</v>
+        <v>636</v>
       </c>
       <c r="F52" s="33" t="n">
-        <v>0</v>
+        <v>7700</v>
       </c>
       <c r="G52" s="33" t="n">
-        <v>100</v>
+        <v>4800</v>
       </c>
       <c r="H52" s="34" t="n">
-        <v>100</v>
+        <v>4800</v>
       </c>
       <c r="I52" s="34" t="n">
-        <v>100</v>
+        <v>220</v>
       </c>
       <c r="J52" s="33" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="K52" s="26" t="inlineStr">
         <is>
@@ -28225,13 +28225,13 @@
         </is>
       </c>
       <c r="L52" s="55" t="n">
-        <v>1.016006974</v>
+        <v>0.40963406676</v>
       </c>
       <c r="M52" s="56" t="n">
-        <v>101.6</v>
+        <v>90.12</v>
       </c>
       <c r="N52" s="57" t="n">
-        <v>101.6</v>
+        <v>1966.24</v>
       </c>
       <c r="O52" s="29" t="inlineStr">
         <is>
@@ -28242,21 +28242,21 @@
     <row r="53" ht="20" customHeight="1">
       <c r="A53" s="51" t="inlineStr">
         <is>
-          <t>AGN0020</t>
+          <t>CZNMNES0005</t>
         </is>
       </c>
       <c r="B53" s="20" t="inlineStr">
         <is>
-          <t>AGROXILATO N, 20 L</t>
+          <t>CODIFOL ZN-MN, 5 KG</t>
         </is>
       </c>
       <c r="C53" s="20" t="inlineStr">
         <is>
-          <t>Garrafas 20L</t>
+          <t>Bolsas 5 Kg</t>
         </is>
       </c>
       <c r="D53" s="25" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="E53" s="24" t="n">
         <v>10</v>
@@ -28265,16 +28265,16 @@
         <v>0</v>
       </c>
       <c r="G53" s="24" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H53" s="25" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I53" s="25" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="J53" s="24" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="K53" s="26" t="inlineStr">
         <is>
@@ -28282,56 +28282,56 @@
         </is>
       </c>
       <c r="L53" s="52" t="n">
-        <v>0.935092885</v>
+        <v>1.79870393195</v>
       </c>
       <c r="M53" s="53" t="n">
-        <v>93.51000000000001</v>
-      </c>
-      <c r="N53" s="58" t="n">
-        <v>93.51000000000001</v>
+        <v>89.94</v>
+      </c>
+      <c r="N53" s="52" t="n">
+        <v>0</v>
       </c>
       <c r="O53" s="20" t="inlineStr">
         <is>
-          <t>Plan Choque Comercial Nac / Oferta</t>
+          <t>Sin Demanda Nacional (Inmovilizado Crítico)</t>
         </is>
       </c>
     </row>
     <row r="54" ht="20" customHeight="1">
       <c r="A54" s="54" t="inlineStr">
         <is>
-          <t>CZNMNES0005</t>
+          <t>PHD0001</t>
         </is>
       </c>
       <c r="B54" s="29" t="inlineStr">
         <is>
-          <t>CODIFOL ZN-MN, 5 KG</t>
+          <t>PH-DOWNER</t>
         </is>
       </c>
       <c r="C54" s="29" t="inlineStr">
         <is>
-          <t>Bolsas 5 Kg</t>
+          <t>Botellas 1L</t>
         </is>
       </c>
       <c r="D54" s="34" t="n">
-        <v>50</v>
+        <v>144</v>
       </c>
       <c r="E54" s="33" t="n">
-        <v>10</v>
+        <v>144</v>
       </c>
       <c r="F54" s="33" t="n">
         <v>0</v>
       </c>
       <c r="G54" s="33" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="H54" s="34" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="I54" s="34" t="n">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="J54" s="33" t="n">
-        <v>10</v>
+        <v>67</v>
       </c>
       <c r="K54" s="26" t="inlineStr">
         <is>
@@ -28339,29 +28339,29 @@
         </is>
       </c>
       <c r="L54" s="55" t="n">
-        <v>1.798703932</v>
+        <v>1.310016923833333</v>
       </c>
       <c r="M54" s="56" t="n">
-        <v>89.94</v>
-      </c>
-      <c r="N54" s="55" t="n">
-        <v>0</v>
+        <v>87.77</v>
+      </c>
+      <c r="N54" s="57" t="n">
+        <v>100.87</v>
       </c>
       <c r="O54" s="29" t="inlineStr">
         <is>
-          <t>Sin Demanda Nacional (Inmovilizado Crítico)</t>
+          <t>Plan Choque Comercial Nac / Oferta</t>
         </is>
       </c>
     </row>
     <row r="55" ht="20" customHeight="1">
       <c r="A55" s="51" t="inlineStr">
         <is>
-          <t>PHD0001</t>
+          <t>BROTA0001</t>
         </is>
       </c>
       <c r="B55" s="20" t="inlineStr">
         <is>
-          <t>PH-DOWNER</t>
+          <t>BROTAMEC, 1 L</t>
         </is>
       </c>
       <c r="C55" s="20" t="inlineStr">
@@ -28370,25 +28370,25 @@
         </is>
       </c>
       <c r="D55" s="25" t="n">
-        <v>144</v>
+        <v>48</v>
       </c>
       <c r="E55" s="24" t="n">
-        <v>144</v>
+        <v>48</v>
       </c>
       <c r="F55" s="24" t="n">
         <v>0</v>
       </c>
       <c r="G55" s="24" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="H55" s="25" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="I55" s="25" t="n">
-        <v>67</v>
+        <v>48</v>
       </c>
       <c r="J55" s="24" t="n">
-        <v>67</v>
+        <v>48</v>
       </c>
       <c r="K55" s="26" t="inlineStr">
         <is>
@@ -28396,29 +28396,29 @@
         </is>
       </c>
       <c r="L55" s="52" t="n">
-        <v>1.310016924</v>
+        <v>1.6976719709</v>
       </c>
       <c r="M55" s="53" t="n">
-        <v>87.77</v>
-      </c>
-      <c r="N55" s="58" t="n">
-        <v>100.87</v>
+        <v>81.48999999999999</v>
+      </c>
+      <c r="N55" s="52" t="n">
+        <v>0</v>
       </c>
       <c r="O55" s="20" t="inlineStr">
         <is>
-          <t>Plan Choque Comercial Nac / Oferta</t>
+          <t>Sin Demanda Nacional (Inmovilizado Crítico)</t>
         </is>
       </c>
     </row>
     <row r="56" ht="20" customHeight="1">
       <c r="A56" s="54" t="inlineStr">
         <is>
-          <t>BROTA0001</t>
+          <t>CODIR0001</t>
         </is>
       </c>
       <c r="B56" s="29" t="inlineStr">
         <is>
-          <t>BROTAMEC, 1 L</t>
+          <t>CODIRESIST, 1 L</t>
         </is>
       </c>
       <c r="C56" s="29" t="inlineStr">
@@ -28427,10 +28427,10 @@
         </is>
       </c>
       <c r="D56" s="34" t="n">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="E56" s="33" t="n">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="F56" s="33" t="n">
         <v>0</v>
@@ -28442,10 +28442,10 @@
         <v>0</v>
       </c>
       <c r="I56" s="34" t="n">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="J56" s="33" t="n">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="K56" s="26" t="inlineStr">
         <is>
@@ -28453,10 +28453,10 @@
         </is>
       </c>
       <c r="L56" s="55" t="n">
-        <v>1.697671971</v>
+        <v>2.5953579061</v>
       </c>
       <c r="M56" s="56" t="n">
-        <v>81.48999999999999</v>
+        <v>59.69</v>
       </c>
       <c r="N56" s="55" t="n">
         <v>0</v>
@@ -28470,24 +28470,24 @@
     <row r="57" ht="20" customHeight="1">
       <c r="A57" s="51" t="inlineStr">
         <is>
-          <t>CODIR0001</t>
+          <t>BAYCAL0020</t>
         </is>
       </c>
       <c r="B57" s="20" t="inlineStr">
         <is>
-          <t>CODIRESIST, 1 L</t>
+          <t>BAYFOLAN CALCIO</t>
         </is>
       </c>
       <c r="C57" s="20" t="inlineStr">
         <is>
-          <t>Botellas 1L</t>
+          <t>Garrafas 20L</t>
         </is>
       </c>
       <c r="D57" s="25" t="n">
-        <v>23</v>
+        <v>100</v>
       </c>
       <c r="E57" s="24" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="F57" s="24" t="n">
         <v>0</v>
@@ -28499,10 +28499,10 @@
         <v>0</v>
       </c>
       <c r="I57" s="25" t="n">
-        <v>23</v>
+        <v>100</v>
       </c>
       <c r="J57" s="24" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="K57" s="26" t="inlineStr">
         <is>
@@ -28510,10 +28510,10 @@
         </is>
       </c>
       <c r="L57" s="52" t="n">
-        <v>2.595357906</v>
+        <v>0.50729927155</v>
       </c>
       <c r="M57" s="53" t="n">
-        <v>59.69</v>
+        <v>50.73</v>
       </c>
       <c r="N57" s="52" t="n">
         <v>0</v>
@@ -28527,24 +28527,24 @@
     <row r="58" ht="20" customHeight="1">
       <c r="A58" s="54" t="inlineStr">
         <is>
-          <t>BAYCAL0020</t>
+          <t>CSIL0001</t>
         </is>
       </c>
       <c r="B58" s="29" t="inlineStr">
         <is>
-          <t>BAYFOLAN CALCIO</t>
+          <t>FITOKONTROL-K, 1 L</t>
         </is>
       </c>
       <c r="C58" s="29" t="inlineStr">
         <is>
-          <t>Garrafas 20L</t>
+          <t>Botellas 1L</t>
         </is>
       </c>
       <c r="D58" s="34" t="n">
-        <v>100</v>
+        <v>24</v>
       </c>
       <c r="E58" s="33" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="F58" s="33" t="n">
         <v>0</v>
@@ -28556,10 +28556,10 @@
         <v>0</v>
       </c>
       <c r="I58" s="34" t="n">
-        <v>100</v>
+        <v>24</v>
       </c>
       <c r="J58" s="33" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="K58" s="26" t="inlineStr">
         <is>
@@ -28567,10 +28567,10 @@
         </is>
       </c>
       <c r="L58" s="55" t="n">
-        <v>0.507299272</v>
+        <v>2.0754295559</v>
       </c>
       <c r="M58" s="56" t="n">
-        <v>50.73</v>
+        <v>49.81</v>
       </c>
       <c r="N58" s="55" t="n">
         <v>0</v>
@@ -28584,24 +28584,24 @@
     <row r="59" ht="20" customHeight="1">
       <c r="A59" s="51" t="inlineStr">
         <is>
-          <t>CSIL0001</t>
+          <t>AQUOMAR0005</t>
         </is>
       </c>
       <c r="B59" s="20" t="inlineStr">
         <is>
-          <t>FITOKONTROL-K, 1 L</t>
+          <t>AQUOM ARABIA, 5 L</t>
         </is>
       </c>
       <c r="C59" s="20" t="inlineStr">
         <is>
-          <t>Botellas 1L</t>
+          <t>Garrafas 5L</t>
         </is>
       </c>
       <c r="D59" s="25" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="E59" s="24" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="F59" s="24" t="n">
         <v>0</v>
@@ -28613,10 +28613,10 @@
         <v>0</v>
       </c>
       <c r="I59" s="25" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="J59" s="24" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="K59" s="26" t="inlineStr">
         <is>
@@ -28624,10 +28624,10 @@
         </is>
       </c>
       <c r="L59" s="52" t="n">
-        <v>2.075429556</v>
+        <v>3.07884919875</v>
       </c>
       <c r="M59" s="53" t="n">
-        <v>49.81</v>
+        <v>46.18</v>
       </c>
       <c r="N59" s="52" t="n">
         <v>0</v>
@@ -28641,90 +28641,90 @@
     <row r="60" ht="20" customHeight="1">
       <c r="A60" s="54" t="inlineStr">
         <is>
-          <t>AQUOMAR0005</t>
+          <t>FTK0005</t>
         </is>
       </c>
       <c r="B60" s="29" t="inlineStr">
         <is>
-          <t>AQUOM ARABIA, 5 L</t>
+          <t>FITOKONTROL CA FLOW, 5 KG</t>
         </is>
       </c>
       <c r="C60" s="29" t="inlineStr">
         <is>
-          <t>Garrafas 5L</t>
+          <t>Bolsas 5 Kg</t>
         </is>
       </c>
       <c r="D60" s="34" t="n">
-        <v>15</v>
+        <v>5740</v>
       </c>
       <c r="E60" s="33" t="n">
-        <v>3</v>
+        <v>1148</v>
       </c>
       <c r="F60" s="33" t="n">
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="G60" s="33" t="n">
-        <v>0</v>
+        <v>3765</v>
       </c>
       <c r="H60" s="34" t="n">
-        <v>0</v>
+        <v>3640</v>
       </c>
       <c r="I60" s="34" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J60" s="33" t="n">
-        <v>3</v>
-      </c>
-      <c r="K60" s="26" t="inlineStr">
-        <is>
-          <t>🔴 NoMover (&gt;6M Nac)</t>
+        <v>0</v>
+      </c>
+      <c r="K60" s="35" t="inlineStr">
+        <is>
+          <t>🟡 SlowMover (3-6M Nac)</t>
         </is>
       </c>
       <c r="L60" s="55" t="n">
-        <v>3.078849199</v>
-      </c>
-      <c r="M60" s="56" t="n">
-        <v>46.18</v>
-      </c>
-      <c r="N60" s="55" t="n">
-        <v>0</v>
+        <v>1.029142978536363</v>
+      </c>
+      <c r="M60" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" s="57" t="n">
+        <v>3746.08</v>
       </c>
       <c r="O60" s="29" t="inlineStr">
         <is>
-          <t>Sin Demanda Nacional (Inmovilizado Crítico)</t>
+          <t>Consumo previsto en Q1-27 Nacional</t>
         </is>
       </c>
     </row>
     <row r="61" ht="20" customHeight="1">
       <c r="A61" s="51" t="inlineStr">
         <is>
-          <t>FTK0005</t>
+          <t>S0200</t>
         </is>
       </c>
       <c r="B61" s="20" t="inlineStr">
         <is>
-          <t>FITOKONTROL CA FLOW, 5 KG</t>
+          <t>SAL-WAX STAR, 200 L</t>
         </is>
       </c>
       <c r="C61" s="20" t="inlineStr">
         <is>
-          <t>Bolsas 5 Kg</t>
+          <t>Depósito 200 L</t>
         </is>
       </c>
       <c r="D61" s="25" t="n">
-        <v>5690</v>
+        <v>8800</v>
       </c>
       <c r="E61" s="24" t="n">
-        <v>1138</v>
+        <v>44</v>
       </c>
       <c r="F61" s="24" t="n">
-        <v>2100</v>
+        <v>5600</v>
       </c>
       <c r="G61" s="24" t="n">
-        <v>3765</v>
+        <v>4000</v>
       </c>
       <c r="H61" s="25" t="n">
-        <v>3590</v>
+        <v>3200</v>
       </c>
       <c r="I61" s="25" t="n">
         <v>0</v>
@@ -28738,13 +28738,13 @@
         </is>
       </c>
       <c r="L61" s="52" t="n">
-        <v>0.943381064</v>
+        <v>0.5342801332</v>
       </c>
       <c r="M61" s="52" t="n">
         <v>0</v>
       </c>
       <c r="N61" s="58" t="n">
-        <v>3386.74</v>
+        <v>1709.7</v>
       </c>
       <c r="O61" s="20" t="inlineStr">
         <is>
@@ -28795,7 +28795,7 @@
         </is>
       </c>
       <c r="L62" s="55" t="n">
-        <v>1.024698561</v>
+        <v>1.02469856052</v>
       </c>
       <c r="M62" s="55" t="n">
         <v>0</v>
@@ -28852,7 +28852,7 @@
         </is>
       </c>
       <c r="L63" s="52" t="n">
-        <v>0.7844144240000001</v>
+        <v>0.7844144242166667</v>
       </c>
       <c r="M63" s="52" t="n">
         <v>0</v>
@@ -28909,7 +28909,7 @@
         </is>
       </c>
       <c r="L64" s="55" t="n">
-        <v>0.853770569</v>
+        <v>0.8537705687200001</v>
       </c>
       <c r="M64" s="55" t="n">
         <v>0</v>
@@ -28966,7 +28966,7 @@
         </is>
       </c>
       <c r="L65" s="52" t="n">
-        <v>3.649516076</v>
+        <v>3.649516075533333</v>
       </c>
       <c r="M65" s="52" t="n">
         <v>0</v>
@@ -29023,7 +29023,7 @@
         </is>
       </c>
       <c r="L66" s="55" t="n">
-        <v>0.677553916</v>
+        <v>0.6775539158999999</v>
       </c>
       <c r="M66" s="55" t="n">
         <v>0</v>
@@ -29080,7 +29080,7 @@
         </is>
       </c>
       <c r="L67" s="52" t="n">
-        <v>1.517011545</v>
+        <v>1.5170115445</v>
       </c>
       <c r="M67" s="52" t="n">
         <v>0</v>
@@ -29137,7 +29137,7 @@
         </is>
       </c>
       <c r="L68" s="55" t="n">
-        <v>0.697021385</v>
+        <v>0.6970213848333332</v>
       </c>
       <c r="M68" s="55" t="n">
         <v>0</v>
@@ -29194,7 +29194,7 @@
         </is>
       </c>
       <c r="L69" s="52" t="n">
-        <v>1.930734655</v>
+        <v>1.9307346551</v>
       </c>
       <c r="M69" s="52" t="n">
         <v>0</v>
@@ -29251,7 +29251,7 @@
         </is>
       </c>
       <c r="L70" s="55" t="n">
-        <v>1.70253852</v>
+        <v>1.702538519866667</v>
       </c>
       <c r="M70" s="55" t="n">
         <v>0</v>
@@ -29308,7 +29308,7 @@
         </is>
       </c>
       <c r="L71" s="52" t="n">
-        <v>1.736254358</v>
+        <v>1.7362543577375</v>
       </c>
       <c r="M71" s="52" t="n">
         <v>0</v>
@@ -29365,7 +29365,7 @@
         </is>
       </c>
       <c r="L72" s="55" t="n">
-        <v>1.173409957</v>
+        <v>1.1734099569</v>
       </c>
       <c r="M72" s="55" t="n">
         <v>0</v>
@@ -29422,7 +29422,7 @@
         </is>
       </c>
       <c r="L73" s="52" t="n">
-        <v>0.8198929780000001</v>
+        <v>0.81989297845</v>
       </c>
       <c r="M73" s="52" t="n">
         <v>0</v>
@@ -29479,7 +29479,7 @@
         </is>
       </c>
       <c r="L74" s="55" t="n">
-        <v>4.062569483</v>
+        <v>4.0625694832</v>
       </c>
       <c r="M74" s="55" t="n">
         <v>0</v>
@@ -29536,7 +29536,7 @@
         </is>
       </c>
       <c r="L75" s="52" t="n">
-        <v>3.323017189</v>
+        <v>3.323017188642857</v>
       </c>
       <c r="M75" s="52" t="n">
         <v>0</v>
@@ -29593,7 +29593,7 @@
         </is>
       </c>
       <c r="L76" s="55" t="n">
-        <v>1.139496735</v>
+        <v>1.13949673532</v>
       </c>
       <c r="M76" s="55" t="n">
         <v>0</v>
@@ -29650,7 +29650,7 @@
         </is>
       </c>
       <c r="L77" s="52" t="n">
-        <v>1.207436703</v>
+        <v>1.207436703033333</v>
       </c>
       <c r="M77" s="52" t="n">
         <v>0</v>
@@ -29707,7 +29707,7 @@
         </is>
       </c>
       <c r="L78" s="55" t="n">
-        <v>1.577293392</v>
+        <v>1.577293392233333</v>
       </c>
       <c r="M78" s="55" t="n">
         <v>0</v>
@@ -29764,7 +29764,7 @@
         </is>
       </c>
       <c r="L79" s="52" t="n">
-        <v>3.84780613</v>
+        <v>3.8478061295</v>
       </c>
       <c r="M79" s="52" t="n">
         <v>0</v>
@@ -29821,7 +29821,7 @@
         </is>
       </c>
       <c r="L80" s="55" t="n">
-        <v>1.053796262</v>
+        <v>1.0537962621</v>
       </c>
       <c r="M80" s="55" t="n">
         <v>0</v>
@@ -29878,7 +29878,7 @@
         </is>
       </c>
       <c r="L81" s="52" t="n">
-        <v>4.116960542</v>
+        <v>4.1169605421</v>
       </c>
       <c r="M81" s="52" t="n">
         <v>0</v>
@@ -29935,7 +29935,7 @@
         </is>
       </c>
       <c r="L82" s="55" t="n">
-        <v>2.629153095</v>
+        <v>2.6291530954</v>
       </c>
       <c r="M82" s="55" t="n">
         <v>0</v>
@@ -29992,7 +29992,7 @@
         </is>
       </c>
       <c r="L83" s="52" t="n">
-        <v>2.447821718</v>
+        <v>2.44782171755</v>
       </c>
       <c r="M83" s="52" t="n">
         <v>0</v>
@@ -30049,7 +30049,7 @@
         </is>
       </c>
       <c r="L84" s="55" t="n">
-        <v>1.830787849</v>
+        <v>1.83078784908</v>
       </c>
       <c r="M84" s="55" t="n">
         <v>0</v>
@@ -30106,7 +30106,7 @@
         </is>
       </c>
       <c r="L85" s="52" t="n">
-        <v>2.102549663</v>
+        <v>2.1025496629</v>
       </c>
       <c r="M85" s="52" t="n">
         <v>0</v>
@@ -30163,7 +30163,7 @@
         </is>
       </c>
       <c r="L86" s="55" t="n">
-        <v>9.755021372</v>
+        <v>9.755021372250001</v>
       </c>
       <c r="M86" s="55" t="n">
         <v>0</v>
@@ -30220,7 +30220,7 @@
         </is>
       </c>
       <c r="L87" s="52" t="n">
-        <v>1.88519534</v>
+        <v>1.88519533995</v>
       </c>
       <c r="M87" s="52" t="n">
         <v>0</v>
@@ -30251,10 +30251,10 @@
         </is>
       </c>
       <c r="D88" s="34" t="n">
-        <v>10640</v>
+        <v>10440</v>
       </c>
       <c r="E88" s="33" t="n">
-        <v>532</v>
+        <v>522</v>
       </c>
       <c r="F88" s="33" t="n">
         <v>13080</v>
@@ -30277,7 +30277,7 @@
         </is>
       </c>
       <c r="L88" s="55" t="n">
-        <v>0.82548993</v>
+        <v>0.8254899297823528</v>
       </c>
       <c r="M88" s="55" t="n">
         <v>0</v>
@@ -30334,7 +30334,7 @@
         </is>
       </c>
       <c r="L89" s="52" t="n">
-        <v>1.125647362</v>
+        <v>1.1256473616</v>
       </c>
       <c r="M89" s="52" t="n">
         <v>0</v>
@@ -30391,7 +30391,7 @@
         </is>
       </c>
       <c r="L90" s="55" t="n">
-        <v>0.715896795</v>
+        <v>0.7158967949666666</v>
       </c>
       <c r="M90" s="55" t="n">
         <v>0</v>
@@ -30422,10 +30422,10 @@
         </is>
       </c>
       <c r="D91" s="25" t="n">
-        <v>13980</v>
+        <v>13880</v>
       </c>
       <c r="E91" s="24" t="n">
-        <v>699</v>
+        <v>694</v>
       </c>
       <c r="F91" s="24" t="n">
         <v>15660</v>
@@ -30448,7 +30448,7 @@
         </is>
       </c>
       <c r="L91" s="52" t="n">
-        <v>1.035782567</v>
+        <v>1.035782567073333</v>
       </c>
       <c r="M91" s="52" t="n">
         <v>0</v>
@@ -30479,10 +30479,10 @@
         </is>
       </c>
       <c r="D92" s="34" t="n">
-        <v>20060</v>
+        <v>21340</v>
       </c>
       <c r="E92" s="33" t="n">
-        <v>1003</v>
+        <v>1067</v>
       </c>
       <c r="F92" s="33" t="n">
         <v>52600</v>
@@ -30505,7 +30505,7 @@
         </is>
       </c>
       <c r="L92" s="55" t="n">
-        <v>0.852102507</v>
+        <v>0.8922922821444443</v>
       </c>
       <c r="M92" s="55" t="n">
         <v>0</v>
@@ -30562,7 +30562,7 @@
         </is>
       </c>
       <c r="L93" s="52" t="n">
-        <v>0.72122703</v>
+        <v>0.7212270296</v>
       </c>
       <c r="M93" s="52" t="n">
         <v>0</v>
@@ -30593,10 +30593,10 @@
         </is>
       </c>
       <c r="D94" s="34" t="n">
-        <v>29200</v>
+        <v>25900</v>
       </c>
       <c r="E94" s="33" t="n">
-        <v>1460</v>
+        <v>1295</v>
       </c>
       <c r="F94" s="33" t="n">
         <v>30100</v>
@@ -30619,7 +30619,7 @@
         </is>
       </c>
       <c r="L94" s="55" t="n">
-        <v>0.392857608</v>
+        <v>0.3928576077272726</v>
       </c>
       <c r="M94" s="55" t="n">
         <v>0</v>
@@ -30676,7 +30676,7 @@
         </is>
       </c>
       <c r="L95" s="52" t="n">
-        <v>1.421740492</v>
+        <v>1.4217404923</v>
       </c>
       <c r="M95" s="52" t="n">
         <v>0</v>
@@ -30707,10 +30707,10 @@
         </is>
       </c>
       <c r="D96" s="34" t="n">
-        <v>3160</v>
+        <v>5080</v>
       </c>
       <c r="E96" s="33" t="n">
-        <v>158</v>
+        <v>254</v>
       </c>
       <c r="F96" s="33" t="n">
         <v>6400</v>
@@ -30733,7 +30733,7 @@
         </is>
       </c>
       <c r="L96" s="55" t="n">
-        <v>0.604915729</v>
+        <v>0.6060273434272727</v>
       </c>
       <c r="M96" s="55" t="n">
         <v>0</v>
@@ -30790,7 +30790,7 @@
         </is>
       </c>
       <c r="L97" s="52" t="n">
-        <v>0.345951136</v>
+        <v>0.345951135625</v>
       </c>
       <c r="M97" s="52" t="n">
         <v>0</v>
@@ -30847,7 +30847,7 @@
         </is>
       </c>
       <c r="L98" s="55" t="n">
-        <v>1.645731742</v>
+        <v>1.645731742028572</v>
       </c>
       <c r="M98" s="55" t="n">
         <v>0</v>
@@ -30904,7 +30904,7 @@
         </is>
       </c>
       <c r="L99" s="52" t="n">
-        <v>1.070542346</v>
+        <v>1.070542345945455</v>
       </c>
       <c r="M99" s="52" t="n">
         <v>0</v>
@@ -30961,7 +30961,7 @@
         </is>
       </c>
       <c r="L100" s="55" t="n">
-        <v>1.982082574</v>
+        <v>1.982082574033334</v>
       </c>
       <c r="M100" s="55" t="n">
         <v>0</v>
@@ -31018,7 +31018,7 @@
         </is>
       </c>
       <c r="L101" s="52" t="n">
-        <v>2.043268413</v>
+        <v>2.043268412633334</v>
       </c>
       <c r="M101" s="52" t="n">
         <v>0</v>
@@ -31075,7 +31075,7 @@
         </is>
       </c>
       <c r="L102" s="55" t="n">
-        <v>2.704237109</v>
+        <v>2.704237108557143</v>
       </c>
       <c r="M102" s="55" t="n">
         <v>0</v>
@@ -31132,7 +31132,7 @@
         </is>
       </c>
       <c r="L103" s="52" t="n">
-        <v>2.09548897</v>
+        <v>2.095488969966667</v>
       </c>
       <c r="M103" s="52" t="n">
         <v>0</v>
@@ -31189,7 +31189,7 @@
         </is>
       </c>
       <c r="L104" s="55" t="n">
-        <v>1.266781043</v>
+        <v>1.2667810432</v>
       </c>
       <c r="M104" s="55" t="n">
         <v>0</v>
@@ -31246,7 +31246,7 @@
         </is>
       </c>
       <c r="L105" s="52" t="n">
-        <v>1.879828899</v>
+        <v>1.8798288988</v>
       </c>
       <c r="M105" s="52" t="n">
         <v>0</v>
@@ -31303,7 +31303,7 @@
         </is>
       </c>
       <c r="L106" s="55" t="n">
-        <v>1.64010932</v>
+        <v>1.640109320425</v>
       </c>
       <c r="M106" s="55" t="n">
         <v>0</v>
@@ -31360,7 +31360,7 @@
         </is>
       </c>
       <c r="L107" s="52" t="n">
-        <v>2.233200185</v>
+        <v>2.233200184888888</v>
       </c>
       <c r="M107" s="52" t="n">
         <v>0</v>
@@ -31417,7 +31417,7 @@
         </is>
       </c>
       <c r="L108" s="55" t="n">
-        <v>0.992750935</v>
+        <v>0.9927509353799999</v>
       </c>
       <c r="M108" s="55" t="n">
         <v>0</v>
@@ -31474,7 +31474,7 @@
         </is>
       </c>
       <c r="L109" s="52" t="n">
-        <v>0.732839327</v>
+        <v>0.7328393268</v>
       </c>
       <c r="M109" s="52" t="n">
         <v>0</v>
@@ -31531,7 +31531,7 @@
         </is>
       </c>
       <c r="L110" s="55" t="n">
-        <v>2.864954856</v>
+        <v>2.864954855866667</v>
       </c>
       <c r="M110" s="55" t="n">
         <v>0</v>
@@ -31588,7 +31588,7 @@
         </is>
       </c>
       <c r="L111" s="52" t="n">
-        <v>1.490180899</v>
+        <v>1.4901808992</v>
       </c>
       <c r="M111" s="52" t="n">
         <v>0</v>
@@ -31645,7 +31645,7 @@
         </is>
       </c>
       <c r="L112" s="55" t="n">
-        <v>1.797952564</v>
+        <v>1.797952564375</v>
       </c>
       <c r="M112" s="55" t="n">
         <v>0</v>
@@ -31702,7 +31702,7 @@
         </is>
       </c>
       <c r="L113" s="52" t="n">
-        <v>1.497879497</v>
+        <v>1.4978794974</v>
       </c>
       <c r="M113" s="52" t="n">
         <v>0</v>
@@ -31759,7 +31759,7 @@
         </is>
       </c>
       <c r="L114" s="55" t="n">
-        <v>0.96217569</v>
+        <v>0.9621756897249999</v>
       </c>
       <c r="M114" s="55" t="n">
         <v>0</v>
@@ -31816,7 +31816,7 @@
         </is>
       </c>
       <c r="L115" s="52" t="n">
-        <v>1.105963041</v>
+        <v>1.105963040772727</v>
       </c>
       <c r="M115" s="52" t="n">
         <v>0</v>
@@ -31873,7 +31873,7 @@
         </is>
       </c>
       <c r="L116" s="55" t="n">
-        <v>0.6878357349999999</v>
+        <v>0.6878357352666667</v>
       </c>
       <c r="M116" s="55" t="n">
         <v>0</v>
@@ -31930,7 +31930,7 @@
         </is>
       </c>
       <c r="L117" s="52" t="n">
-        <v>0.794613011</v>
+        <v>0.7946130110624999</v>
       </c>
       <c r="M117" s="52" t="n">
         <v>0</v>
@@ -31987,7 +31987,7 @@
         </is>
       </c>
       <c r="L118" s="55" t="n">
-        <v>1.827109111</v>
+        <v>1.827109111233333</v>
       </c>
       <c r="M118" s="55" t="n">
         <v>0</v>
@@ -32044,7 +32044,7 @@
         </is>
       </c>
       <c r="L119" s="52" t="n">
-        <v>0.9438241550000001</v>
+        <v>0.9438241546333334</v>
       </c>
       <c r="M119" s="52" t="n">
         <v>0</v>
@@ -32101,7 +32101,7 @@
         </is>
       </c>
       <c r="L120" s="55" t="n">
-        <v>0.9611953559999999</v>
+        <v>0.9611953559666667</v>
       </c>
       <c r="M120" s="55" t="n">
         <v>0</v>
@@ -32158,7 +32158,7 @@
         </is>
       </c>
       <c r="L121" s="52" t="n">
-        <v>1.568672415</v>
+        <v>1.568672415285714</v>
       </c>
       <c r="M121" s="52" t="n">
         <v>0</v>
@@ -32215,7 +32215,7 @@
         </is>
       </c>
       <c r="L122" s="55" t="n">
-        <v>0.438175951</v>
+        <v>0.4381759509571428</v>
       </c>
       <c r="M122" s="55" t="n">
         <v>0</v>
@@ -32272,7 +32272,7 @@
         </is>
       </c>
       <c r="L123" s="52" t="n">
-        <v>1.201215013</v>
+        <v>1.201215013333333</v>
       </c>
       <c r="M123" s="52" t="n">
         <v>0</v>
@@ -32329,7 +32329,7 @@
         </is>
       </c>
       <c r="L124" s="55" t="n">
-        <v>3.871111145</v>
+        <v>3.871111144666667</v>
       </c>
       <c r="M124" s="55" t="n">
         <v>0</v>
@@ -32386,7 +32386,7 @@
         </is>
       </c>
       <c r="L125" s="52" t="n">
-        <v>1.299525481</v>
+        <v>1.2995254806</v>
       </c>
       <c r="M125" s="52" t="n">
         <v>0</v>
@@ -32443,7 +32443,7 @@
         </is>
       </c>
       <c r="L126" s="55" t="n">
-        <v>2.4359826</v>
+        <v>2.435982600083333</v>
       </c>
       <c r="M126" s="55" t="n">
         <v>0</v>
@@ -32500,7 +32500,7 @@
         </is>
       </c>
       <c r="L127" s="52" t="n">
-        <v>5.153120375</v>
+        <v>5.1531203746</v>
       </c>
       <c r="M127" s="52" t="n">
         <v>0</v>
@@ -32557,7 +32557,7 @@
         </is>
       </c>
       <c r="L128" s="55" t="n">
-        <v>0.67950347</v>
+        <v>0.67950346995</v>
       </c>
       <c r="M128" s="55" t="n">
         <v>0</v>
@@ -32614,7 +32614,7 @@
         </is>
       </c>
       <c r="L129" s="52" t="n">
-        <v>0.816114042</v>
+        <v>0.8161140418444445</v>
       </c>
       <c r="M129" s="52" t="n">
         <v>0</v>
@@ -32671,7 +32671,7 @@
         </is>
       </c>
       <c r="L130" s="55" t="n">
-        <v>1.093907371</v>
+        <v>1.0939073714</v>
       </c>
       <c r="M130" s="55" t="n">
         <v>0</v>

--- a/web_dashboard/Orden_Fabricacion_MRP_Codiagro.xlsx
+++ b/web_dashboard/Orden_Fabricacion_MRP_Codiagro.xlsx
@@ -845,7 +845,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Horizonte: Oct 26 (N) + Nov 26 + Dic 26 (3 meses)  |  Ámbito: Global (Nacional + Exportación)  |  Exportación: Siempre Sobre Pedido  |  Fecha Emisión: 23/10/2026 08:38</t>
+          <t xml:space="preserve">  Horizonte: Oct 26 (N) + Nov 26 + Dic 26 (3 meses)  |  Ámbito: Global (Nacional + Exportación)  |  Exportación: Siempre Sobre Pedido  |  Fecha Emisión: 23/10/2026 08:50</t>
         </is>
       </c>
     </row>
@@ -22390,7 +22390,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Horizonte: Octubre 2026 - Diciembre 2026  |  Total Graneles Químicos a Fabricar en Planta  |  Fecha Emisión: 23/10/2026 08:38</t>
+          <t xml:space="preserve">  Horizonte: Octubre 2026 - Diciembre 2026  |  Total Graneles Químicos a Fabricar en Planta  |  Fecha Emisión: 23/10/2026 08:50</t>
         </is>
       </c>
     </row>
@@ -27213,7 +27213,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Premisa de Gestión: Previsiones exclusivamente del Mercado Nacional (España). La exportación se fabricará siempre sobre pedido.  |  Fecha: 23/10/2026 08:38</t>
+          <t xml:space="preserve">  Premisa de Gestión: Previsiones exclusivamente del Mercado Nacional (España). La exportación se fabricará siempre sobre pedido.  |  Fecha: 23/10/2026 08:50</t>
         </is>
       </c>
     </row>

--- a/web_dashboard/Orden_Fabricacion_MRP_Codiagro.xlsx
+++ b/web_dashboard/Orden_Fabricacion_MRP_Codiagro.xlsx
@@ -845,7 +845,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Horizonte: Oct 26 (N) + Nov 26 + Dic 26 (3 meses)  |  Ámbito: Global (Nacional + Exportación)  |  Exportación: Siempre Sobre Pedido  |  Fecha Emisión: 23/10/2026 08:50</t>
+          <t xml:space="preserve">  Horizonte: Oct 26 (N) + Nov 26 + Dic 26 (3 meses)  |  Ámbito: Global (Nacional + Exportación)  |  Exportación: Siempre Sobre Pedido  |  Fecha Emisión: 23/10/2026 08:56</t>
         </is>
       </c>
     </row>
@@ -22390,7 +22390,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Horizonte: Octubre 2026 - Diciembre 2026  |  Total Graneles Químicos a Fabricar en Planta  |  Fecha Emisión: 23/10/2026 08:50</t>
+          <t xml:space="preserve">  Horizonte: Octubre 2026 - Diciembre 2026  |  Total Graneles Químicos a Fabricar en Planta  |  Fecha Emisión: 23/10/2026 08:56</t>
         </is>
       </c>
     </row>
@@ -27213,7 +27213,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Premisa de Gestión: Previsiones exclusivamente del Mercado Nacional (España). La exportación se fabricará siempre sobre pedido.  |  Fecha: 23/10/2026 08:50</t>
+          <t xml:space="preserve">  Premisa de Gestión: Previsiones exclusivamente del Mercado Nacional (España). La exportación se fabricará siempre sobre pedido.  |  Fecha: 23/10/2026 08:56</t>
         </is>
       </c>
     </row>

--- a/web_dashboard/Orden_Fabricacion_MRP_Codiagro.xlsx
+++ b/web_dashboard/Orden_Fabricacion_MRP_Codiagro.xlsx
@@ -845,7 +845,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Horizonte: Oct 26 (N) + Nov 26 + Dic 26 (3 meses)  |  Ámbito: Global (Nacional + Exportación)  |  Exportación: Siempre Sobre Pedido  |  Fecha Emisión: 29/10/2026 07:32</t>
+          <t xml:space="preserve">  Horizonte: Oct 26 (N) + Nov 26 + Dic 26 (3 meses)  |  Ámbito: Global (Nacional + Exportación)  |  Exportación: Siempre Sobre Pedido  |  Fecha Emisión: 29/10/2026 08:06</t>
         </is>
       </c>
     </row>
@@ -21586,7 +21586,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Horizonte: Octubre 2026 - Diciembre 2026  |  Total Graneles Químicos a Fabricar en Planta  |  Fecha Emisión: 29/10/2026 07:32</t>
+          <t xml:space="preserve">  Horizonte: Octubre 2026 - Diciembre 2026  |  Total Graneles Químicos a Fabricar en Planta  |  Fecha Emisión: 29/10/2026 08:06</t>
         </is>
       </c>
     </row>
@@ -26409,7 +26409,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Premisa de Gestión: Previsiones exclusivamente del Mercado Nacional (España). La exportación se fabricará siempre sobre pedido.  |  Fecha: 29/10/2026 07:32</t>
+          <t xml:space="preserve">  Premisa de Gestión: Previsiones exclusivamente del Mercado Nacional (España). La exportación se fabricará siempre sobre pedido.  |  Fecha: 29/10/2026 08:06</t>
         </is>
       </c>
     </row>

--- a/web_dashboard/Orden_Fabricacion_MRP_Codiagro.xlsx
+++ b/web_dashboard/Orden_Fabricacion_MRP_Codiagro.xlsx
@@ -845,7 +845,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Horizonte: Oct 26 (N) + Nov 26 + Dic 26 (3 meses)  |  Ámbito: Global (Nacional + Exportación)  |  Exportación: Siempre Sobre Pedido  |  Fecha Emisión: 29/10/2026 08:06</t>
+          <t xml:space="preserve">  Horizonte: Oct 26 (N) + Nov 26 + Dic 26 (3 meses)  |  Ámbito: Global (Nacional + Exportación)  |  Exportación: Siempre Sobre Pedido  |  Fecha Emisión: 29/10/2026 09:19</t>
         </is>
       </c>
     </row>
@@ -21586,7 +21586,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Horizonte: Octubre 2026 - Diciembre 2026  |  Total Graneles Químicos a Fabricar en Planta  |  Fecha Emisión: 29/10/2026 08:06</t>
+          <t xml:space="preserve">  Horizonte: Octubre 2026 - Diciembre 2026  |  Total Graneles Químicos a Fabricar en Planta  |  Fecha Emisión: 29/10/2026 09:19</t>
         </is>
       </c>
     </row>
@@ -26409,7 +26409,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Premisa de Gestión: Previsiones exclusivamente del Mercado Nacional (España). La exportación se fabricará siempre sobre pedido.  |  Fecha: 29/10/2026 08:06</t>
+          <t xml:space="preserve">  Premisa de Gestión: Previsiones exclusivamente del Mercado Nacional (España). La exportación se fabricará siempre sobre pedido.  |  Fecha: 29/10/2026 09:19</t>
         </is>
       </c>
     </row>

--- a/web_dashboard/Orden_Fabricacion_MRP_Codiagro.xlsx
+++ b/web_dashboard/Orden_Fabricacion_MRP_Codiagro.xlsx
@@ -845,7 +845,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Horizonte: Oct 26 (N) + Nov 26 + Dic 26 (3 meses)  |  Ámbito: Global (Nacional + Exportación)  |  Exportación: Siempre Sobre Pedido  |  Fecha Emisión: 29/10/2026 09:19</t>
+          <t xml:space="preserve">  Horizonte: Oct 26 (N) + Nov 26 + Dic 26 (3 meses)  |  Ámbito: Global (Nacional + Exportación)  |  Exportación: Siempre Sobre Pedido  |  Fecha Emisión: 29/10/2026 11:16</t>
         </is>
       </c>
     </row>
@@ -21586,7 +21586,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Horizonte: Octubre 2026 - Diciembre 2026  |  Total Graneles Químicos a Fabricar en Planta  |  Fecha Emisión: 29/10/2026 09:19</t>
+          <t xml:space="preserve">  Horizonte: Octubre 2026 - Diciembre 2026  |  Total Graneles Químicos a Fabricar en Planta  |  Fecha Emisión: 29/10/2026 11:16</t>
         </is>
       </c>
     </row>
@@ -26409,7 +26409,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Premisa de Gestión: Previsiones exclusivamente del Mercado Nacional (España). La exportación se fabricará siempre sobre pedido.  |  Fecha: 29/10/2026 09:19</t>
+          <t xml:space="preserve">  Premisa de Gestión: Previsiones exclusivamente del Mercado Nacional (España). La exportación se fabricará siempre sobre pedido.  |  Fecha: 29/10/2026 11:16</t>
         </is>
       </c>
     </row>

--- a/web_dashboard/Orden_Fabricacion_MRP_Codiagro.xlsx
+++ b/web_dashboard/Orden_Fabricacion_MRP_Codiagro.xlsx
@@ -845,7 +845,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Horizonte: Oct 26 (N) + Nov 26 + Dic 26 (3 meses)  |  Ámbito: Global (Nacional + Exportación)  |  Exportación: Siempre Sobre Pedido  |  Fecha Emisión: 29/10/2026 11:16</t>
+          <t xml:space="preserve">  Horizonte: Oct 26 (N) + Nov 26 + Dic 26 (3 meses)  |  Ámbito: Global (Nacional + Exportación)  |  Exportación: Siempre Sobre Pedido  |  Fecha Emisión: 29/10/2026 11:42</t>
         </is>
       </c>
     </row>
@@ -21586,7 +21586,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Horizonte: Octubre 2026 - Diciembre 2026  |  Total Graneles Químicos a Fabricar en Planta  |  Fecha Emisión: 29/10/2026 11:16</t>
+          <t xml:space="preserve">  Horizonte: Octubre 2026 - Diciembre 2026  |  Total Graneles Químicos a Fabricar en Planta  |  Fecha Emisión: 29/10/2026 11:42</t>
         </is>
       </c>
     </row>
@@ -26409,7 +26409,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Premisa de Gestión: Previsiones exclusivamente del Mercado Nacional (España). La exportación se fabricará siempre sobre pedido.  |  Fecha: 29/10/2026 11:16</t>
+          <t xml:space="preserve">  Premisa de Gestión: Previsiones exclusivamente del Mercado Nacional (España). La exportación se fabricará siempre sobre pedido.  |  Fecha: 29/10/2026 11:42</t>
         </is>
       </c>
     </row>

--- a/web_dashboard/Orden_Fabricacion_MRP_Codiagro.xlsx
+++ b/web_dashboard/Orden_Fabricacion_MRP_Codiagro.xlsx
@@ -845,7 +845,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Horizonte: Oct 26 (N) + Nov 26 + Dic 26 (3 meses)  |  Ámbito: Global (Nacional + Exportación)  |  Exportación: Siempre Sobre Pedido  |  Fecha Emisión: 29/10/2026 11:42</t>
+          <t xml:space="preserve">  Horizonte: Oct 26 (N) + Nov 26 + Dic 26 (3 meses)  |  Ámbito: Global (Nacional + Exportación)  |  Exportación: Siempre Sobre Pedido  |  Fecha Emisión: 29/10/2026 12:42</t>
         </is>
       </c>
     </row>
@@ -21586,7 +21586,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Horizonte: Octubre 2026 - Diciembre 2026  |  Total Graneles Químicos a Fabricar en Planta  |  Fecha Emisión: 29/10/2026 11:42</t>
+          <t xml:space="preserve">  Horizonte: Octubre 2026 - Diciembre 2026  |  Total Graneles Químicos a Fabricar en Planta  |  Fecha Emisión: 29/10/2026 12:42</t>
         </is>
       </c>
     </row>
@@ -26409,7 +26409,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Premisa de Gestión: Previsiones exclusivamente del Mercado Nacional (España). La exportación se fabricará siempre sobre pedido.  |  Fecha: 29/10/2026 11:42</t>
+          <t xml:space="preserve">  Premisa de Gestión: Previsiones exclusivamente del Mercado Nacional (España). La exportación se fabricará siempre sobre pedido.  |  Fecha: 29/10/2026 12:42</t>
         </is>
       </c>
     </row>

--- a/web_dashboard/Orden_Fabricacion_MRP_Codiagro.xlsx
+++ b/web_dashboard/Orden_Fabricacion_MRP_Codiagro.xlsx
@@ -845,7 +845,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Horizonte: Oct 26 (N) + Nov 26 + Dic 26 (3 meses)  |  Ámbito: Global (Nacional + Exportación)  |  Exportación: Siempre Sobre Pedido  |  Fecha Emisión: 29/10/2026 12:42</t>
+          <t xml:space="preserve">  Horizonte: Oct 26 (N) + Nov 26 + Dic 26 (3 meses)  |  Ámbito: Global (Nacional + Exportación)  |  Exportación: Siempre Sobre Pedido  |  Fecha Emisión: 29/10/2026 13:17</t>
         </is>
       </c>
     </row>
@@ -21586,7 +21586,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Horizonte: Octubre 2026 - Diciembre 2026  |  Total Graneles Químicos a Fabricar en Planta  |  Fecha Emisión: 29/10/2026 12:42</t>
+          <t xml:space="preserve">  Horizonte: Octubre 2026 - Diciembre 2026  |  Total Graneles Químicos a Fabricar en Planta  |  Fecha Emisión: 29/10/2026 13:17</t>
         </is>
       </c>
     </row>
@@ -26409,7 +26409,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Premisa de Gestión: Previsiones exclusivamente del Mercado Nacional (España). La exportación se fabricará siempre sobre pedido.  |  Fecha: 29/10/2026 12:42</t>
+          <t xml:space="preserve">  Premisa de Gestión: Previsiones exclusivamente del Mercado Nacional (España). La exportación se fabricará siempre sobre pedido.  |  Fecha: 29/10/2026 13:17</t>
         </is>
       </c>
     </row>

--- a/web_dashboard/Orden_Fabricacion_MRP_Codiagro.xlsx
+++ b/web_dashboard/Orden_Fabricacion_MRP_Codiagro.xlsx
@@ -845,7 +845,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Horizonte: Oct 26 (N) + Nov 26 + Dic 26 (3 meses)  |  Ámbito: Global (Nacional + Exportación)  |  Exportación: Siempre Sobre Pedido  |  Fecha Emisión: 29/10/2026 13:17</t>
+          <t xml:space="preserve">  Horizonte: Oct 26 (N) + Nov 26 + Dic 26 (3 meses)  |  Ámbito: Global (Nacional + Exportación)  |  Exportación: Siempre Sobre Pedido  |  Fecha Emisión: 29/10/2026 13:40</t>
         </is>
       </c>
     </row>
@@ -21586,7 +21586,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Horizonte: Octubre 2026 - Diciembre 2026  |  Total Graneles Químicos a Fabricar en Planta  |  Fecha Emisión: 29/10/2026 13:17</t>
+          <t xml:space="preserve">  Horizonte: Octubre 2026 - Diciembre 2026  |  Total Graneles Químicos a Fabricar en Planta  |  Fecha Emisión: 29/10/2026 13:40</t>
         </is>
       </c>
     </row>
@@ -26409,7 +26409,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Premisa de Gestión: Previsiones exclusivamente del Mercado Nacional (España). La exportación se fabricará siempre sobre pedido.  |  Fecha: 29/10/2026 13:17</t>
+          <t xml:space="preserve">  Premisa de Gestión: Previsiones exclusivamente del Mercado Nacional (España). La exportación se fabricará siempre sobre pedido.  |  Fecha: 29/10/2026 13:40</t>
         </is>
       </c>
     </row>
